--- a/01_Thermal/B_results/single_annular_bemt_params_pchip.xlsx
+++ b/01_Thermal/B_results/single_annular_bemt_params_pchip.xlsx
@@ -470,22 +470,22 @@
         <v>0.2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.07018419497319295</v>
+        <v>0.06797329609303578</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2917526020043204</v>
+        <v>0.2915344141975234</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1764097096672853</v>
+        <v>0.1788218862659403</v>
       </c>
       <c r="E2" t="n">
-        <v>7.562844380899158</v>
+        <v>7.167467894583679</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6323323785528056</v>
+        <v>0.4378798599304675</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3588787940714297</v>
+        <v>0.1828318586006233</v>
       </c>
     </row>
     <row r="3">
@@ -493,22 +493,22 @@
         <v>0.21</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06350546508642989</v>
+        <v>0.06152968036192982</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2919594957438642</v>
+        <v>0.2917448556584337</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1830709821251981</v>
+        <v>0.1849548055877714</v>
       </c>
       <c r="E3" t="n">
-        <v>7.348101294008322</v>
+        <v>6.990271983850854</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6311891238072729</v>
+        <v>0.4378522457369501</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3420248160488482</v>
+        <v>0.1823418779670907</v>
       </c>
     </row>
     <row r="4">
@@ -516,22 +516,22 @@
         <v>0.22</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05696754081928197</v>
+        <v>0.05522079825589636</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2925675269382021</v>
+        <v>0.2923626854742379</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1894517782033113</v>
+        <v>0.1908625174022587</v>
       </c>
       <c r="E4" t="n">
-        <v>7.137727125837946</v>
+        <v>6.816625639523846</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6278298280988766</v>
+        <v>0.4377694730950648</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3251774345552331</v>
+        <v>0.1809139568221489</v>
       </c>
     </row>
     <row r="5">
@@ -539,22 +539,22 @@
         <v>0.23</v>
       </c>
       <c r="B5" t="n">
-        <v>0.05061781960005252</v>
+        <v>0.04909254392997003</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2935577205508944</v>
+        <v>0.2933676617945468</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1955131500086216</v>
+        <v>0.1965091511650544</v>
       </c>
       <c r="E5" t="n">
-        <v>6.93223945189445</v>
+        <v>6.646884518424427</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6223601942199197</v>
+        <v>0.4376316469128121</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3083366535040037</v>
+        <v>0.1786111262992818</v>
       </c>
     </row>
     <row r="6">
@@ -562,22 +562,22 @@
         <v>0.24</v>
       </c>
       <c r="B6" t="n">
-        <v>0.04450369885704489</v>
+        <v>0.04319081153918544</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2949111015455012</v>
+        <v>0.2947395427689706</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2012182355537857</v>
+        <v>0.2018594289437717</v>
       </c>
       <c r="E6" t="n">
-        <v>6.732155847684256</v>
+        <v>6.481404277374363</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6148859249627051</v>
+        <v>0.4374388720981928</v>
       </c>
       <c r="G6" t="n">
-        <v>0.291502476808579</v>
+        <v>0.1754964175319734</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         <v>0.25</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03867257601856244</v>
+        <v>0.03756149523857726</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2966086948855825</v>
+        <v>0.2964580865471199</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2065326610219915</v>
+        <v>0.2068790218141968</v>
       </c>
       <c r="E7" t="n">
-        <v>6.537993888713788</v>
+        <v>6.320540573195425</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6055127231195355</v>
+        <v>0.4371912535592073</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2746749083823782</v>
+        <v>0.1716328616537074</v>
       </c>
     </row>
     <row r="8">
@@ -608,22 +608,22 @@
         <v>0.26</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03317184851290846</v>
+        <v>0.0322504891831801</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2986315255346985</v>
+        <v>0.2985030512786049</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2114249076941792</v>
+        <v>0.2115349077658135</v>
       </c>
       <c r="E8" t="n">
-        <v>6.350271150489466</v>
+        <v>6.164649062709379</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5943462914827141</v>
+        <v>0.4368888962038561</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2578539521388205</v>
+        <v>0.1670834897979678</v>
       </c>
     </row>
     <row r="9">
@@ -631,22 +631,22 @@
         <v>0.27</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02804891376838633</v>
+        <v>0.02730368752802858</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3009606184564093</v>
+        <v>0.3008541951130363</v>
       </c>
       <c r="D9" t="n">
-        <v>0.215866637952786</v>
+        <v>0.2157957260546939</v>
       </c>
       <c r="E9" t="n">
-        <v>6.169505208517712</v>
+        <v>6.014085402737996</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5814923328445436</v>
+        <v>0.4365319049401399</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2410396119913248</v>
+        <v>0.1619113330982385</v>
       </c>
     </row>
     <row r="10">
@@ -654,22 +654,22 @@
         <v>0.28</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0233511692132994</v>
+        <v>0.02276698442815734</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3035769986142748</v>
+        <v>0.3034912762000245</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2198329756703292</v>
+        <v>0.219632122816334</v>
       </c>
       <c r="E10" t="n">
-        <v>5.99621363830495</v>
+        <v>5.869205250103041</v>
       </c>
       <c r="F10" t="n">
-        <v>0.567056549997327</v>
+        <v>0.4361203846760593</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2242318918533105</v>
+        <v>0.1561794226880035</v>
       </c>
     </row>
     <row r="11">
@@ -677,22 +677,22 @@
         <v>0.29</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01912601227595099</v>
+        <v>0.01868627403860103</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3064616909718555</v>
+        <v>0.3063940526891799</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2233027372654982</v>
+        <v>0.2230170827200622</v>
       </c>
       <c r="E11" t="n">
-        <v>5.830914015357599</v>
+        <v>5.730364261626288</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5511446457333672</v>
+        <v>0.4356544403196147</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2074307956381966</v>
+        <v>0.1499507897007465</v>
       </c>
     </row>
     <row r="12">
@@ -700,22 +700,22 @@
         <v>0.3</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01542084038464444</v>
+        <v>0.01510745051439427</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3095957204927112</v>
+        <v>0.3095422827301128</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2262586107369134</v>
+        <v>0.2259262415144025</v>
       </c>
       <c r="E12" t="n">
-        <v>5.674123915182084</v>
+        <v>5.597918094129504</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5338623228449669</v>
+        <v>0.4351341767788067</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1906363272594023</v>
+        <v>0.1432884652699516</v>
       </c>
     </row>
     <row r="13">
@@ -723,22 +723,22 @@
         <v>0.31</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01228305096768314</v>
+        <v>0.01207640801057169</v>
       </c>
       <c r="C13" t="n">
-        <v>0.312960112140402</v>
+        <v>0.3129157244724338</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2286872810378548</v>
+        <v>0.228338174481192</v>
       </c>
       <c r="E13" t="n">
-        <v>5.526360913284825</v>
+        <v>5.472222404434456</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5153152841244293</v>
+        <v>0.434559698961636</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1738484906303469</v>
+        <v>0.1362554805291026</v>
       </c>
     </row>
     <row r="14">
@@ -746,22 +746,22 @@
         <v>0.32</v>
       </c>
       <c r="B14" t="n">
-        <v>0.009760041453370352</v>
+        <v>0.009639040682167912</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3165358908784882</v>
+        <v>0.3164941360657534</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2305795012070668</v>
+        <v>0.2302346560849494</v>
       </c>
       <c r="E14" t="n">
-        <v>5.388142585172244</v>
+        <v>5.353632849362914</v>
       </c>
       <c r="F14" t="n">
-        <v>0.495609232364057</v>
+        <v>0.433931111776103</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1570672896644492</v>
+        <v>0.1289148666116834</v>
       </c>
     </row>
     <row r="15">
@@ -769,22 +769,22 @@
         <v>0.33</v>
       </c>
       <c r="B15" t="n">
-        <v>0.007899209270009472</v>
+        <v>0.007841242684217577</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3203040816705299</v>
+        <v>0.3202572756596819</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2319301096954775</v>
+        <v>0.2316008864701806</v>
       </c>
       <c r="E15" t="n">
-        <v>5.259986506350764</v>
+        <v>5.242505085736647</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4748498703561529</v>
+        <v>0.4332485201302084</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1402927282751285</v>
+        <v>0.1213296546511779</v>
       </c>
     </row>
     <row r="16">
@@ -792,22 +792,22 @@
         <v>0.34</v>
       </c>
       <c r="B16" t="n">
-        <v>0.006747951845903816</v>
+        <v>0.006728908171755314</v>
       </c>
       <c r="C16" t="n">
-        <v>0.324245709480087</v>
+        <v>0.3241849014038298</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2327379953026146</v>
+        <v>0.2324256809177603</v>
       </c>
       <c r="E16" t="n">
-        <v>5.142410252326805</v>
+        <v>5.139194770377421</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4531429008930202</v>
+        <v>0.4325120289319526</v>
       </c>
       <c r="G16" t="n">
-        <v>0.123524810375804</v>
+        <v>0.1135628757810701</v>
       </c>
     </row>
     <row r="17">
@@ -815,22 +815,22 @@
         <v>0.35</v>
       </c>
       <c r="B17" t="n">
-        <v>0.006353666609356753</v>
+        <v>0.006347931299815749</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3283417992707197</v>
+        <v>0.3282567714478075</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2330060120385242</v>
+        <v>0.2327016189146754</v>
       </c>
       <c r="E17" t="n">
-        <v>5.035931398606792</v>
+        <v>5.044057560107008</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4305940267669616</v>
+        <v>0.4317217430893363</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1067635398798949</v>
+        <v>0.1056775611348438</v>
       </c>
     </row>
     <row r="18">
@@ -838,22 +838,22 @@
         <v>0.36</v>
       </c>
       <c r="B18" t="n">
-        <v>0.006487551683570324</v>
+        <v>0.006475267873536688</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3347016784102876</v>
+        <v>0.3344108583673852</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2320591288425236</v>
+        <v>0.2319448765114562</v>
       </c>
       <c r="E18" t="n">
-        <v>4.937589477918626</v>
+        <v>4.955441024838044</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3957438916385362</v>
+        <v>0.4147130705969681</v>
       </c>
       <c r="G18" t="n">
-        <v>0.08905373101632114</v>
+        <v>0.09547999132234394</v>
       </c>
     </row>
     <row r="19">
@@ -861,22 +861,22 @@
         <v>0.37</v>
       </c>
       <c r="B19" t="n">
-        <v>0.006864298055194556</v>
+        <v>0.006833587069356076</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3450135041552205</v>
+        <v>0.3441977455521746</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2294152413513295</v>
+        <v>0.2298286182644702</v>
       </c>
       <c r="E19" t="n">
-        <v>4.843938962337156</v>
+        <v>4.87125031125215</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3394217458664177</v>
+        <v>0.3683387937098757</v>
       </c>
       <c r="G19" t="n">
-        <v>0.06971309817123372</v>
+        <v>0.08120663396109426</v>
       </c>
     </row>
     <row r="20">
@@ -884,22 +884,22 @@
         <v>0.38</v>
       </c>
       <c r="B20" t="n">
-        <v>0.007446542447704734</v>
+        <v>0.007387353099258765</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3586265463019336</v>
+        <v>0.3570161073725492</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2253883592241607</v>
+        <v>0.2265959533210997</v>
       </c>
       <c r="E20" t="n">
-        <v>4.754769836389219</v>
+        <v>4.79117744132457</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2651662022900814</v>
+        <v>0.297125078726688</v>
       </c>
       <c r="G20" t="n">
-        <v>0.04915099549389787</v>
+        <v>0.06356580069609682</v>
       </c>
     </row>
     <row r="21">
@@ -907,22 +907,22 @@
         <v>0.39</v>
       </c>
       <c r="B21" t="n">
-        <v>0.00819692158457614</v>
+        <v>0.008101030175229612</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3748900746468424</v>
+        <v>0.372264618198882</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2203027043488396</v>
+        <v>0.2224967607340952</v>
       </c>
       <c r="E21" t="n">
-        <v>4.669872084601645</v>
+        <v>4.71491443703055</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1765158737490022</v>
+        <v>0.205598091946034</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02777677713357885</v>
+        <v>0.04326580317235378</v>
       </c>
     </row>
     <row r="22">
@@ -930,22 +930,22 @@
         <v>0.4</v>
       </c>
       <c r="B22" t="n">
-        <v>0.009078072189284057</v>
+        <v>0.008939082509253468</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3931533589863623</v>
+        <v>0.3893419524015466</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2144770525347854</v>
+        <v>0.217777753074012</v>
       </c>
       <c r="E22" t="n">
-        <v>4.589035691501275</v>
+        <v>4.642153320345336</v>
       </c>
       <c r="F22" t="n">
-        <v>0.07700937308265507</v>
+        <v>0.09828399966654283</v>
       </c>
       <c r="G22" t="n">
-        <v>0.005999797239541894</v>
+        <v>0.02101495303486722</v>
       </c>
     </row>
     <row r="23">
@@ -953,22 +953,22 @@
         <v>0.41</v>
       </c>
       <c r="B23" t="n">
-        <v>0.01005263098530377</v>
+        <v>0.009865974313315189</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4127656691169088</v>
+        <v>0.4076467843509159</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2082130860670232</v>
+        <v>0.2126749737337219</v>
       </c>
       <c r="E23" t="n">
-        <v>4.512050641614941</v>
+        <v>4.572586113244171</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.02981468686948482</v>
+        <v>-0.02029103181315667</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.01577059003894773</v>
+        <v>-0.002478438071360778</v>
       </c>
     </row>
     <row r="24">
@@ -976,22 +976,22 @@
         <v>0.42</v>
       </c>
       <c r="B24" t="n">
-        <v>0.01108323469611055</v>
+        <v>0.01084616979939963</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4330762748348972</v>
+        <v>0.4265777884173634</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2017878068476977</v>
+        <v>0.2074087604996193</v>
       </c>
       <c r="E24" t="n">
-        <v>4.438706919469478</v>
+        <v>4.505904837702301</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1404176932679425</v>
+        <v>-0.1456008361944354</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.03712503055262478</v>
+        <v>-0.02650605850132806</v>
       </c>
     </row>
     <row r="25">
@@ -999,22 +999,22 @@
         <v>0.43</v>
       </c>
       <c r="B25" t="n">
-        <v>0.01213252004517969</v>
+        <v>0.01184413317949164</v>
       </c>
       <c r="C25" t="n">
-        <v>0.453434445936743</v>
+        <v>0.4455336389712624</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1954497215414201</v>
+        <v>0.2021810349777272</v>
       </c>
       <c r="E25" t="n">
-        <v>4.368794509591724</v>
+        <v>4.44180151569497</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2512610332732431</v>
+        <v>-0.2731192471786643</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.05765417015222402</v>
+        <v>-0.05035959661003257</v>
       </c>
     </row>
     <row r="26">
@@ -1022,22 +1022,22 @@
         <v>0.44</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01316312375598647</v>
+        <v>0.01282432866557608</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4731894522188615</v>
+        <v>0.4639130103829858</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1894183089248338</v>
+        <v>0.1971746704610571</v>
       </c>
       <c r="E26" t="n">
-        <v>4.302103396508512</v>
+        <v>4.379968169197426</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3588060940459107</v>
+        <v>-0.3983200984672141</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0769486546884801</v>
+        <v>-0.0733307407524721</v>
       </c>
     </row>
     <row r="27">
@@ -1045,22 +1045,22 @@
         <v>0.45</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01413768255200618</v>
+        <v>0.01375122046963779</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4916905634776683</v>
+        <v>0.4811145770229074</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1838862022427311</v>
+        <v>0.1925546446748821</v>
       </c>
       <c r="E27" t="n">
-        <v>4.238423564746678</v>
+        <v>4.32009682018491</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4595142627464719</v>
+        <v>-0.5166772237614566</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.09459913001212798</v>
+        <v>-0.0947111792836447</v>
       </c>
     </row>
     <row r="28">
@@ -1068,22 +1068,22 @@
         <v>0.46</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0150188331567141</v>
+        <v>0.01458927280366165</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5082870495095786</v>
+        <v>0.4965370132614001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1790235429719732</v>
+        <v>0.1884706892941055</v>
       </c>
       <c r="E28" t="n">
-        <v>4.177544998833058</v>
+        <v>4.261879490632669</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.5498469265354504</v>
+        <v>-0.6236644567627627</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.1101962419739023</v>
+        <v>-0.1137926005585482</v>
       </c>
     </row>
     <row r="29">
@@ -1091,22 +1091,22 @@
         <v>0.47</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0157692122935855</v>
+        <v>0.0153029498796325</v>
       </c>
       <c r="C29" t="n">
-        <v>0.522328180111008</v>
+        <v>0.5095789934688372</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1749840621520824</v>
+        <v>0.1850611948124135</v>
       </c>
       <c r="E29" t="n">
-        <v>4.119257683294487</v>
+        <v>4.205008202515948</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.6262654725733721</v>
+        <v>-0.7147556311725025</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.1233306364245379</v>
+        <v>-0.1298666929321806</v>
       </c>
     </row>
     <row r="30">
@@ -1114,22 +1114,22 @@
         <v>0.48</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01635145668609568</v>
+        <v>0.01585671590953518</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5331632250783718</v>
+        <v>0.5196391920155921</v>
       </c>
       <c r="D30" t="n">
-        <v>0.171912600167826</v>
+        <v>0.1824582081114278</v>
       </c>
       <c r="E30" t="n">
-        <v>4.063351602657799</v>
+        <v>4.149174977809992</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6852312880207612</v>
+        <v>-0.7854245806920486</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1335929592147694</v>
+        <v>-0.1422251447595396</v>
       </c>
     </row>
     <row r="31">
@@ -1137,22 +1137,22 @@
         <v>0.49</v>
       </c>
       <c r="B31" t="n">
-        <v>0.01672820305771991</v>
+        <v>0.01621503510535457</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5401414542080853</v>
+        <v>0.5261162832720379</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1699539718844681</v>
+        <v>0.1807934647747625</v>
       </c>
       <c r="E31" t="n">
-        <v>4.009616741449832</v>
+        <v>4.094071838490045</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.7232057600381427</v>
+        <v>-0.8311451390227695</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1405738561953316</v>
+        <v>-0.1501596443956231</v>
       </c>
     </row>
     <row r="32">
@@ -1160,22 +1160,22 @@
         <v>0.5</v>
       </c>
       <c r="B32" t="n">
-        <v>0.01686208813193348</v>
+        <v>0.01634237167907551</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5426121372965643</v>
+        <v>0.528408941608548</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1692633177736018</v>
+        <v>0.1802055269612738</v>
       </c>
       <c r="E32" t="n">
-        <v>3.957843084197418</v>
+        <v>4.039390806531354</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7366502757860423</v>
+        <v>-0.8473911398660394</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1438639732169592</v>
+        <v>-0.1529618801954292</v>
       </c>
     </row>
     <row r="33">
@@ -1183,22 +1183,22 @@
         <v>0.51</v>
       </c>
       <c r="B33" t="n">
-        <v>0.01681780971411207</v>
+        <v>0.0162946423322595</v>
       </c>
       <c r="C33" t="n">
-        <v>0.541662660950042</v>
+        <v>0.5275427073397032</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1698417784651304</v>
+        <v>0.1808509440993696</v>
       </c>
       <c r="E33" t="n">
-        <v>3.907676752898404</v>
+        <v>3.98495921905333</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7351770924698585</v>
+        <v>-0.8452224545634464</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.145142818401113</v>
+        <v>-0.152939686886667</v>
       </c>
     </row>
     <row r="34">
@@ -1206,22 +1206,22 @@
         <v>0.52</v>
       </c>
       <c r="B34" t="n">
-        <v>0.01668958676427421</v>
+        <v>0.01615654286864298</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5389182841128334</v>
+        <v>0.5250389343160562</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1715270298331087</v>
+        <v>0.1827303195802273</v>
       </c>
       <c r="E34" t="n">
-        <v>3.858874823067712</v>
+        <v>3.930851557868982</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7308785964461246</v>
+        <v>-0.8389106477735785</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.1463631604394563</v>
+        <v>-0.1528743935630462</v>
       </c>
     </row>
     <row r="35">
@@ -1229,22 +1229,22 @@
         <v>0.53</v>
       </c>
       <c r="B35" t="n">
-        <v>0.01648433773785939</v>
+        <v>0.01593570615347324</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5345350850884767</v>
+        <v>0.5210400172119373</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1742574945321267</v>
+        <v>0.1857741688741759</v>
       </c>
       <c r="E35" t="n">
-        <v>3.811393709507803</v>
+        <v>3.877130561993947</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.723936368602066</v>
+        <v>-0.8287470931733026</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1475255360380281</v>
+        <v>-0.1527679301285654</v>
       </c>
     </row>
     <row r="36">
@@ -1252,22 +1252,22 @@
         <v>0.54</v>
       </c>
       <c r="B36" t="n">
-        <v>0.01620898109030716</v>
+        <v>0.01563976505199756</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5286691421805096</v>
+        <v>0.5156883507016774</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1779859509345061</v>
+        <v>0.1899295939165543</v>
       </c>
       <c r="E36" t="n">
-        <v>3.76518982702113</v>
+        <v>3.823858970443865</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7145319898249084</v>
+        <v>-0.8150231644394859</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.1486304819028673</v>
+        <v>-0.152622226487223</v>
       </c>
     </row>
     <row r="37">
@@ -1275,22 +1275,22 @@
         <v>0.55</v>
       </c>
       <c r="B37" t="n">
-        <v>0.01587043527705703</v>
+        <v>0.0152763524294632</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5214765336924703</v>
+        <v>0.509126329459607</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1826753049677799</v>
+        <v>0.1951552645891703</v>
       </c>
       <c r="E37" t="n">
-        <v>3.720219590410151</v>
+        <v>3.771099522234373</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7028470410018773</v>
+        <v>-0.798030235248995</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.1496785347400128</v>
+        <v>-0.1524392125430176</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B38" t="n">
-        <v>0.01547561875354851</v>
+        <v>0.01485310115111746</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5131133379278965</v>
+        <v>0.5014963481600567</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1882947967843802</v>
+        <v>0.2014169160532863</v>
       </c>
       <c r="E38" t="n">
-        <v>3.676439414477323</v>
+        <v>3.718914956381107</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.6890631030201987</v>
+        <v>-0.7780596792786969</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.1506702312555035</v>
+        <v>-0.1522208181999478</v>
       </c>
     </row>
     <row r="39">
@@ -1321,22 +1321,22 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B39" t="n">
-        <v>0.01503144997522114</v>
+        <v>0.0143776440822076</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5037356331903261</v>
+        <v>0.4929408014773573</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1948164646502348</v>
+        <v>0.208683144025425</v>
       </c>
       <c r="E39" t="n">
-        <v>3.633805714025102</v>
+        <v>3.667368011899708</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.673361756767098</v>
+        <v>-0.7554028702054586</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.1516061081553783</v>
+        <v>-0.1519689733620122</v>
       </c>
     </row>
     <row r="40">
@@ -1344,22 +1344,22 @@
         <v>0.5800000000000001</v>
       </c>
       <c r="B40" t="n">
-        <v>0.01454484739751442</v>
+        <v>0.01385761408798091</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4934994977832972</v>
+        <v>0.4836020840858394</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2022117359533517</v>
+        <v>0.2169213399615852</v>
       </c>
       <c r="E40" t="n">
-        <v>3.592274903855945</v>
+        <v>3.616521427805812</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.6559245831298007</v>
+        <v>-0.730351181706147</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1524867021456762</v>
+        <v>-0.1516856079332092</v>
       </c>
     </row>
     <row r="41">
@@ -1367,22 +1367,22 @@
         <v>0.5900000000000001</v>
       </c>
       <c r="B41" t="n">
-        <v>0.01402272947586789</v>
+        <v>0.01330064403368468</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4825610100103476</v>
+        <v>0.4736225906598336</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2104480560247875</v>
+        <v>0.2260936596895782</v>
       </c>
       <c r="E41" t="n">
-        <v>3.551803398772309</v>
+        <v>3.566437943115058</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.6369331629955327</v>
+        <v>-0.703195987457629</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1533125499324361</v>
+        <v>-0.1513726518175375</v>
       </c>
     </row>
     <row r="42">
@@ -1390,22 +1390,22 @@
         <v>0.6000000000000001</v>
       </c>
       <c r="B42" t="n">
-        <v>0.01347201466572106</v>
+        <v>0.01271436678456617</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4710762481750154</v>
+        <v>0.4631447158736705</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2194855031596639</v>
+        <v>0.2361529670181133</v>
       </c>
       <c r="E42" t="n">
-        <v>3.512347613576651</v>
+        <v>3.517180296843082</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.6165690772515195</v>
+        <v>-0.6742286611367714</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.1540841882216969</v>
+        <v>-0.1510320349189956</v>
       </c>
     </row>
     <row r="43">
@@ -1413,22 +1413,22 @@
         <v>0.6100000000000001</v>
       </c>
       <c r="B43" t="n">
-        <v>0.01289962142251345</v>
+        <v>0.01210641520587266</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4592012905808383</v>
+        <v>0.4523108544016808</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2292733754408053</v>
+        <v>0.2470387416145174</v>
       </c>
       <c r="E43" t="n">
-        <v>3.473863963071427</v>
+        <v>3.468811228005524</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.5950139067849869</v>
+        <v>-0.6437405764204414</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.1548021537194975</v>
+        <v>-0.150665687141582</v>
       </c>
     </row>
     <row r="44">
@@ -1436,22 +1436,22 @@
         <v>0.62</v>
       </c>
       <c r="B44" t="n">
-        <v>0.0123124682016846</v>
+        <v>0.01148442216285144</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4470922155313544</v>
+        <v>0.4412634009181954</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2397467734445007</v>
+        <v>0.2586729901556082</v>
       </c>
       <c r="E44" t="n">
-        <v>3.436308862059094</v>
+        <v>3.421393475618021</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.5724492324831606</v>
+        <v>-0.612023106985506</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.1554669831318769</v>
+        <v>-0.1502755383892954</v>
       </c>
     </row>
     <row r="45">
@@ -1459,22 +1459,22 @@
         <v>0.63</v>
       </c>
       <c r="B45" t="n">
-        <v>0.011717473458674</v>
+        <v>0.01085602052074978</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4349051013301014</v>
+        <v>0.4301447500975444</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2508232435407919</v>
+        <v>0.2709562524242994</v>
       </c>
       <c r="E45" t="n">
-        <v>3.399638725342108</v>
+        <v>3.374989778696211</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.5490566352332659</v>
+        <v>-0.5793676265088316</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.1560792131648739</v>
+        <v>-0.1498635185661342</v>
       </c>
     </row>
     <row r="46">
@@ -1482,22 +1482,22 @@
         <v>0.64</v>
       </c>
       <c r="B46" t="n">
-        <v>0.01112155564892119</v>
+        <v>0.01022884314481496</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4227960262806174</v>
+        <v>0.4190972966140588</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2623995892817516</v>
+        <v>0.2837638493956167</v>
       </c>
       <c r="E46" t="n">
-        <v>3.363809967722927</v>
+        <v>3.329662876255732</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.5250176959225286</v>
+        <v>-0.5460655086672853</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.1566393805245274</v>
+        <v>-0.149431557576097</v>
       </c>
     </row>
     <row r="47">
@@ -1505,22 +1505,22 @@
         <v>0.65</v>
       </c>
       <c r="B47" t="n">
-        <v>0.01053163322786569</v>
+        <v>0.009610522900294263</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4109210686864403</v>
+        <v>0.4082634351420691</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2743490022932093</v>
+        <v>0.2969425767747055</v>
       </c>
       <c r="E47" t="n">
-        <v>3.328779004004006</v>
+        <v>3.285475507312221</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.5005139954381742</v>
+        <v>-0.5124081271377342</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.1571480219168765</v>
+        <v>-0.1489815853231823</v>
       </c>
     </row>
     <row r="48">
@@ -1528,22 +1528,22 @@
         <v>0.66</v>
       </c>
       <c r="B48" t="n">
-        <v>0.00995462465094701</v>
+        <v>0.009008692652434962</v>
       </c>
       <c r="C48" t="n">
-        <v>0.399436306851108</v>
+        <v>0.3977855603559061</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2865187070359454</v>
+        <v>0.3103081017138736</v>
       </c>
       <c r="E48" t="n">
-        <v>3.294502248987804</v>
+        <v>3.242490410881318</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.4757271146674286</v>
+        <v>-0.4786868555970449</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.15760567404796</v>
+        <v>-0.1485155317113888</v>
       </c>
     </row>
     <row r="49">
@@ -1551,22 +1551,22 @@
         <v>0.67</v>
       </c>
       <c r="B49" t="n">
-        <v>0.009397448373604681</v>
+        <v>0.008430985266484338</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3884978190781584</v>
+        <v>0.3878060669299003</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2987283524938162</v>
+        <v>0.3236433677183853</v>
       </c>
       <c r="E49" t="n">
-        <v>3.260936117476775</v>
+        <v>3.200770325978658</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.4508386344975173</v>
+        <v>-0.4451930677220849</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.1580128736238169</v>
+        <v>-0.1480353266447149</v>
       </c>
     </row>
     <row r="50">
@@ -1574,22 +1574,22 @@
         <v>0.6799999999999999</v>
       </c>
       <c r="B50" t="n">
-        <v>0.008867022851278225</v>
+        <v>0.007885033607689676</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3782616836711296</v>
+        <v>0.3784673495383825</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3107694138298008</v>
+        <v>0.3366983466614017</v>
       </c>
       <c r="E50" t="n">
-        <v>3.228037024273378</v>
+        <v>3.160377991619881</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.4260301358156662</v>
+        <v>-0.4122181371897209</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.158370157350486</v>
+        <v>-0.1475429000271593</v>
       </c>
     </row>
     <row r="51">
@@ -1597,22 +1597,22 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="B51" t="n">
-        <v>0.008370266539407152</v>
+        <v>0.007378470541298242</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3688839789335593</v>
+        <v>0.3699118028556831</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3224058828694377</v>
+        <v>0.3491914896964313</v>
       </c>
       <c r="E51" t="n">
-        <v>3.195761384180068</v>
+        <v>3.121376146820624</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.4014831995091005</v>
+        <v>-0.3800534376768194</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.1586780619340063</v>
+        <v>-0.1470401817627204</v>
       </c>
     </row>
     <row r="52">
@@ -1620,22 +1620,22 @@
         <v>0.7</v>
       </c>
       <c r="B52" t="n">
-        <v>0.007914097893430991</v>
+        <v>0.006918928932557326</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3605207831689855</v>
+        <v>0.3622818215561329</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3333765218018689</v>
+        <v>0.3608132123049669</v>
       </c>
       <c r="E52" t="n">
-        <v>3.164065611999303</v>
+        <v>3.083827530596526</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.3773794064650461</v>
+        <v>-0.3489903428602475</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.1589371240804167</v>
+        <v>-0.1465291017553969</v>
       </c>
     </row>
     <row r="53">
@@ -1643,22 +1643,22 @@
         <v>0.71</v>
       </c>
       <c r="B53" t="n">
-        <v>0.007505435368789256</v>
+        <v>0.006514041646714194</v>
       </c>
       <c r="C53" t="n">
-        <v>0.353328174680946</v>
+        <v>0.3557198003140625</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3433989235169817</v>
+        <v>0.371231694585772</v>
       </c>
       <c r="E53" t="n">
-        <v>3.132906122533539</v>
+        <v>3.047794881963223</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3539003375707284</v>
+        <v>-0.3193202264168721</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.1591478804957561</v>
+        <v>-0.1460115899091873</v>
       </c>
     </row>
     <row r="54">
@@ -1666,22 +1666,22 @@
         <v>0.72</v>
       </c>
       <c r="B54" t="n">
-        <v>0.007151197420921476</v>
+        <v>0.006171441549016141</v>
       </c>
       <c r="C54" t="n">
-        <v>0.347462231772979</v>
+        <v>0.3503681338038024</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3521755590362515</v>
+        <v>0.3801011795032067</v>
       </c>
       <c r="E54" t="n">
-        <v>3.102239330585233</v>
+        <v>3.013340939936354</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3312275737133733</v>
+        <v>-0.2913344620235604</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.1593108678860634</v>
+        <v>-0.14548957612809</v>
       </c>
     </row>
     <row r="55">
@@ -1689,22 +1689,22 @@
         <v>0.73</v>
       </c>
       <c r="B55" t="n">
-        <v>0.006858302505267172</v>
+        <v>0.005898761504710437</v>
       </c>
       <c r="C55" t="n">
-        <v>0.3430790327486224</v>
+        <v>0.3463692166996836</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3594018938302244</v>
+        <v>0.3870728055347544</v>
       </c>
       <c r="E55" t="n">
-        <v>3.072021650956842</v>
+        <v>2.980528443531557</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3095426957802066</v>
+        <v>-0.2653244233571793</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.1594266229573776</v>
+        <v>-0.1449649903161038</v>
       </c>
     </row>
     <row r="56">
@@ -1712,22 +1712,22 @@
         <v>0.74</v>
       </c>
       <c r="B56" t="n">
-        <v>0.006633669077265855</v>
+        <v>0.005703634379044357</v>
       </c>
       <c r="C56" t="n">
-        <v>0.3403346559114139</v>
+        <v>0.3438654436760365</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3647765196956815</v>
+        <v>0.3918078171176564</v>
       </c>
       <c r="E56" t="n">
-        <v>3.042209498450822</v>
+        <v>2.94942013176447</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2890272846584535</v>
+        <v>-0.2415814840945955</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.1594956824157376</v>
+        <v>-0.1444397623772271</v>
       </c>
     </row>
     <row r="57">
@@ -1735,22 +1735,22 @@
         <v>0.75</v>
       </c>
       <c r="B57" t="n">
-        <v>0.006484215592357054</v>
+        <v>0.005593693037265187</v>
       </c>
       <c r="C57" t="n">
-        <v>0.3393851795648914</v>
+        <v>0.3429992094071918</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3680130807013923</v>
+        <v>0.3939927639831015</v>
       </c>
       <c r="E57" t="n">
-        <v>3.012759287869629</v>
+        <v>2.920078743650731</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2698629212353399</v>
+        <v>-0.2203970179126757</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.1595185829671823</v>
+        <v>-0.1439158222154585</v>
       </c>
     </row>
     <row r="58">
@@ -1758,22 +1758,22 @@
         <v>0.76</v>
       </c>
       <c r="B58" t="n">
-        <v>0.006375775243100341</v>
+        <v>0.005529743629648109</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3395092885607871</v>
+        <v>0.343104541962123</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3700711920106864</v>
+        <v>0.3947858979570568</v>
       </c>
       <c r="E58" t="n">
-        <v>2.983158148539944</v>
+        <v>2.891545047302296</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.2510882913558547</v>
+        <v>-0.2003559711591471</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.1594649132165568</v>
+        <v>-0.1433845817729934</v>
       </c>
     </row>
     <row r="59">
@@ -1781,22 +1781,22 @@
         <v>0.77</v>
       </c>
       <c r="B59" t="n">
-        <v>0.006269603721758836</v>
+        <v>0.005467509245747987</v>
       </c>
       <c r="C59" t="n">
-        <v>0.3398719760148123</v>
+        <v>0.3434124863293022</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3720877798330186</v>
+        <v>0.3955363161429449</v>
       </c>
       <c r="E59" t="n">
-        <v>2.952979409177475</v>
+        <v>2.862857047043099</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.2316626588961853</v>
+        <v>-0.1798891121007686</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.1593053802151518</v>
+        <v>-0.1428354428538349</v>
       </c>
     </row>
     <row r="60">
@@ -1804,22 +1804,22 @@
         <v>0.78</v>
       </c>
       <c r="B60" t="n">
-        <v>0.006165753233327372</v>
+        <v>0.005406998159731621</v>
       </c>
       <c r="C60" t="n">
-        <v>0.3404587826264744</v>
+        <v>0.3439109625623075</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3740616334824202</v>
+        <v>0.3962456879301783</v>
       </c>
       <c r="E60" t="n">
-        <v>2.922308783668222</v>
+        <v>2.834073336206751</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.2116484717903549</v>
+        <v>-0.1590565472929554</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.1590421983386746</v>
+        <v>-0.142267320154693</v>
       </c>
     </row>
     <row r="61">
@@ -1827,22 +1827,22 @@
         <v>0.79</v>
       </c>
       <c r="B61" t="n">
-        <v>0.006064275982800783</v>
+        <v>0.00534821864576581</v>
       </c>
       <c r="C61" t="n">
-        <v>0.3412552490952807</v>
+        <v>0.3445878907147172</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3759915476764959</v>
+        <v>0.3969157096226718</v>
       </c>
       <c r="E61" t="n">
-        <v>2.891231985898186</v>
+        <v>2.805252508126857</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.1911081779723867</v>
+        <v>-0.1379183832911231</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.1586775819628322</v>
+        <v>-0.1416791283722779</v>
       </c>
     </row>
     <row r="62">
@@ -1850,22 +1850,22 @@
         <v>0.8</v>
       </c>
       <c r="B62" t="n">
-        <v>0.005965224175173907</v>
+        <v>0.005291178978017351</v>
       </c>
       <c r="C62" t="n">
-        <v>0.3422469161207384</v>
+        <v>0.3454311908401098</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3778763235462227</v>
+        <v>0.3975481026069751</v>
       </c>
       <c r="E62" t="n">
-        <v>2.859834729753368</v>
+        <v>2.776453156137026</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.170104225376304</v>
+        <v>-0.1165347266506869</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.158213745463332</v>
+        <v>-0.1410697822032996</v>
       </c>
     </row>
     <row r="63">
@@ -1873,22 +1873,22 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B63" t="n">
-        <v>0.005868650015441576</v>
+        <v>0.005235887430653046</v>
       </c>
       <c r="C63" t="n">
-        <v>0.3434193244023548</v>
+        <v>0.3464287829920633</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3797147696595237</v>
+        <v>0.3981446115871652</v>
       </c>
       <c r="E63" t="n">
-        <v>2.828202729119769</v>
+        <v>2.747733873570865</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.1486990619361301</v>
+        <v>-0.09496568392706227</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.1576529032158812</v>
+        <v>-0.1404381963444682</v>
       </c>
     </row>
     <row r="64">
@@ -1896,22 +1896,22 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B64" t="n">
-        <v>0.005774605708598626</v>
+        <v>0.005182352277839693</v>
       </c>
       <c r="C64" t="n">
-        <v>0.3447580146396374</v>
+        <v>0.3475685872241561</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3815057030576807</v>
+        <v>0.3987070028894285</v>
       </c>
       <c r="E64" t="n">
-        <v>2.796421697883389</v>
+        <v>2.719153253761984</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.1269551355858882</v>
+        <v>-0.07327136167566457</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.156997269596187</v>
+        <v>-0.1397832854924937</v>
       </c>
     </row>
     <row r="65">
@@ -1919,22 +1919,22 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B65" t="n">
-        <v>0.005683143459639893</v>
+        <v>0.005130581793744091</v>
       </c>
       <c r="C65" t="n">
-        <v>0.3462485275320932</v>
+        <v>0.3488385235899664</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3832479503036077</v>
+        <v>0.3992370628390471</v>
       </c>
       <c r="E65" t="n">
-        <v>2.764577349930229</v>
+        <v>2.690769890043988</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.1049348942596015</v>
+        <v>-0.05151186645190917</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.1562490589799566</v>
+        <v>-0.1391039643440863</v>
       </c>
     </row>
     <row r="66">
@@ -1942,22 +1942,22 @@
         <v>0.8400000000000001</v>
       </c>
       <c r="B66" t="n">
-        <v>0.005594315473560209</v>
+        <v>0.00508058425253304</v>
       </c>
       <c r="C66" t="n">
-        <v>0.3478764037792298</v>
+        <v>0.3502265121430724</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3849403485409636</v>
+        <v>0.3997365962122919</v>
       </c>
       <c r="E66" t="n">
-        <v>2.73275539914629</v>
+        <v>2.662642375750486</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.08270078589129332</v>
+        <v>-0.02974730481121145</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.1554104857428971</v>
+        <v>-0.138399147595956</v>
       </c>
     </row>
     <row r="67">
@@ -1965,22 +1965,22 @@
         <v>0.8500000000000001</v>
       </c>
       <c r="B67" t="n">
-        <v>0.005508173955354411</v>
+        <v>0.005032367928373337</v>
       </c>
       <c r="C67" t="n">
-        <v>0.3496271840805543</v>
+        <v>0.3517204729370526</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3865817465630482</v>
+        <v>0.4002074247655201</v>
       </c>
       <c r="E67" t="n">
-        <v>2.701041559417572</v>
+        <v>2.634829304215085</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.06031525841498687</v>
+        <v>-0.008037783308986758</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.154483764260716</v>
+        <v>-0.1376677499448129</v>
       </c>
     </row>
     <row r="68">
@@ -1988,22 +1988,22 @@
         <v>0.8600000000000001</v>
       </c>
       <c r="B68" t="n">
-        <v>0.005424771110017334</v>
+        <v>0.004985941095431782</v>
       </c>
       <c r="C68" t="n">
-        <v>0.3514864091355741</v>
+        <v>0.3533083260254851</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3881710058903785</v>
+        <v>0.4006513858435796</v>
       </c>
       <c r="E68" t="n">
-        <v>2.669521544630077</v>
+        <v>2.607389268771393</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.0378407597647054</v>
+        <v>0.01355659149934947</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.1534711089091202</v>
+        <v>-0.1369086860873671</v>
       </c>
     </row>
     <row r="69">
@@ -2011,22 +2011,22 @@
         <v>0.8700000000000001</v>
       </c>
       <c r="B69" t="n">
-        <v>0.005344159142543812</v>
+        <v>0.004941312027875176</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3534396196437964</v>
+        <v>0.3549779914619481</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3897070018558108</v>
+        <v>0.4010703310694382</v>
       </c>
       <c r="E69" t="n">
-        <v>2.638281068669804</v>
+        <v>2.580380862753019</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.01533973787447217</v>
+        <v>0.03497571305838188</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.1523747340638172</v>
+        <v>-0.1361208707203286</v>
       </c>
     </row>
     <row r="70">
@@ -2034,22 +2034,22 @@
         <v>0.8800000000000001</v>
       </c>
       <c r="B70" t="n">
-        <v>0.00526639025792868</v>
+        <v>0.004898488999870315</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3554723563047285</v>
+        <v>0.3567173893000201</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3911886246960299</v>
+        <v>0.4014661251167756</v>
       </c>
       <c r="E70" t="n">
-        <v>2.607405845422755</v>
+        <v>2.553862679493569</v>
       </c>
       <c r="F70" t="n">
-        <v>0.007125359321689555</v>
+        <v>0.05615947481269511</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.151196854100514</v>
+        <v>-0.1353032185404075</v>
       </c>
     </row>
     <row r="71">
@@ -2057,22 +2057,22 @@
         <v>0.8900000000000001</v>
       </c>
       <c r="B71" t="n">
-        <v>0.005191516661166773</v>
+        <v>0.004857480285584</v>
       </c>
       <c r="C71" t="n">
-        <v>0.3575701598178778</v>
+        <v>0.3585144395932791</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3926147806481958</v>
+        <v>0.4018406445671139</v>
       </c>
       <c r="E71" t="n">
-        <v>2.576981588774929</v>
+        <v>2.527893312326651</v>
       </c>
       <c r="F71" t="n">
-        <v>0.02949208388975658</v>
+        <v>0.07704777020687377</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.149939683394918</v>
+        <v>-0.1344546442443139</v>
       </c>
     </row>
     <row r="72">
@@ -2080,22 +2080,22 @@
         <v>0.9000000000000001</v>
       </c>
       <c r="B72" t="n">
-        <v>0.005119590557252925</v>
+        <v>0.00481829415918303</v>
       </c>
       <c r="C72" t="n">
-        <v>0.3597185708827516</v>
+        <v>0.3603570623953036</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3939843930504975</v>
+        <v>0.4021957768529001</v>
       </c>
       <c r="E72" t="n">
-        <v>2.547094012612329</v>
+        <v>2.502531354585874</v>
       </c>
       <c r="F72" t="n">
-        <v>0.05169798789570564</v>
+        <v>0.09758049268550249</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.1486054363227363</v>
+        <v>-0.1335740625287578</v>
       </c>
     </row>
     <row r="73">
@@ -2103,22 +2103,22 @@
         <v>0.9099999999999999</v>
       </c>
       <c r="B73" t="n">
-        <v>0.005050664151181976</v>
+        <v>0.004780938894834204</v>
       </c>
       <c r="C73" t="n">
-        <v>0.3619031301988571</v>
+        <v>0.3622331777596716</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3952964034453343</v>
+        <v>0.4025334192878143</v>
       </c>
       <c r="E73" t="n">
-        <v>2.517828830820955</v>
+        <v>2.477835399604845</v>
       </c>
       <c r="F73" t="n">
-        <v>0.07368062340551294</v>
+        <v>0.1176975356931654</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.1471963272596761</v>
+        <v>-0.1326603880904494</v>
       </c>
     </row>
     <row r="74">
@@ -2126,22 +2126,22 @@
         <v>0.9199999999999999</v>
       </c>
       <c r="B74" t="n">
-        <v>0.004984789647948754</v>
+        <v>0.004745422766704322</v>
       </c>
       <c r="C74" t="n">
-        <v>0.3641093784657016</v>
+        <v>0.3641307057399616</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3965497726838068</v>
+        <v>0.4028554781854371</v>
       </c>
       <c r="E74" t="n">
-        <v>2.489271757286807</v>
+        <v>2.453864040717171</v>
       </c>
       <c r="F74" t="n">
-        <v>0.09537754248515629</v>
+        <v>0.1373387926744481</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.1457145705814446</v>
+        <v>-0.1317125356260987</v>
       </c>
     </row>
     <row r="75">
@@ -2149,22 +2149,22 @@
         <v>0.9299999999999999</v>
       </c>
       <c r="B75" t="n">
-        <v>0.004922019252548096</v>
+        <v>0.00471175404896018</v>
       </c>
       <c r="C75" t="n">
-        <v>0.3663228563827925</v>
+        <v>0.3660375663897519</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3977434820301728</v>
+        <v>0.4031638680672905</v>
       </c>
       <c r="E75" t="n">
-        <v>2.461508505895886</v>
+        <v>2.430675871256461</v>
       </c>
       <c r="F75" t="n">
-        <v>0.116726297200612</v>
+        <v>0.1564441570739347</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.1441623806637492</v>
+        <v>-0.1307294198324158</v>
       </c>
     </row>
     <row r="76">
@@ -2172,22 +2172,22 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="B76" t="n">
-        <v>0.004862405169974836</v>
+        <v>0.004679941015768581</v>
       </c>
       <c r="C76" t="n">
-        <v>0.3685291046496371</v>
+        <v>0.3679416797626206</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3988765342648921</v>
+        <v>0.403460510961152</v>
       </c>
       <c r="E76" t="n">
-        <v>2.434624790534192</v>
+        <v>2.408329484556321</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1376644396178566</v>
+        <v>0.17495352233621</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.1425419718822969</v>
+        <v>-0.1297099554061108</v>
       </c>
     </row>
     <row r="77">
@@ -2195,22 +2195,22 @@
         <v>0.95</v>
       </c>
       <c r="B77" t="n">
-        <v>0.004805999605223814</v>
+        <v>0.004649991941296321</v>
       </c>
       <c r="C77" t="n">
-        <v>0.3707136639657426</v>
+        <v>0.369830965912146</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3999479547848531</v>
+        <v>0.4037473357904421</v>
       </c>
       <c r="E77" t="n">
-        <v>2.408706325087728</v>
+        <v>2.38688347395036</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1581295218028671</v>
+        <v>0.1928067819058583</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.140855558612795</v>
+        <v>-0.1286530570438937</v>
       </c>
     </row>
     <row r="78">
@@ -2218,22 +2218,22 @@
         <v>0.96</v>
       </c>
       <c r="B78" t="n">
-        <v>0.004752854763289858</v>
+        <v>0.004621915099710201</v>
       </c>
       <c r="C78" t="n">
-        <v>0.3728620750306164</v>
+        <v>0.3716933448919064</v>
       </c>
       <c r="D78" t="n">
-        <v>0.4009567926993536</v>
+        <v>0.4040262778553991</v>
       </c>
       <c r="E78" t="n">
-        <v>2.383838823442492</v>
+        <v>2.366396432772186</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1780590958216202</v>
+        <v>0.2099438292274645</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.1391053552309507</v>
+        <v>-0.1275576394424746</v>
       </c>
     </row>
     <row r="79">
@@ -2241,22 +2241,22 @@
         <v>0.97</v>
       </c>
       <c r="B79" t="n">
-        <v>0.004703022849167808</v>
+        <v>0.004595718765177018</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3749598785437657</v>
+        <v>0.3735167367554801</v>
       </c>
       <c r="D79" t="n">
-        <v>0.4019021219203762</v>
+        <v>0.4042992784066758</v>
       </c>
       <c r="E79" t="n">
-        <v>2.360107999484486</v>
+        <v>2.346926954355407</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1973907137400925</v>
+        <v>0.226304557745613</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.1372935761124713</v>
+        <v>-0.1264226172985636</v>
       </c>
     </row>
     <row r="80">
@@ -2264,22 +2264,22 @@
         <v>0.98</v>
       </c>
       <c r="B80" t="n">
-        <v>0.004656556067852496</v>
+        <v>0.004571411211863575</v>
       </c>
       <c r="C80" t="n">
-        <v>0.3769926152046978</v>
+        <v>0.3752890615564453</v>
       </c>
       <c r="D80" t="n">
-        <v>0.4027830422456833</v>
+        <v>0.4045682843119314</v>
       </c>
       <c r="E80" t="n">
-        <v>2.337599567099711</v>
+        <v>2.328533632033629</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2160619276242608</v>
+        <v>0.2418288609048885</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.135422435633064</v>
+        <v>-0.1252469053088708</v>
       </c>
     </row>
     <row r="81">
@@ -2287,22 +2287,22 @@
         <v>0.99</v>
       </c>
       <c r="B81" t="n">
-        <v>0.004613506624338758</v>
+        <v>0.004549000713936666</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3789458257129201</v>
+        <v>0.3769982393483803</v>
       </c>
       <c r="D81" t="n">
-        <v>0.4035986804332318</v>
+        <v>0.4048352478159409</v>
       </c>
       <c r="E81" t="n">
-        <v>2.316399240174167</v>
+        <v>2.311275059140462</v>
       </c>
       <c r="F81" t="n">
-        <v>0.234010289540102</v>
+        <v>0.2564566321498757</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.1334941481684359</v>
+        <v>-0.1240294181701062</v>
       </c>
     </row>
     <row r="82">
@@ -2310,22 +2310,22 @@
         <v>1</v>
       </c>
       <c r="B82" t="n">
-        <v>0.004573926723621428</v>
+        <v>0.004528495545563095</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3808050507679399</v>
+        <v>0.3786321901848634</v>
       </c>
       <c r="D82" t="n">
-        <v>0.4043481912653886</v>
+        <v>0.4051021263947031</v>
       </c>
       <c r="E82" t="n">
-        <v>2.296592732593855</v>
+        <v>2.295209829009511</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2511733515535927</v>
+        <v>0.2701277649251593</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.1315109280942943</v>
+        <v>-0.1227690705789799</v>
       </c>
     </row>
     <row r="83">
@@ -2333,22 +2333,22 @@
         <v>1.01</v>
       </c>
       <c r="B83" t="n">
-        <v>0.004537868570695344</v>
+        <v>0.004509903980909658</v>
       </c>
       <c r="C83" t="n">
-        <v>0.3825558310692644</v>
+        <v>0.3801788341194728</v>
       </c>
       <c r="D83" t="n">
-        <v>0.4050307586014167</v>
+        <v>0.4053708827040051</v>
       </c>
       <c r="E83" t="n">
-        <v>2.278265758244776</v>
+        <v>2.280396534974385</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2674886657307097</v>
+        <v>0.2827821526753237</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.1294749897863464</v>
+        <v>-0.1214647772322021</v>
       </c>
     </row>
     <row r="84">
@@ -2356,22 +2356,22 @@
         <v>1.02</v>
       </c>
       <c r="B84" t="n">
-        <v>0.004505384370555336</v>
+        <v>0.004493234294143156</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3841837073164009</v>
+        <v>0.3816260912057868</v>
       </c>
       <c r="D84" t="n">
-        <v>0.4056455964166815</v>
+        <v>0.4056434846228859</v>
       </c>
       <c r="E84" t="n">
-        <v>2.26150403101293</v>
+        <v>2.266893770368694</v>
       </c>
       <c r="F84" t="n">
-        <v>0.2828937841374298</v>
+        <v>0.2943596888449537</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.1273885476202994</v>
+        <v>-0.1201154528264827</v>
       </c>
     </row>
     <row r="85">
@@ -2379,22 +2379,22 @@
         <v>1.03</v>
       </c>
       <c r="B85" t="n">
-        <v>0.004476526328196243</v>
+        <v>0.004478494759430385</v>
       </c>
       <c r="C85" t="n">
-        <v>0.3856742202088568</v>
+        <v>0.3829618814973836</v>
       </c>
       <c r="D85" t="n">
-        <v>0.4061919498270216</v>
+        <v>0.4059219053924419</v>
       </c>
       <c r="E85" t="n">
-        <v>2.246393264784318</v>
+        <v>2.254760128526042</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2973262588397296</v>
+        <v>0.3048002668786336</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.1252538159718606</v>
+        <v>-0.1187200120585318</v>
       </c>
     </row>
     <row r="86">
@@ -2402,22 +2402,22 @@
         <v>1.04</v>
       </c>
       <c r="B86" t="n">
-        <v>0.004451346648612897</v>
+        <v>0.004465693650938149</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3870129104461393</v>
+        <v>0.3841741250478417</v>
       </c>
       <c r="D86" t="n">
-        <v>0.4066690960967138</v>
+        <v>0.40620812385043</v>
       </c>
       <c r="E86" t="n">
-        <v>2.233019173444941</v>
+        <v>2.244054202780039</v>
       </c>
       <c r="F86" t="n">
-        <v>0.3107236419035861</v>
+        <v>0.3140437802209486</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.1230730092167371</v>
+        <v>-0.1172773696250596</v>
       </c>
     </row>
     <row r="87">
@@ -2425,22 +2425,22 @@
         <v>1.05</v>
       </c>
       <c r="B87" t="n">
-        <v>0.004429897536800134</v>
+        <v>0.004454839242833243</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3881853187277558</v>
+        <v>0.385250741910739</v>
       </c>
       <c r="D87" t="n">
-        <v>0.4070763456284611</v>
+        <v>0.406504124762147</v>
       </c>
       <c r="E87" t="n">
-        <v>2.2214674708808</v>
+        <v>2.234834586464292</v>
       </c>
       <c r="F87" t="n">
-        <v>0.3230234853949759</v>
+        <v>0.3220301223164829</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.1208483417306362</v>
+        <v>-0.115786440222776</v>
       </c>
     </row>
     <row r="88">
@@ -2448,22 +2448,22 @@
         <v>1.06</v>
       </c>
       <c r="B88" t="n">
-        <v>0.004412231197752791</v>
+        <v>0.004445939809282466</v>
       </c>
       <c r="C88" t="n">
-        <v>0.3891769857532135</v>
+        <v>0.386179652139654</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4074130429338253</v>
+        <v>0.4068118992481072</v>
       </c>
       <c r="E88" t="n">
-        <v>2.211823870977895</v>
+        <v>2.227159872912409</v>
       </c>
       <c r="F88" t="n">
-        <v>0.3341633413798759</v>
+        <v>0.3286991866098211</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.1185820278892652</v>
+        <v>-0.1142461385483912</v>
       </c>
     </row>
     <row r="89">
@@ -2471,22 +2471,22 @@
         <v>1.07</v>
       </c>
       <c r="B89" t="n">
-        <v>0.004398399836465699</v>
+        <v>0.00443900362445262</v>
       </c>
       <c r="C89" t="n">
-        <v>0.3899734522220197</v>
+        <v>0.386948775788165</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4076785675825251</v>
+        <v>0.407133445309085</v>
       </c>
       <c r="E89" t="n">
-        <v>2.204174087622227</v>
+        <v>2.221088655457998</v>
       </c>
       <c r="F89" t="n">
-        <v>0.3440807619242626</v>
+        <v>0.3339908665455479</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.116276282068331</v>
+        <v>-0.1126553792986153</v>
       </c>
     </row>
     <row r="90">
@@ -2494,22 +2494,22 @@
         <v>1.08</v>
       </c>
       <c r="B90" t="n">
-        <v>0.004388455657933695</v>
+        <v>0.004434038962510502</v>
       </c>
       <c r="C90" t="n">
-        <v>0.3905602588336818</v>
+        <v>0.3875460329098502</v>
       </c>
       <c r="D90" t="n">
-        <v>0.4078723351290252</v>
+        <v>0.4074707684491622</v>
       </c>
       <c r="E90" t="n">
-        <v>2.198603834699796</v>
+        <v>2.216679527434666</v>
       </c>
       <c r="F90" t="n">
-        <v>0.3527132990941127</v>
+        <v>0.3378450555682481</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.1139333186435412</v>
+        <v>-0.1110130771701583</v>
       </c>
     </row>
     <row r="91">
@@ -2517,22 +2517,22 @@
         <v>1.09</v>
       </c>
       <c r="B91" t="n">
-        <v>0.004382450867151614</v>
+        <v>0.004431054097622912</v>
       </c>
       <c r="C91" t="n">
-        <v>0.3909229462877071</v>
+        <v>0.3879593435582878</v>
       </c>
       <c r="D91" t="n">
-        <v>0.4079937980148426</v>
+        <v>0.4078258823974898</v>
       </c>
       <c r="E91" t="n">
-        <v>2.195198826096604</v>
+        <v>2.213991082176021</v>
       </c>
       <c r="F91" t="n">
-        <v>0.3599985049554033</v>
+        <v>0.3402016471225061</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.1115553519906028</v>
+        <v>-0.1093181468597303</v>
       </c>
     </row>
     <row r="92">
@@ -2540,22 +2540,22 @@
         <v>1.1</v>
       </c>
       <c r="B92" t="n">
-        <v>0.00438043766911429</v>
+        <v>0.004430057303956649</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3910470552836028</v>
+        <v>0.3881766277870562</v>
       </c>
       <c r="D92" t="n">
-        <v>0.408042446445009</v>
+        <v>0.4082008099295733</v>
       </c>
       <c r="E92" t="n">
-        <v>2.194044775698651</v>
+        <v>2.213081913015671</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3658739315741111</v>
+        <v>0.3410005346529067</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.109144596485223</v>
+        <v>-0.1075695030640413</v>
       </c>
     </row>
     <row r="93">
@@ -2563,22 +2563,22 @@
         <v>1.11</v>
       </c>
       <c r="B93" t="n">
-        <v>0.004387943522937084</v>
+        <v>0.004430266793030347</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3910360594815572</v>
+        <v>0.3882906783363895</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4080541707711351</v>
+        <v>0.4085811812093132</v>
       </c>
       <c r="E93" t="n">
-        <v>2.194274868482536</v>
+        <v>2.213347896667924</v>
       </c>
       <c r="F93" t="n">
-        <v>0.3709885251772723</v>
+        <v>0.3409603010668458</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.1061853220495494</v>
+        <v>-0.1053413354733361</v>
       </c>
     </row>
     <row r="94">
@@ -2586,22 +2586,22 @@
         <v>1.12</v>
       </c>
       <c r="B94" t="n">
-        <v>0.004410055362577207</v>
+        <v>0.004430883936517725</v>
       </c>
       <c r="C94" t="n">
-        <v>0.3910035177220774</v>
+        <v>0.3884023434807359</v>
       </c>
       <c r="D94" t="n">
-        <v>0.408065200673435</v>
+        <v>0.4089516441850401</v>
       </c>
       <c r="E94" t="n">
-        <v>2.194952709386413</v>
+        <v>2.214131470129967</v>
       </c>
       <c r="F94" t="n">
-        <v>0.3760319790942123</v>
+        <v>0.3408407081887339</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.1021904373145753</v>
+        <v>-0.1022339661732606</v>
       </c>
     </row>
     <row r="95">
@@ -2609,22 +2609,22 @@
         <v>1.13</v>
       </c>
       <c r="B95" t="n">
-        <v>0.00444616460529227</v>
+        <v>0.004431891748818216</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3909500984751484</v>
+        <v>0.3885116265749947</v>
       </c>
       <c r="D95" t="n">
-        <v>0.4080755641897059</v>
+        <v>0.4093127577701773</v>
       </c>
       <c r="E95" t="n">
-        <v>2.196059642238616</v>
+        <v>2.215411067159726</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3810029660443406</v>
+        <v>0.3406434178386761</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.09720511471927701</v>
+        <v>-0.09828550845362707</v>
       </c>
     </row>
     <row r="96">
@@ -2632,22 +2632,22 @@
         <v>1.14</v>
       </c>
       <c r="B96" t="n">
-        <v>0.004495662668339884</v>
+        <v>0.004433273244331247</v>
       </c>
       <c r="C96" t="n">
-        <v>0.3908764702107557</v>
+        <v>0.3886185309740655</v>
       </c>
       <c r="D96" t="n">
-        <v>0.4080852893639574</v>
+        <v>0.4096650836161547</v>
       </c>
       <c r="E96" t="n">
-        <v>2.197577010867479</v>
+        <v>2.217165121515125</v>
       </c>
       <c r="F96" t="n">
-        <v>0.3859001587470671</v>
+        <v>0.3403700918367785</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.09127452670263057</v>
+        <v>-0.09353407560424765</v>
       </c>
     </row>
     <row r="97">
@@ -2655,22 +2655,22 @@
         <v>1.15</v>
       </c>
       <c r="B97" t="n">
-        <v>0.00455794096897766</v>
+        <v>0.004435011437456249</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3907833013988844</v>
+        <v>0.3887230600328474</v>
       </c>
       <c r="D97" t="n">
-        <v>0.4080944042459628</v>
+        <v>0.4100091859852613</v>
       </c>
       <c r="E97" t="n">
-        <v>2.199486159101335</v>
+        <v>2.219372066954091</v>
       </c>
       <c r="F97" t="n">
-        <v>0.3907222299218013</v>
+        <v>0.3400223920031465</v>
       </c>
       <c r="G97" t="n">
-        <v>-0.08444384570361219</v>
+        <v>-0.08801778091493447</v>
       </c>
     </row>
     <row r="98">
@@ -2678,22 +2678,22 @@
         <v>1.16</v>
       </c>
       <c r="B98" t="n">
-        <v>0.004632390924463209</v>
+        <v>0.004437089342592653</v>
       </c>
       <c r="C98" t="n">
-        <v>0.3906712605095198</v>
+        <v>0.3888252171062397</v>
       </c>
       <c r="D98" t="n">
-        <v>0.4081029368908293</v>
+        <v>0.410345631631168</v>
       </c>
       <c r="E98" t="n">
-        <v>2.201768430768518</v>
+        <v>2.222010337234548</v>
       </c>
       <c r="F98" t="n">
-        <v>0.3954678522879531</v>
+        <v>0.3396019801578858</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.07675824416119818</v>
+        <v>-0.08177473767549985</v>
       </c>
     </row>
     <row r="99">
@@ -2701,22 +2701,22 @@
         <v>1.17</v>
       </c>
       <c r="B99" t="n">
-        <v>0.004718403952054145</v>
+        <v>0.004439489974139888</v>
       </c>
       <c r="C99" t="n">
-        <v>0.3905410160126471</v>
+        <v>0.3889250055491421</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4081109153585882</v>
+        <v>0.4106749896871953</v>
       </c>
       <c r="E99" t="n">
-        <v>2.204405169697362</v>
+        <v>2.225058366114422</v>
       </c>
       <c r="F99" t="n">
-        <v>0.4001356985649323</v>
+        <v>0.339110518121102</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.06826289451436436</v>
+        <v>-0.07484305917575569</v>
       </c>
     </row>
     <row r="100">
@@ -2724,22 +2724,22 @@
         <v>1.18</v>
       </c>
       <c r="B100" t="n">
-        <v>0.004815371469008077</v>
+        <v>0.004442196346497384</v>
       </c>
       <c r="C100" t="n">
-        <v>0.3903932363782515</v>
+        <v>0.3890224287164536</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4081183677138036</v>
+        <v>0.4109978315623985</v>
       </c>
       <c r="E100" t="n">
-        <v>2.2073777197162</v>
+        <v>2.228494587351639</v>
       </c>
       <c r="F100" t="n">
-        <v>0.4047244414721483</v>
+        <v>0.3385496677129007</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.05900296920208704</v>
+        <v>-0.06726085870551428</v>
       </c>
     </row>
     <row r="101">
@@ -2747,22 +2747,22 @@
         <v>1.19</v>
       </c>
       <c r="B101" t="n">
-        <v>0.004922684892582616</v>
+        <v>0.004445191474064571</v>
       </c>
       <c r="C101" t="n">
-        <v>0.3902285900763184</v>
+        <v>0.3891174899630736</v>
       </c>
       <c r="D101" t="n">
-        <v>0.4081253220252011</v>
+        <v>0.4113147308455377</v>
       </c>
       <c r="E101" t="n">
-        <v>2.210667424653365</v>
+        <v>2.232297434704124</v>
       </c>
       <c r="F101" t="n">
-        <v>0.4092327537290111</v>
+        <v>0.3379210907533877</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.04902364066334238</v>
+        <v>-0.05906624955458775</v>
       </c>
     </row>
     <row r="102">
@@ -2770,22 +2770,22 @@
         <v>1.2</v>
       </c>
       <c r="B102" t="n">
-        <v>0.005039735640035376</v>
+        <v>0.004448458371240878</v>
       </c>
       <c r="C102" t="n">
-        <v>0.3900477455768329</v>
+        <v>0.3892101926439016</v>
       </c>
       <c r="D102" t="n">
-        <v>0.408131806365315</v>
+        <v>0.4116262632169995</v>
       </c>
       <c r="E102" t="n">
-        <v>2.214255628337193</v>
+        <v>2.236445341929802</v>
       </c>
       <c r="F102" t="n">
-        <v>0.4136593080549303</v>
+        <v>0.3372264490626684</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.03837008133710656</v>
+        <v>-0.05029734501278831</v>
       </c>
     </row>
     <row r="103">
@@ -2793,22 +2793,22 @@
         <v>1.21</v>
       </c>
       <c r="B103" t="n">
-        <v>0.005165915128623966</v>
+        <v>0.004451980052425738</v>
       </c>
       <c r="C103" t="n">
-        <v>0.3898513713497803</v>
+        <v>0.3893005401138369</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4081378488101557</v>
+        <v>0.4119330063687273</v>
       </c>
       <c r="E103" t="n">
-        <v>2.218123674596015</v>
+        <v>2.240916742786598</v>
       </c>
       <c r="F103" t="n">
-        <v>0.4180027771693157</v>
+        <v>0.3364674044608485</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.0270874636623557</v>
+        <v>-0.04099225836992808</v>
       </c>
     </row>
     <row r="104">
@@ -2816,22 +2816,22 @@
         <v>1.22</v>
       </c>
       <c r="B104" t="n">
-        <v>0.005300614775605997</v>
+        <v>0.004455739532018577</v>
       </c>
       <c r="C104" t="n">
-        <v>0.3896401358651459</v>
+        <v>0.3893885357277788</v>
       </c>
       <c r="D104" t="n">
-        <v>0.4081434774388956</v>
+        <v>0.4122355399322208</v>
       </c>
       <c r="E104" t="n">
-        <v>2.222252907258166</v>
+        <v>2.24569007103244</v>
       </c>
       <c r="F104" t="n">
-        <v>0.4222618337915768</v>
+        <v>0.3356456187680337</v>
       </c>
       <c r="G104" t="n">
-        <v>-0.01522096007806594</v>
+        <v>-0.03118910291581924</v>
       </c>
     </row>
     <row r="105">
@@ -2839,22 +2839,22 @@
         <v>1.23</v>
       </c>
       <c r="B105" t="n">
-        <v>0.005443225998239082</v>
+        <v>0.004459719824418827</v>
       </c>
       <c r="C105" t="n">
-        <v>0.3894147075929149</v>
+        <v>0.3894741828406265</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4081487203335746</v>
+        <v>0.4125344454146564</v>
       </c>
       <c r="E105" t="n">
-        <v>2.22662467015198</v>
+        <v>2.25074376042525</v>
       </c>
       <c r="F105" t="n">
-        <v>0.4264351506411236</v>
+        <v>0.3347627538043297</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.002815743023213503</v>
+        <v>-0.02092599194027397</v>
       </c>
     </row>
     <row r="106">
@@ -2862,22 +2862,22 @@
         <v>1.24</v>
       </c>
       <c r="B106" t="n">
-        <v>0.005593140213780831</v>
+        <v>0.004463903944025918</v>
       </c>
       <c r="C106" t="n">
-        <v>0.3891757550030725</v>
+        <v>0.3895574848072796</v>
       </c>
       <c r="D106" t="n">
-        <v>0.4081536055788256</v>
+        <v>0.4128303061431813</v>
       </c>
       <c r="E106" t="n">
-        <v>2.231220307105791</v>
+        <v>2.256056244722955</v>
       </c>
       <c r="F106" t="n">
-        <v>0.4305214004373655</v>
+        <v>0.3338204713898419</v>
       </c>
       <c r="G106" t="n">
-        <v>0.01008301506322553</v>
+        <v>-0.01024103873310439</v>
       </c>
     </row>
     <row r="107">
@@ -2885,22 +2885,22 @@
         <v>1.25</v>
       </c>
       <c r="B107" t="n">
-        <v>0.005749748839488856</v>
+        <v>0.004468274905239279</v>
       </c>
       <c r="C107" t="n">
-        <v>0.3889239465656039</v>
+        <v>0.3896384449826374</v>
       </c>
       <c r="D107" t="n">
-        <v>0.4081581612616176</v>
+        <v>0.4131237072174308</v>
       </c>
       <c r="E107" t="n">
-        <v>2.23602116194793</v>
+        <v>2.261605957683481</v>
       </c>
       <c r="F107" t="n">
-        <v>0.4345192558997124</v>
+        <v>0.3328204333446761</v>
       </c>
       <c r="G107" t="n">
-        <v>0.02343014174227498</v>
+        <v>0.0008276434158773181</v>
       </c>
     </row>
     <row r="108">
@@ -2908,22 +2908,22 @@
         <v>1.26</v>
       </c>
       <c r="B108" t="n">
-        <v>0.005912443292620767</v>
+        <v>0.004472815722458341</v>
       </c>
       <c r="C108" t="n">
-        <v>0.3886599507504945</v>
+        <v>0.3897170667215992</v>
       </c>
       <c r="D108" t="n">
-        <v>0.4081624154710202</v>
+        <v>0.4134152354703138</v>
       </c>
       <c r="E108" t="n">
-        <v>2.241008578506734</v>
+        <v>2.267371333064753</v>
       </c>
       <c r="F108" t="n">
-        <v>0.4384273897475741</v>
+        <v>0.3317643014889379</v>
       </c>
       <c r="G108" t="n">
-        <v>0.03718046457495866</v>
+        <v>0.01224194121685896</v>
       </c>
     </row>
     <row r="109">
@@ -2931,22 +2931,22 @@
         <v>1.27</v>
       </c>
       <c r="B109" t="n">
-        <v>0.006080614990434176</v>
+        <v>0.004477509410082534</v>
       </c>
       <c r="C109" t="n">
-        <v>0.3883844360277295</v>
+        <v>0.3897933533790643</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4081663962979857</v>
+        <v>0.4137054794371151</v>
       </c>
       <c r="E109" t="n">
-        <v>2.246163900610533</v>
+        <v>2.273330804624696</v>
       </c>
       <c r="F109" t="n">
-        <v>0.4422444747003602</v>
+        <v>0.3306537376427329</v>
       </c>
       <c r="G109" t="n">
-        <v>0.05128881112230046</v>
+        <v>0.02396374138002844</v>
       </c>
     </row>
     <row r="110">
@@ -2954,22 +2954,22 @@
         <v>1.28</v>
       </c>
       <c r="B110" t="n">
-        <v>0.006253655350186697</v>
+        <v>0.004482338982511287</v>
       </c>
       <c r="C110" t="n">
-        <v>0.3880980708672941</v>
+        <v>0.389867308309932</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4081701318351517</v>
+        <v>0.4139950293329547</v>
       </c>
       <c r="E110" t="n">
-        <v>2.251468472087665</v>
+        <v>2.279462806121236</v>
       </c>
       <c r="F110" t="n">
-        <v>0.4459691834774803</v>
+        <v>0.3294904036261667</v>
       </c>
       <c r="G110" t="n">
-        <v>0.06571000894532419</v>
+        <v>0.03595493061557353</v>
       </c>
     </row>
     <row r="111">
@@ -2977,22 +2977,22 @@
         <v>1.29</v>
       </c>
       <c r="B111" t="n">
-        <v>0.006430955789135937</v>
+        <v>0.004487287454144031</v>
       </c>
       <c r="C111" t="n">
-        <v>0.3878015237391735</v>
+        <v>0.3899389348691019</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4081736501766625</v>
+        <v>0.4142844770386507</v>
       </c>
       <c r="E111" t="n">
-        <v>2.25690363676646</v>
+        <v>2.285745771312298</v>
       </c>
       <c r="F111" t="n">
-        <v>0.4496001887983442</v>
+        <v>0.328275961259345</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0803988856050537</v>
+        <v>0.04817739563368211</v>
       </c>
     </row>
     <row r="112">
@@ -3000,22 +3000,22 @@
         <v>1.3</v>
       </c>
       <c r="B112" t="n">
-        <v>0.006611907724539509</v>
+        <v>0.004492337839380195</v>
       </c>
       <c r="C112" t="n">
-        <v>0.387495463113353</v>
+        <v>0.3900082364114731</v>
       </c>
       <c r="D112" t="n">
-        <v>0.4081769794180096</v>
+        <v>0.4145744160950253</v>
       </c>
       <c r="E112" t="n">
-        <v>2.262450738475254</v>
+        <v>2.292158133955806</v>
       </c>
       <c r="F112" t="n">
-        <v>0.4531361633823618</v>
+        <v>0.3270120723623733</v>
       </c>
       <c r="G112" t="n">
-        <v>0.09531026866251285</v>
+        <v>0.06059302314454199</v>
       </c>
     </row>
     <row r="113">
@@ -3023,22 +3023,22 @@
         <v>1.31</v>
       </c>
       <c r="B113" t="n">
-        <v>0.006795902573655026</v>
+        <v>0.004497473152619209</v>
       </c>
       <c r="C113" t="n">
-        <v>0.3871805574598179</v>
+        <v>0.3900752162919451</v>
       </c>
       <c r="D113" t="n">
-        <v>0.4081801476558923</v>
+        <v>0.4148654417056966</v>
       </c>
       <c r="E113" t="n">
-        <v>2.268091121042379</v>
+        <v>2.298678327809689</v>
       </c>
       <c r="F113" t="n">
-        <v>0.4565757799489426</v>
+        <v>0.3257003987553575</v>
       </c>
       <c r="G113" t="n">
-        <v>0.1103989856787255</v>
+        <v>0.07316369985834109</v>
       </c>
     </row>
     <row r="114">
@@ -3046,22 +3046,22 @@
         <v>1.32</v>
       </c>
       <c r="B114" t="n">
-        <v>0.006982331753740096</v>
+        <v>0.004502676408260503</v>
       </c>
       <c r="C114" t="n">
-        <v>0.3868574752485535</v>
+        <v>0.3901398778654171</v>
       </c>
       <c r="D114" t="n">
-        <v>0.4081831829880971</v>
+        <v>0.4151581507483976</v>
       </c>
       <c r="E114" t="n">
-        <v>2.273806128296171</v>
+        <v>2.305284786631869</v>
       </c>
       <c r="F114" t="n">
-        <v>0.4599177112174964</v>
+        <v>0.324342602258403</v>
       </c>
       <c r="G114" t="n">
-        <v>0.1256198642147155</v>
+        <v>0.08585131248526712</v>
       </c>
     </row>
     <row r="115">
@@ -3069,22 +3069,22 @@
         <v>1.33</v>
       </c>
       <c r="B115" t="n">
-        <v>0.007170586682052334</v>
+        <v>0.004507930620703508</v>
       </c>
       <c r="C115" t="n">
-        <v>0.3865268849495447</v>
+        <v>0.3902022244867885</v>
       </c>
       <c r="D115" t="n">
-        <v>0.4081861135133961</v>
+        <v>0.4154531417948656</v>
       </c>
       <c r="E115" t="n">
-        <v>2.27957710406496</v>
+        <v>2.311955944180273</v>
       </c>
       <c r="F115" t="n">
-        <v>0.4631606299074329</v>
+        <v>0.3229403446916155</v>
       </c>
       <c r="G115" t="n">
-        <v>0.1409277318315066</v>
+        <v>0.09861774773550797</v>
       </c>
     </row>
     <row r="116">
@@ -3092,22 +3092,22 @@
         <v>1.34</v>
       </c>
       <c r="B116" t="n">
-        <v>0.007360058775849348</v>
+        <v>0.004513218804347653</v>
       </c>
       <c r="C116" t="n">
-        <v>0.3861894550327771</v>
+        <v>0.3902622595109588</v>
       </c>
       <c r="D116" t="n">
-        <v>0.4081889673314658</v>
+        <v>0.4157510151393424</v>
       </c>
       <c r="E116" t="n">
-        <v>2.285385392177083</v>
+        <v>2.318670234212826</v>
       </c>
       <c r="F116" t="n">
-        <v>0.4663032087381618</v>
+        <v>0.3214952878751006</v>
       </c>
       <c r="G116" t="n">
-        <v>0.1562774160901229</v>
+        <v>0.1114248923192515</v>
       </c>
     </row>
     <row r="117">
@@ -3115,22 +3115,22 @@
         <v>1.35</v>
       </c>
       <c r="B117" t="n">
-        <v>0.007550139452388751</v>
+        <v>0.004518523973592368</v>
       </c>
       <c r="C117" t="n">
-        <v>0.3858458539682358</v>
+        <v>0.3903199862928272</v>
       </c>
       <c r="D117" t="n">
-        <v>0.4081917725428242</v>
+        <v>0.4160523728357312</v>
       </c>
       <c r="E117" t="n">
-        <v>2.291212336460871</v>
+        <v>2.325406090487454</v>
       </c>
       <c r="F117" t="n">
-        <v>0.4693441204290928</v>
+        <v>0.320009093628964</v>
       </c>
       <c r="G117" t="n">
-        <v>0.1716237445515878</v>
+        <v>0.1242346329466856</v>
       </c>
     </row>
     <row r="118">
@@ -3138,22 +3138,22 @@
         <v>1.36</v>
       </c>
       <c r="B118" t="n">
-        <v>0.007740220128928148</v>
+        <v>0.004523829142837082</v>
       </c>
       <c r="C118" t="n">
-        <v>0.3854967502259062</v>
+        <v>0.390375408187293</v>
       </c>
       <c r="D118" t="n">
-        <v>0.4081945572487878</v>
+        <v>0.4163578187434531</v>
       </c>
       <c r="E118" t="n">
-        <v>2.29703928074466</v>
+        <v>2.332141946762082</v>
       </c>
       <c r="F118" t="n">
-        <v>0.4722820376996356</v>
+        <v>0.3184834237733112</v>
       </c>
       <c r="G118" t="n">
-        <v>0.1869215447769251</v>
+        <v>0.1370088563279976</v>
       </c>
     </row>
     <row r="119">
@@ -3161,22 +3161,22 @@
         <v>1.37</v>
       </c>
       <c r="B119" t="n">
-        <v>0.007929692222725163</v>
+        <v>0.004529117326481227</v>
       </c>
       <c r="C119" t="n">
-        <v>0.3851428122757733</v>
+        <v>0.3904285285492556</v>
       </c>
       <c r="D119" t="n">
-        <v>0.4081973495514479</v>
+        <v>0.4166679585820519</v>
       </c>
       <c r="E119" t="n">
-        <v>2.302847568856783</v>
+        <v>2.338856236794635</v>
       </c>
       <c r="F119" t="n">
-        <v>0.4751156332691999</v>
+        <v>0.316919940128248</v>
       </c>
       <c r="G119" t="n">
-        <v>0.2021256443271595</v>
+        <v>0.1497094491733763</v>
       </c>
     </row>
     <row r="120">
@@ -3184,22 +3184,22 @@
         <v>1.38</v>
       </c>
       <c r="B120" t="n">
-        <v>0.008117947151037398</v>
+        <v>0.004534371538924231</v>
       </c>
       <c r="C120" t="n">
-        <v>0.3847847085878225</v>
+        <v>0.3904793507336144</v>
       </c>
       <c r="D120" t="n">
-        <v>0.408200177553666</v>
+        <v>0.4169833999945928</v>
       </c>
       <c r="E120" t="n">
-        <v>2.308618544625572</v>
+        <v>2.34552739434304</v>
       </c>
       <c r="F120" t="n">
-        <v>0.4778435798571956</v>
+        <v>0.3153203045138799</v>
       </c>
       <c r="G120" t="n">
-        <v>0.2171908707633141</v>
+        <v>0.1622982981930089</v>
       </c>
     </row>
     <row r="121">
@@ -3207,22 +3207,22 @@
         <v>1.39</v>
       </c>
       <c r="B121" t="n">
-        <v>0.00830437633112247</v>
+        <v>0.004539574794565526</v>
       </c>
       <c r="C121" t="n">
-        <v>0.384423107632039</v>
+        <v>0.3905278780952688</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4082030693590887</v>
+        <v>0.4173047526199098</v>
       </c>
       <c r="E121" t="n">
-        <v>2.314333551879363</v>
+        <v>2.35213385316522</v>
       </c>
       <c r="F121" t="n">
-        <v>0.4804645501830321</v>
+        <v>0.3136861787503125</v>
       </c>
       <c r="G121" t="n">
-        <v>0.232072051646413</v>
+        <v>0.1747372900970833</v>
       </c>
     </row>
     <row r="122">
@@ -3230,22 +3230,22 @@
         <v>1.4</v>
       </c>
       <c r="B122" t="n">
-        <v>0.008488371180237986</v>
+        <v>0.00454471010780454</v>
       </c>
       <c r="C122" t="n">
-        <v>0.384058677878408</v>
+        <v>0.390574113989118</v>
       </c>
       <c r="D122" t="n">
-        <v>0.4082060530721821</v>
+        <v>0.4176326281737525</v>
       </c>
       <c r="E122" t="n">
-        <v>2.319973934446488</v>
+        <v>2.358654047019102</v>
       </c>
       <c r="F122" t="n">
-        <v>0.4829772169661193</v>
+        <v>0.3120192246576516</v>
       </c>
       <c r="G122" t="n">
-        <v>0.2467240145374801</v>
+        <v>0.1869883115957875</v>
       </c>
     </row>
     <row r="123">
@@ -3253,22 +3253,22 @@
         <v>1.41</v>
       </c>
       <c r="B123" t="n">
-        <v>0.00866932311564156</v>
+        <v>0.004549760493040704</v>
       </c>
       <c r="C123" t="n">
-        <v>0.3836920877969148</v>
+        <v>0.3906180617700614</v>
       </c>
       <c r="D123" t="n">
-        <v>0.4082091567982852</v>
+        <v>0.4179676405388899</v>
       </c>
       <c r="E123" t="n">
-        <v>2.325521036155282</v>
+        <v>2.365066409662612</v>
       </c>
       <c r="F123" t="n">
-        <v>0.4853802529258671</v>
+        <v>0.3103211040560027</v>
       </c>
       <c r="G123" t="n">
-        <v>0.2611015869975389</v>
+        <v>0.1990132493993092</v>
       </c>
     </row>
     <row r="124">
@@ -3276,22 +3276,22 @@
         <v>1.42</v>
       </c>
       <c r="B124" t="n">
-        <v>0.0088466235545908</v>
+        <v>0.004554708964673447</v>
       </c>
       <c r="C124" t="n">
-        <v>0.3833240058575447</v>
+        <v>0.3906597247929983</v>
       </c>
       <c r="D124" t="n">
-        <v>0.4082124086436831</v>
+        <v>0.4183104058642326</v>
       </c>
       <c r="E124" t="n">
-        <v>2.330956200834078</v>
+        <v>2.371349374853673</v>
       </c>
       <c r="F124" t="n">
-        <v>0.4876723307816849</v>
+        <v>0.3085934787654714</v>
       </c>
       <c r="G124" t="n">
-        <v>0.2751595965876137</v>
+        <v>0.2107739902178362</v>
       </c>
     </row>
     <row r="125">
@@ -3299,22 +3299,22 @@
         <v>1.43</v>
       </c>
       <c r="B125" t="n">
-        <v>0.009019663914343319</v>
+        <v>0.004559538537102201</v>
       </c>
       <c r="C125" t="n">
-        <v>0.3829551005302828</v>
+        <v>0.3906991064128282</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4082158367156993</v>
+        <v>0.4186615426730361</v>
       </c>
       <c r="E125" t="n">
-        <v>2.336260772311209</v>
+        <v>2.377481376350213</v>
       </c>
       <c r="F125" t="n">
-        <v>0.4898521232529825</v>
+        <v>0.3068380106061635</v>
       </c>
       <c r="G125" t="n">
-        <v>0.288852870868728</v>
+        <v>0.2222324207615566</v>
       </c>
     </row>
     <row r="126">
@@ -3322,22 +3322,22 @@
         <v>1.44</v>
       </c>
       <c r="B126" t="n">
-        <v>0.00918783561215673</v>
+        <v>0.004564232224726393</v>
       </c>
       <c r="C126" t="n">
-        <v>0.3825860402851145</v>
+        <v>0.3907362099844502</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4082194691228069</v>
+        <v>0.4190216719802552</v>
       </c>
       <c r="E126" t="n">
-        <v>2.341416094415009</v>
+        <v>2.383440847910156</v>
       </c>
       <c r="F126" t="n">
-        <v>0.4919183030591697</v>
+        <v>0.3050563613981845</v>
       </c>
       <c r="G126" t="n">
-        <v>0.3021362374019058</v>
+        <v>0.2333504277406579</v>
       </c>
     </row>
     <row r="127">
@@ -3345,22 +3345,22 @@
         <v>1.45</v>
       </c>
       <c r="B127" t="n">
-        <v>0.009350530065288642</v>
+        <v>0.004568773041945456</v>
       </c>
       <c r="C127" t="n">
-        <v>0.3822174935920249</v>
+        <v>0.3907710388627639</v>
       </c>
       <c r="D127" t="n">
-        <v>0.4082233339747602</v>
+        <v>0.4193914174191198</v>
       </c>
       <c r="E127" t="n">
-        <v>2.346403510973812</v>
+        <v>2.389206223291428</v>
       </c>
       <c r="F127" t="n">
-        <v>0.4938695429196562</v>
+        <v>0.30325019296164</v>
       </c>
       <c r="G127" t="n">
-        <v>0.314964523748171</v>
+        <v>0.2440898978653282</v>
       </c>
     </row>
     <row r="128">
@@ -3368,22 +3368,22 @@
         <v>1.46</v>
       </c>
       <c r="B128" t="n">
-        <v>0.009507138690996666</v>
+        <v>0.004573144003158816</v>
       </c>
       <c r="C128" t="n">
-        <v>0.3818501289209994</v>
+        <v>0.3908035964026686</v>
       </c>
       <c r="D128" t="n">
-        <v>0.4082274593827447</v>
+        <v>0.419771405377014</v>
       </c>
       <c r="E128" t="n">
-        <v>2.351204365815952</v>
+        <v>2.394755936251953</v>
       </c>
       <c r="F128" t="n">
-        <v>0.4957045155538516</v>
+        <v>0.3014211671166357</v>
       </c>
       <c r="G128" t="n">
-        <v>0.3272925574685472</v>
+        <v>0.2544127178457551</v>
       </c>
     </row>
     <row r="129">
@@ -3391,22 +3391,22 @@
         <v>1.47</v>
       </c>
       <c r="B129" t="n">
-        <v>0.009657052906538413</v>
+        <v>0.004577328122765907</v>
       </c>
       <c r="C129" t="n">
-        <v>0.3814846147420232</v>
+        <v>0.3908338859590635</v>
       </c>
       <c r="D129" t="n">
-        <v>0.408231873459547</v>
+        <v>0.4201622651407373</v>
       </c>
       <c r="E129" t="n">
-        <v>2.355800002769763</v>
+        <v>2.400068420549659</v>
       </c>
       <c r="F129" t="n">
-        <v>0.4974218936811656</v>
+        <v>0.2995709456832772</v>
       </c>
       <c r="G129" t="n">
-        <v>0.3390751661240585</v>
+        <v>0.2642807743921267</v>
       </c>
     </row>
     <row r="130">
@@ -3414,22 +3414,22 @@
         <v>1.48</v>
       </c>
       <c r="B130" t="n">
-        <v>0.009799664129171499</v>
+        <v>0.004581308415166158</v>
       </c>
       <c r="C130" t="n">
-        <v>0.3811216195250814</v>
+        <v>0.3908619108868481</v>
       </c>
       <c r="D130" t="n">
-        <v>0.4082366043197436</v>
+        <v>0.4205646290512416</v>
       </c>
       <c r="E130" t="n">
-        <v>2.360171765663576</v>
+        <v>2.405122109942469</v>
       </c>
       <c r="F130" t="n">
-        <v>0.499020350021008</v>
+        <v>0.2977011904816702</v>
       </c>
       <c r="G130" t="n">
-        <v>0.3502671772757286</v>
+        <v>0.2736559542146306</v>
       </c>
     </row>
     <row r="131">
@@ -3437,22 +3437,22 @@
         <v>1.49</v>
       </c>
       <c r="B131" t="n">
-        <v>0.009934363776153532</v>
+        <v>0.004585067894758997</v>
       </c>
       <c r="C131" t="n">
-        <v>0.3807618117401594</v>
+        <v>0.3908876745409217</v>
       </c>
       <c r="D131" t="n">
-        <v>0.4082416800799101</v>
+        <v>0.4209791326679347</v>
       </c>
       <c r="E131" t="n">
-        <v>2.364300998325727</v>
+        <v>2.40989543818831</v>
       </c>
       <c r="F131" t="n">
-        <v>0.5004985572927886</v>
+        <v>0.2958135633319202</v>
       </c>
       <c r="G131" t="n">
-        <v>0.3608234184845815</v>
+        <v>0.2825001440234548</v>
       </c>
     </row>
     <row r="132">
@@ -3460,22 +3460,22 @@
         <v>1.5</v>
       </c>
       <c r="B132" t="n">
-        <v>0.01006054326474212</v>
+        <v>0.004588589575943857</v>
       </c>
       <c r="C132" t="n">
-        <v>0.3804058598572424</v>
+        <v>0.3909111802761835</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4082471288588477</v>
+        <v>0.4214064149426566</v>
       </c>
       <c r="E132" t="n">
-        <v>2.36816904458455</v>
+        <v>2.414366839045107</v>
       </c>
       <c r="F132" t="n">
-        <v>0.501855188215917</v>
+        <v>0.2939097260541329</v>
       </c>
       <c r="G132" t="n">
-        <v>0.3706987173116407</v>
+        <v>0.2907752305287869</v>
       </c>
     </row>
     <row r="133">
@@ -3483,22 +3483,22 @@
         <v>1.51</v>
       </c>
       <c r="B133" t="n">
-        <v>0.01017759401219488</v>
+        <v>0.004591856473120164</v>
       </c>
       <c r="C133" t="n">
-        <v>0.3800544323463156</v>
+        <v>0.3909324314475331</v>
       </c>
       <c r="D133" t="n">
-        <v>0.408252978777832</v>
+        <v>0.4218471184034329</v>
       </c>
       <c r="E133" t="n">
-        <v>2.371757248268377</v>
+        <v>2.418514746270785</v>
       </c>
       <c r="F133" t="n">
-        <v>0.5030889155098029</v>
+        <v>0.291991340468414</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3798479013179304</v>
+        <v>0.2984431004408151</v>
       </c>
     </row>
     <row r="134">
@@ -3506,22 +3506,22 @@
         <v>1.52</v>
       </c>
       <c r="B134" t="n">
-        <v>0.01028490743576942</v>
+        <v>0.004594851600687351</v>
       </c>
       <c r="C134" t="n">
-        <v>0.3797081976773643</v>
+        <v>0.3909514314098697</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4082592579608781</v>
+        <v>0.4223018893481258</v>
       </c>
       <c r="E134" t="n">
-        <v>2.375046953205543</v>
+        <v>2.42231759362327</v>
       </c>
       <c r="F134" t="n">
-        <v>0.5041984118938562</v>
+        <v>0.290060068394869</v>
       </c>
       <c r="G134" t="n">
-        <v>0.3882257980644744</v>
+        <v>0.3054656404697272</v>
       </c>
     </row>
     <row r="135">
@@ -3529,22 +3529,22 @@
         <v>1.53</v>
       </c>
       <c r="B135" t="n">
-        <v>0.01038187495272335</v>
+        <v>0.004597557973044846</v>
       </c>
       <c r="C135" t="n">
-        <v>0.3793678243203738</v>
+        <v>0.3909681835180926</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4082659945350277</v>
+        <v>0.4227713780481037</v>
       </c>
       <c r="E135" t="n">
-        <v>2.378019503224381</v>
+        <v>2.425753814860487</v>
       </c>
       <c r="F135" t="n">
-        <v>0.5051823500874864</v>
+        <v>0.2881175716536036</v>
       </c>
       <c r="G135" t="n">
-        <v>0.3957872351122965</v>
+        <v>0.3118047373257107</v>
       </c>
     </row>
     <row r="136">
@@ -3552,22 +3552,22 @@
         <v>1.54</v>
       </c>
       <c r="B136" t="n">
-        <v>0.01046788798031429</v>
+        <v>0.004599958604592082</v>
       </c>
       <c r="C136" t="n">
-        <v>0.3790339807453292</v>
+        <v>0.3909826911271013</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4082732166306533</v>
+        <v>0.4232562389620627</v>
       </c>
       <c r="E136" t="n">
-        <v>2.380656242153224</v>
+        <v>2.428801843740361</v>
       </c>
       <c r="F136" t="n">
-        <v>0.5060394028101033</v>
+        <v>0.2861655120647234</v>
       </c>
       <c r="G136" t="n">
-        <v>0.4024870400224208</v>
+        <v>0.3174222777189536</v>
       </c>
     </row>
     <row r="137">
@@ -3575,22 +3575,22 @@
         <v>1.55</v>
       </c>
       <c r="B137" t="n">
-        <v>0.01054233793579984</v>
+        <v>0.004602036509728485</v>
       </c>
       <c r="C137" t="n">
-        <v>0.3787073354222159</v>
+        <v>0.3909949575917951</v>
       </c>
       <c r="D137" t="n">
-        <v>0.408280952381784</v>
+        <v>0.4237571309601416</v>
       </c>
       <c r="E137" t="n">
-        <v>2.382938513820407</v>
+        <v>2.431440114020818</v>
       </c>
       <c r="F137" t="n">
-        <v>0.5067682427811165</v>
+        <v>0.2842055514483341</v>
       </c>
       <c r="G137" t="n">
-        <v>0.4082800403558702</v>
+        <v>0.3222801483596438</v>
       </c>
     </row>
     <row r="138">
@@ -3598,22 +3598,22 @@
         <v>1.56</v>
       </c>
       <c r="B138" t="n">
-        <v>0.01060461623643762</v>
+        <v>0.004603774702853488</v>
       </c>
       <c r="C138" t="n">
-        <v>0.378388556821019</v>
+        <v>0.3910049862670733</v>
       </c>
       <c r="D138" t="n">
-        <v>0.4082892299264489</v>
+        <v>0.4242747175584796</v>
       </c>
       <c r="E138" t="n">
-        <v>2.384847662054264</v>
+        <v>2.433647059459783</v>
       </c>
       <c r="F138" t="n">
-        <v>0.507367542719936</v>
+        <v>0.2822393516245412</v>
       </c>
       <c r="G138" t="n">
-        <v>0.4131210636736694</v>
+        <v>0.326340235957969</v>
       </c>
     </row>
     <row r="139">
@@ -3621,22 +3621,22 @@
         <v>1.57</v>
       </c>
       <c r="B139" t="n">
-        <v>0.01065411429948523</v>
+        <v>0.004605156198366519</v>
       </c>
       <c r="C139" t="n">
-        <v>0.3780783134117238</v>
+        <v>0.3910127805078352</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4082980774070409</v>
+        <v>0.4248096671643776</v>
       </c>
       <c r="E139" t="n">
-        <v>2.386365030683126</v>
+        <v>2.435401113815184</v>
       </c>
       <c r="F139" t="n">
-        <v>0.5078359753459711</v>
+        <v>0.2802685744134505</v>
       </c>
       <c r="G139" t="n">
-        <v>0.4169649375368424</v>
+        <v>0.3295644272241174</v>
       </c>
     </row>
     <row r="140">
@@ -3644,22 +3644,22 @@
         <v>1.58</v>
       </c>
       <c r="B140" t="n">
-        <v>0.01069022354220029</v>
+        <v>0.004606164010667009</v>
       </c>
       <c r="C140" t="n">
-        <v>0.3777772736643156</v>
+        <v>0.3910183436689803</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4083075229706994</v>
+        <v>0.4253626533322317</v>
       </c>
       <c r="E140" t="n">
-        <v>2.387471963535329</v>
+        <v>2.436680710844942</v>
       </c>
       <c r="F140" t="n">
-        <v>0.5081722133786319</v>
+        <v>0.2782948816351675</v>
       </c>
       <c r="G140" t="n">
-        <v>0.4197664895064125</v>
+        <v>0.3319146088682765</v>
       </c>
     </row>
     <row r="141">
@@ -3667,22 +3667,22 @@
         <v>1.59</v>
       </c>
       <c r="B141" t="n">
-        <v>0.01071233538184042</v>
+        <v>0.004606781154154388</v>
       </c>
       <c r="C141" t="n">
-        <v>0.3774861060487795</v>
+        <v>0.3910216791054078</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4083175947697131</v>
+        <v>0.425934355030421</v>
       </c>
       <c r="E141" t="n">
-        <v>2.388149804439207</v>
+        <v>2.437464284306985</v>
       </c>
       <c r="F141" t="n">
-        <v>0.5083749295373279</v>
+        <v>0.2763199351097979</v>
       </c>
       <c r="G141" t="n">
-        <v>0.4214805471434035</v>
+        <v>0.3333526676006341</v>
       </c>
     </row>
     <row r="142">
@@ -3690,22 +3690,22 @@
         <v>1.6</v>
       </c>
       <c r="B142" t="n">
-        <v>0.01071984123566321</v>
+        <v>0.004606990643228085</v>
       </c>
       <c r="C142" t="n">
-        <v>0.377205479035101</v>
+        <v>0.3910227901720171</v>
       </c>
       <c r="D142" t="n">
-        <v>0.408328320961941</v>
+        <v>0.4265254569193407</v>
       </c>
       <c r="E142" t="n">
-        <v>2.388379897223092</v>
+        <v>2.437730267959238</v>
       </c>
       <c r="F142" t="n">
-        <v>0.5084427965414687</v>
+        <v>0.2743453966574473</v>
       </c>
       <c r="G142" t="n">
-        <v>0.42206193800884</v>
+        <v>0.3338404901313784</v>
       </c>
     </row>
     <row r="143">
@@ -3713,22 +3713,22 @@
         <v>1.61</v>
       </c>
       <c r="B143" t="n">
-        <v>0.0107179567107531</v>
+        <v>0.004605935766460317</v>
       </c>
       <c r="C143" t="n">
-        <v>0.3769303729224602</v>
+        <v>0.3910163453258863</v>
       </c>
       <c r="D143" t="n">
-        <v>0.4083751848036904</v>
+        <v>0.4271509436804268</v>
       </c>
       <c r="E143" t="n">
-        <v>2.388260183256548</v>
+        <v>2.437594650599037</v>
       </c>
       <c r="F143" t="n">
-        <v>0.5083071339444455</v>
+        <v>0.2723276758532968</v>
       </c>
       <c r="G143" t="n">
-        <v>0.4220124005819819</v>
+        <v>0.3337820713803235</v>
       </c>
     </row>
     <row r="144">
@@ -3736,22 +3736,22 @@
         <v>1.62</v>
       </c>
       <c r="B144" t="n">
-        <v>0.01071228949756168</v>
+        <v>0.00460279174565297</v>
       </c>
       <c r="C144" t="n">
-        <v>0.3766553224927195</v>
+        <v>0.3909971219158956</v>
       </c>
       <c r="D144" t="n">
-        <v>0.408492925722616</v>
+        <v>0.4278250761097339</v>
       </c>
       <c r="E144" t="n">
-        <v>2.387901920517504</v>
+        <v>2.437188756801539</v>
       </c>
       <c r="F144" t="n">
-        <v>0.5079017929607275</v>
+        <v>0.2702227262620701</v>
       </c>
       <c r="G144" t="n">
-        <v>0.4218603758367594</v>
+        <v>0.3336043408811648</v>
       </c>
     </row>
     <row r="145">
@@ -3759,22 +3759,22 @@
         <v>1.63</v>
       </c>
       <c r="B145" t="n">
-        <v>0.01070281913839735</v>
+        <v>0.004597589495049985</v>
       </c>
       <c r="C145" t="n">
-        <v>0.3763803279398873</v>
+        <v>0.3909652866346474</v>
       </c>
       <c r="D145" t="n">
-        <v>0.4086804828539023</v>
+        <v>0.4285474670615807</v>
       </c>
       <c r="E145" t="n">
-        <v>2.387306427746836</v>
+        <v>2.436514023991399</v>
       </c>
       <c r="F145" t="n">
-        <v>0.5072292438013419</v>
+        <v>0.268031525688187</v>
       </c>
       <c r="G145" t="n">
-        <v>0.4216007450762008</v>
+        <v>0.3333035872649107</v>
       </c>
     </row>
     <row r="146">
@@ -3782,22 +3782,22 @@
         <v>1.64</v>
       </c>
       <c r="B146" t="n">
-        <v>0.01068952517556847</v>
+        <v>0.004590359928895299</v>
       </c>
       <c r="C146" t="n">
-        <v>0.376105389457972</v>
+        <v>0.390921006174744</v>
       </c>
       <c r="D146" t="n">
-        <v>0.4089368294580357</v>
+        <v>0.4293177417109042</v>
       </c>
       <c r="E146" t="n">
-        <v>2.386475023685422</v>
+        <v>2.435571889593274</v>
       </c>
       <c r="F146" t="n">
-        <v>0.5062919566773163</v>
+        <v>0.265755051936067</v>
       </c>
       <c r="G146" t="n">
-        <v>0.4212283896033342</v>
+        <v>0.3328760991625702</v>
       </c>
     </row>
     <row r="147">
@@ -3805,22 +3805,22 @@
         <v>1.65</v>
       </c>
       <c r="B147" t="n">
-        <v>0.01067238715138344</v>
+        <v>0.004581133961432852</v>
       </c>
       <c r="C147" t="n">
-        <v>0.3758305072409815</v>
+        <v>0.3908644472287879</v>
       </c>
       <c r="D147" t="n">
-        <v>0.4092609710982023</v>
+        <v>0.4301355369958929</v>
       </c>
       <c r="E147" t="n">
-        <v>2.385409027074138</v>
+        <v>2.43436379103182</v>
       </c>
       <c r="F147" t="n">
-        <v>0.5050924017996776</v>
+        <v>0.26339428281013</v>
       </c>
       <c r="G147" t="n">
-        <v>0.4207381907211875</v>
+        <v>0.3323181652051517</v>
       </c>
     </row>
     <row r="148">
@@ -3828,22 +3828,22 @@
         <v>1.66</v>
       </c>
       <c r="B148" t="n">
-        <v>0.01065138460815063</v>
+        <v>0.004569942506906584</v>
       </c>
       <c r="C148" t="n">
-        <v>0.3755556814829243</v>
+        <v>0.3907957764893816</v>
       </c>
       <c r="D148" t="n">
-        <v>0.4096519438716188</v>
+        <v>0.4310005010713447</v>
       </c>
       <c r="E148" t="n">
-        <v>2.384109756653863</v>
+        <v>2.432891165731693</v>
       </c>
       <c r="F148" t="n">
-        <v>0.5036330493794534</v>
+        <v>0.2609501961147956</v>
       </c>
       <c r="G148" t="n">
-        <v>0.4201250297327889</v>
+        <v>0.3316260740236641</v>
       </c>
     </row>
     <row r="149">
@@ -3851,22 +3851,22 @@
         <v>1.67</v>
       </c>
       <c r="B149" t="n">
-        <v>0.01062649708817844</v>
+        <v>0.004556816479560433</v>
       </c>
       <c r="C149" t="n">
-        <v>0.3752809123778088</v>
+        <v>0.3907151606491274</v>
       </c>
       <c r="D149" t="n">
-        <v>0.4101088126917654</v>
+        <v>0.4319122927721676</v>
       </c>
       <c r="E149" t="n">
-        <v>2.382578531165474</v>
+        <v>2.43115545111755</v>
       </c>
       <c r="F149" t="n">
-        <v>0.5019163696276708</v>
+        <v>0.2584237696544835</v>
       </c>
       <c r="G149" t="n">
-        <v>0.4193837879411663</v>
+        <v>0.3307961142491161</v>
       </c>
     </row>
     <row r="150">
@@ -3874,22 +3874,22 @@
         <v>1.68</v>
       </c>
       <c r="B150" t="n">
-        <v>0.01059770413377522</v>
+        <v>0.004541786793638338</v>
       </c>
       <c r="C150" t="n">
-        <v>0.375006200119643</v>
+        <v>0.3906227664006277</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4106306696186461</v>
+        <v>0.4328705810864632</v>
       </c>
       <c r="E150" t="n">
-        <v>2.380816669349849</v>
+        <v>2.429158084614047</v>
       </c>
       <c r="F150" t="n">
-        <v>0.4999448327553575</v>
+        <v>0.2558159812336133</v>
       </c>
       <c r="G150" t="n">
-        <v>0.4185093466493481</v>
+        <v>0.3298245745125163</v>
       </c>
     </row>
     <row r="151">
@@ -3897,22 +3897,22 @@
         <v>1.69</v>
       </c>
       <c r="B151" t="n">
-        <v>0.01056498528724938</v>
+        <v>0.004524884363384238</v>
       </c>
       <c r="C151" t="n">
-        <v>0.3747315449024354</v>
+        <v>0.390518760436485</v>
       </c>
       <c r="D151" t="n">
-        <v>0.4112166322343547</v>
+        <v>0.4338750446376551</v>
       </c>
       <c r="E151" t="n">
-        <v>2.378825489947865</v>
+        <v>2.42690050364584</v>
       </c>
       <c r="F151" t="n">
-        <v>0.4977209089735404</v>
+        <v>0.2531278086566049</v>
       </c>
       <c r="G151" t="n">
-        <v>0.417496587160362</v>
+        <v>0.3287077434448733</v>
       </c>
     </row>
     <row r="152">
@@ -3920,22 +3920,22 @@
         <v>1.7</v>
       </c>
       <c r="B152" t="n">
-        <v>0.0105283200909093</v>
+        <v>0.004506140103042074</v>
       </c>
       <c r="C152" t="n">
-        <v>0.3744569469201943</v>
+        <v>0.3904033094493016</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4118658420613652</v>
+        <v>0.4349253711751459</v>
       </c>
       <c r="E152" t="n">
-        <v>2.376606311700399</v>
+        <v>2.424384145637585</v>
       </c>
       <c r="F152" t="n">
-        <v>0.4952470684932471</v>
+        <v>0.2503602297278777</v>
       </c>
       <c r="G152" t="n">
-        <v>0.4163403907772364</v>
+        <v>0.3274419096771961</v>
       </c>
     </row>
     <row r="153">
@@ -3943,22 +3943,22 @@
         <v>1.71</v>
       </c>
       <c r="B153" t="n">
-        <v>0.01048768808706334</v>
+        <v>0.004485584926855782</v>
       </c>
       <c r="C153" t="n">
-        <v>0.3741824063669278</v>
+        <v>0.39027658013168</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4125774630211025</v>
+        <v>0.4360212570730064</v>
       </c>
       <c r="E153" t="n">
-        <v>2.37416045334833</v>
+        <v>2.421610448013939</v>
       </c>
       <c r="F153" t="n">
-        <v>0.4925257815255047</v>
+        <v>0.2475142222518516</v>
       </c>
       <c r="G153" t="n">
-        <v>0.4150356388029993</v>
+        <v>0.326023361840493</v>
       </c>
     </row>
     <row r="154">
@@ -3966,22 +3966,22 @@
         <v>1.72</v>
       </c>
       <c r="B154" t="n">
-        <v>0.01044306881801991</v>
+        <v>0.004463249749069303</v>
       </c>
       <c r="C154" t="n">
-        <v>0.3739079234366444</v>
+        <v>0.3901387391762227</v>
       </c>
       <c r="D154" t="n">
-        <v>0.4133506799304803</v>
+        <v>0.4371624068362218</v>
       </c>
       <c r="E154" t="n">
-        <v>2.371489233632534</v>
+        <v>2.418580848199557</v>
       </c>
       <c r="F154" t="n">
-        <v>0.4895595182813408</v>
+        <v>0.2445907640329463</v>
       </c>
       <c r="G154" t="n">
-        <v>0.4135772125406787</v>
+        <v>0.324448388565773</v>
       </c>
     </row>
     <row r="155">
@@ -3989,22 +3989,22 @@
         <v>1.73</v>
       </c>
       <c r="B155" t="n">
-        <v>0.01039444182608737</v>
+        <v>0.004439165483926576</v>
       </c>
       <c r="C155" t="n">
-        <v>0.3736334983233521</v>
+        <v>0.3899899532755318</v>
       </c>
       <c r="D155" t="n">
-        <v>0.4141846970342168</v>
+        <v>0.4383485326140364</v>
       </c>
       <c r="E155" t="n">
-        <v>2.368593971293889</v>
+        <v>2.415296783619096</v>
       </c>
       <c r="F155" t="n">
-        <v>0.4863507489717824</v>
+        <v>0.2415908328755813</v>
       </c>
       <c r="G155" t="n">
-        <v>0.4119599932933027</v>
+        <v>0.3227132784840446</v>
       </c>
     </row>
     <row r="156">
@@ -4012,22 +4012,22 @@
         <v>1.74</v>
       </c>
       <c r="B156" t="n">
-        <v>0.01034178665357412</v>
+        <v>0.004413363045671539</v>
       </c>
       <c r="C156" t="n">
-        <v>0.3733591312210595</v>
+        <v>0.38983038912221</v>
       </c>
       <c r="D156" t="n">
-        <v>0.4150787365708596</v>
+        <v>0.4395793537199601</v>
       </c>
       <c r="E156" t="n">
-        <v>2.365475985073273</v>
+        <v>2.411759691697213</v>
       </c>
       <c r="F156" t="n">
-        <v>0.482901943807857</v>
+        <v>0.2385154065841765</v>
       </c>
       <c r="G156" t="n">
-        <v>0.4101788623638994</v>
+        <v>0.3208143202263167</v>
       </c>
     </row>
     <row r="157">
@@ -4035,22 +4035,22 @@
         <v>1.75</v>
       </c>
       <c r="B157" t="n">
-        <v>0.01028508284278852</v>
+        <v>0.004385873348548133</v>
       </c>
       <c r="C157" t="n">
-        <v>0.3730848223237747</v>
+        <v>0.3896602134088596</v>
       </c>
       <c r="D157" t="n">
-        <v>0.4160320373705647</v>
+        <v>0.4408545961580151</v>
       </c>
       <c r="E157" t="n">
-        <v>2.362136593711563</v>
+        <v>2.407971009858563</v>
       </c>
       <c r="F157" t="n">
-        <v>0.4792155730005919</v>
+        <v>0.2353654629631514</v>
       </c>
       <c r="G157" t="n">
-        <v>0.4082287010554969</v>
+        <v>0.3187478024235977</v>
       </c>
     </row>
     <row r="158">
@@ -4058,22 +4058,22 @@
         <v>1.76</v>
       </c>
       <c r="B158" t="n">
-        <v>0.01022430993603898</v>
+        <v>0.004356727306800295</v>
       </c>
       <c r="C158" t="n">
-        <v>0.3728105718255059</v>
+        <v>0.3894795928280831</v>
       </c>
       <c r="D158" t="n">
-        <v>0.4170438534827831</v>
+        <v>0.4421739921548202</v>
       </c>
       <c r="E158" t="n">
-        <v>2.358577115949636</v>
+        <v>2.403932175527803</v>
       </c>
       <c r="F158" t="n">
-        <v>0.4752941067610144</v>
+        <v>0.2321419798169258</v>
       </c>
       <c r="G158" t="n">
-        <v>0.4061043906711232</v>
+        <v>0.3165100137068966</v>
       </c>
     </row>
     <row r="159">
@@ -4081,22 +4081,22 @@
         <v>1.77</v>
       </c>
       <c r="B159" t="n">
-        <v>0.01015944747563385</v>
+        <v>0.004325955834671965</v>
       </c>
       <c r="C159" t="n">
-        <v>0.3725363799202616</v>
+        <v>0.3892886940724827</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4181134528321196</v>
+        <v>0.4435372796971266</v>
       </c>
       <c r="E159" t="n">
-        <v>2.35479887052837</v>
+        <v>2.399644626129589</v>
       </c>
       <c r="F159" t="n">
-        <v>0.4711400153001518</v>
+        <v>0.2288459349499194</v>
       </c>
       <c r="G159" t="n">
-        <v>0.4038008125138065</v>
+        <v>0.3140972427072219</v>
       </c>
     </row>
     <row r="160">
@@ -4104,22 +4104,22 @@
         <v>1.78</v>
       </c>
       <c r="B160" t="n">
-        <v>0.01009047500388154</v>
+        <v>0.004293589846407081</v>
       </c>
       <c r="C160" t="n">
-        <v>0.3722622468020499</v>
+        <v>0.3890876838346611</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4192401159007225</v>
+        <v>0.4449442020744362</v>
       </c>
       <c r="E160" t="n">
-        <v>2.350803176188642</v>
+        <v>2.395109799088576</v>
       </c>
       <c r="F160" t="n">
-        <v>0.4667557688290313</v>
+        <v>0.2254783061665518</v>
       </c>
       <c r="G160" t="n">
-        <v>0.4013128478865748</v>
+        <v>0.3115057780555824</v>
       </c>
     </row>
     <row r="161">
@@ -4127,22 +4127,22 @@
         <v>1.79</v>
       </c>
       <c r="B161" t="n">
-        <v>0.01001737206309042</v>
+        <v>0.004259660256249584</v>
       </c>
       <c r="C161" t="n">
-        <v>0.3719881726648793</v>
+        <v>0.3888767288072205</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4204231344356673</v>
+        <v>0.4463945074263475</v>
       </c>
       <c r="E161" t="n">
-        <v>2.346591351671332</v>
+        <v>2.390329131829422</v>
       </c>
       <c r="F161" t="n">
-        <v>0.4621438375586805</v>
+        <v>0.2220400712712427</v>
       </c>
       <c r="G161" t="n">
-        <v>0.3986353780924561</v>
+        <v>0.3087319083829866</v>
       </c>
     </row>
     <row r="162">
@@ -4150,22 +4150,22 @@
         <v>1.8</v>
       </c>
       <c r="B162" t="n">
-        <v>0.009940118195568866</v>
+        <v>0.004224197978443412</v>
       </c>
       <c r="C162" t="n">
-        <v>0.3717141577027578</v>
+        <v>0.3886559956827634</v>
       </c>
       <c r="D162" t="n">
-        <v>0.4216618101798891</v>
+        <v>0.4478879482942936</v>
       </c>
       <c r="E162" t="n">
-        <v>2.342164715717313</v>
+        <v>2.385304061776783</v>
       </c>
       <c r="F162" t="n">
-        <v>0.4573066917001266</v>
+        <v>0.2185322080684119</v>
       </c>
       <c r="G162" t="n">
-        <v>0.3957632844344787</v>
+        <v>0.3057719223204434</v>
       </c>
     </row>
     <row r="163">
@@ -4173,22 +4173,22 @@
         <v>1.81</v>
       </c>
       <c r="B163" t="n">
-        <v>0.009858692943625269</v>
+        <v>0.004187233927232504</v>
       </c>
       <c r="C163" t="n">
-        <v>0.3714402021096939</v>
+        <v>0.3884256511538922</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4229554536253117</v>
+        <v>0.4494242811773468</v>
       </c>
       <c r="E163" t="n">
-        <v>2.337524587067466</v>
+        <v>2.380036026355314</v>
       </c>
       <c r="F163" t="n">
-        <v>0.4522468014643967</v>
+        <v>0.2149556943624789</v>
       </c>
       <c r="G163" t="n">
-        <v>0.3926914482156705</v>
+        <v>0.3026221084989615</v>
       </c>
     </row>
     <row r="164">
@@ -4196,22 +4196,22 @@
         <v>1.82</v>
       </c>
       <c r="B164" t="n">
-        <v>0.009773075849568011</v>
+        <v>0.004148799016860799</v>
       </c>
       <c r="C164" t="n">
-        <v>0.3711663060796959</v>
+        <v>0.3881858619132093</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4243033827869066</v>
+        <v>0.4510032660917849</v>
       </c>
       <c r="E164" t="n">
-        <v>2.332672284462668</v>
+        <v>2.374526462989673</v>
       </c>
       <c r="F164" t="n">
-        <v>0.4469666370625184</v>
+        <v>0.2113115079578636</v>
       </c>
       <c r="G164" t="n">
-        <v>0.3894147507390596</v>
+        <v>0.2992787555495494</v>
       </c>
     </row>
     <row r="165">
@@ -4219,22 +4219,22 @@
         <v>1.83</v>
       </c>
       <c r="B165" t="n">
-        <v>0.009683246455705469</v>
+        <v>0.004108924161572236</v>
       </c>
       <c r="C165" t="n">
-        <v>0.3708924698067718</v>
+        <v>0.3879367946533172</v>
       </c>
       <c r="D165" t="n">
-        <v>0.4257049219965078</v>
+        <v>0.4526246661341242</v>
       </c>
       <c r="E165" t="n">
-        <v>2.327609126643796</v>
+        <v>2.368776809104515</v>
       </c>
       <c r="F165" t="n">
-        <v>0.4414686687055189</v>
+        <v>0.2076006266589855</v>
       </c>
       <c r="G165" t="n">
-        <v>0.3859280733076742</v>
+        <v>0.295738152103216</v>
       </c>
     </row>
     <row r="166">
@@ -4242,22 +4242,22 @@
         <v>1.84</v>
       </c>
       <c r="B166" t="n">
-        <v>0.009589184304346028</v>
+        <v>0.004067640275610755</v>
       </c>
       <c r="C166" t="n">
-        <v>0.3706186934849301</v>
+        <v>0.3876786160668181</v>
       </c>
       <c r="D166" t="n">
-        <v>0.4271594007152831</v>
+        <v>0.4542882470473408</v>
       </c>
       <c r="E166" t="n">
-        <v>2.322336432351727</v>
+        <v>2.362788502124496</v>
       </c>
       <c r="F166" t="n">
-        <v>0.4357553666044255</v>
+        <v>0.2038240282702645</v>
       </c>
       <c r="G166" t="n">
-        <v>0.3822262972245422</v>
+        <v>0.2919965867909698</v>
       </c>
     </row>
     <row r="167">
@@ -4265,22 +4265,22 @@
         <v>1.85</v>
       </c>
       <c r="B167" t="n">
-        <v>0.00949086893779807</v>
+        <v>0.004024978273220294</v>
       </c>
       <c r="C167" t="n">
-        <v>0.3703449773081791</v>
+        <v>0.3874114928463146</v>
       </c>
       <c r="D167" t="n">
-        <v>0.4286661523638519</v>
+        <v>0.4559937767900162</v>
       </c>
       <c r="E167" t="n">
-        <v>2.316855520327338</v>
+        <v>2.356562979474274</v>
       </c>
       <c r="F167" t="n">
-        <v>0.4298292009702656</v>
+        <v>0.19998269059612</v>
       </c>
       <c r="G167" t="n">
-        <v>0.3783043037926918</v>
+        <v>0.2880503482438196</v>
       </c>
     </row>
     <row r="168">
@@ -4288,22 +4288,22 @@
         <v>1.86</v>
       </c>
       <c r="B168" t="n">
-        <v>0.009388279898369975</v>
+        <v>0.003980969068644792</v>
       </c>
       <c r="C168" t="n">
-        <v>0.3700713214705271</v>
+        <v>0.387135591684409</v>
       </c>
       <c r="D168" t="n">
-        <v>0.4302245131691129</v>
+        <v>0.4577410251081558</v>
       </c>
       <c r="E168" t="n">
-        <v>2.311167709311509</v>
+        <v>2.350101678578503</v>
       </c>
       <c r="F168" t="n">
-        <v>0.4236926420140664</v>
+        <v>0.1960775914409719</v>
       </c>
       <c r="G168" t="n">
-        <v>0.374156974315151</v>
+        <v>0.2838957250927741</v>
       </c>
     </row>
     <row r="169">
@@ -4311,22 +4311,22 @@
         <v>1.87</v>
       </c>
       <c r="B169" t="n">
-        <v>0.009281396728370129</v>
+        <v>0.00393564357612819</v>
       </c>
       <c r="C169" t="n">
-        <v>0.3697977261659822</v>
+        <v>0.3868510792737039</v>
       </c>
       <c r="D169" t="n">
-        <v>0.431833821026926</v>
+        <v>0.4595297631094417</v>
       </c>
       <c r="E169" t="n">
-        <v>2.305274318045115</v>
+        <v>2.343406036861841</v>
       </c>
       <c r="F169" t="n">
-        <v>0.4173481599468555</v>
+        <v>0.1921097086092399</v>
       </c>
       <c r="G169" t="n">
-        <v>0.3697791900949481</v>
+        <v>0.279529005968842</v>
       </c>
     </row>
     <row r="170">
@@ -4334,22 +4334,22 @@
         <v>1.88</v>
       </c>
       <c r="B170" t="n">
-        <v>0.009170198970106909</v>
+        <v>0.003889032709914425</v>
       </c>
       <c r="C170" t="n">
-        <v>0.3695241915885529</v>
+        <v>0.3865581223068015</v>
       </c>
       <c r="D170" t="n">
-        <v>0.433493414379866</v>
+        <v>0.4613597628396979</v>
       </c>
       <c r="E170" t="n">
-        <v>2.299176665269034</v>
+        <v>2.336477491748942</v>
       </c>
       <c r="F170" t="n">
-        <v>0.4107982249796598</v>
+        <v>0.1880800199053436</v>
       </c>
       <c r="G170" t="n">
-        <v>0.365165832435111</v>
+        <v>0.274946479503032</v>
       </c>
     </row>
     <row r="171">
@@ -4357,22 +4357,22 @@
         <v>1.89</v>
       </c>
       <c r="B171" t="n">
-        <v>0.0090546661658887</v>
+        <v>0.003841167384247436</v>
       </c>
       <c r="C171" t="n">
-        <v>0.3692507179322473</v>
+        <v>0.3862568874763043</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4352026311093403</v>
+        <v>0.4632307968613549</v>
       </c>
       <c r="E171" t="n">
-        <v>2.292876069724145</v>
+        <v>2.329317480664466</v>
       </c>
       <c r="F171" t="n">
-        <v>0.4040453073235069</v>
+        <v>0.1839895031337026</v>
       </c>
       <c r="G171" t="n">
-        <v>0.3603117826386677</v>
+        <v>0.2701444343263527</v>
       </c>
     </row>
     <row r="172">
@@ -4380,22 +4380,22 @@
         <v>1.9</v>
       </c>
       <c r="B172" t="n">
-        <v>0.008934777858023881</v>
+        <v>0.003792078513371163</v>
       </c>
       <c r="C172" t="n">
-        <v>0.3689773053910739</v>
+        <v>0.3859475414748146</v>
       </c>
       <c r="D172" t="n">
-        <v>0.436960807441435</v>
+        <v>0.4651426378337166</v>
       </c>
       <c r="E172" t="n">
-        <v>2.286373850151323</v>
+        <v>2.321927441033065</v>
       </c>
       <c r="F172" t="n">
-        <v>0.3970918771894238</v>
+        <v>0.1798391360987367</v>
       </c>
       <c r="G172" t="n">
-        <v>0.3552119220086463</v>
+        <v>0.2651191590698128</v>
       </c>
     </row>
     <row r="173">
@@ -4403,22 +4403,22 @@
         <v>1.91</v>
       </c>
       <c r="B173" t="n">
-        <v>0.008810513588820838</v>
+        <v>0.003741797011529545</v>
       </c>
       <c r="C173" t="n">
-        <v>0.3687039541590407</v>
+        <v>0.3856302509949351</v>
       </c>
       <c r="D173" t="n">
-        <v>0.4387672768659256</v>
+        <v>0.4670950580948449</v>
       </c>
       <c r="E173" t="n">
-        <v>2.279671325291448</v>
+        <v>2.314308810279398</v>
       </c>
       <c r="F173" t="n">
-        <v>0.3899404047884383</v>
+        <v>0.1756298966048657</v>
       </c>
       <c r="G173" t="n">
-        <v>0.349861131848075</v>
+        <v>0.2598669423644211</v>
       </c>
     </row>
     <row r="174">
@@ -4426,22 +4426,22 @@
         <v>1.92</v>
       </c>
       <c r="B174" t="n">
-        <v>0.008681852900587952</v>
+        <v>0.00369035379296652</v>
       </c>
       <c r="C174" t="n">
-        <v>0.3684306644301562</v>
+        <v>0.3853051827292679</v>
       </c>
       <c r="D174" t="n">
-        <v>0.4406213690679577</v>
+        <v>0.4690878292448886</v>
       </c>
       <c r="E174" t="n">
-        <v>2.272769813885396</v>
+        <v>2.30646302582812</v>
       </c>
       <c r="F174" t="n">
-        <v>0.3825933603315774</v>
+        <v>0.1713627624565091</v>
       </c>
       <c r="G174" t="n">
-        <v>0.3442542934599819</v>
+        <v>0.2543840728411861</v>
       </c>
     </row>
     <row r="175">
@@ -4449,22 +4449,22 @@
         <v>1.93</v>
       </c>
       <c r="B175" t="n">
-        <v>0.008548775335633602</v>
+        <v>0.003637779771926028</v>
       </c>
       <c r="C175" t="n">
-        <v>0.3681574363984286</v>
+        <v>0.3849725033704156</v>
       </c>
       <c r="D175" t="n">
-        <v>0.4425224088719709</v>
+        <v>0.4711207217306975</v>
       </c>
       <c r="E175" t="n">
-        <v>2.265670634674045</v>
+        <v>2.298391525103888</v>
       </c>
       <c r="F175" t="n">
-        <v>0.3750532140298684</v>
+        <v>0.1670387114580866</v>
       </c>
       <c r="G175" t="n">
-        <v>0.3383862881473949</v>
+        <v>0.2486668391311167</v>
       </c>
     </row>
     <row r="176">
@@ -4472,22 +4472,22 @@
         <v>1.94</v>
       </c>
       <c r="B176" t="n">
-        <v>0.008411260436266173</v>
+        <v>0.003584105862652008</v>
       </c>
       <c r="C176" t="n">
-        <v>0.3678842702578662</v>
+        <v>0.3846323796109805</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4444697151975084</v>
+        <v>0.4731935044315739</v>
       </c>
       <c r="E176" t="n">
-        <v>2.258375106398272</v>
+        <v>2.290095745531358</v>
       </c>
       <c r="F176" t="n">
-        <v>0.3673224360943387</v>
+        <v>0.1626587214140179</v>
       </c>
       <c r="G176" t="n">
-        <v>0.3322519972133422</v>
+        <v>0.2427115298652216</v>
       </c>
     </row>
     <row r="177">
@@ -4495,22 +4495,22 @@
         <v>1.95</v>
       </c>
       <c r="B177" t="n">
-        <v>0.008269287744794046</v>
+        <v>0.0035293629793884</v>
       </c>
       <c r="C177" t="n">
-        <v>0.3676111662024773</v>
+        <v>0.3842849781435652</v>
       </c>
       <c r="D177" t="n">
-        <v>0.4464626000266222</v>
+        <v>0.4753059442460276</v>
       </c>
       <c r="E177" t="n">
-        <v>2.250884547798954</v>
+        <v>2.281577124535186</v>
       </c>
       <c r="F177" t="n">
-        <v>0.3594034967360157</v>
+        <v>0.1582237701287228</v>
       </c>
       <c r="G177" t="n">
-        <v>0.325846301960852</v>
+        <v>0.2365144336745094</v>
       </c>
     </row>
     <row r="178">
@@ -4518,22 +4518,22 @@
         <v>1.96</v>
       </c>
       <c r="B178" t="n">
-        <v>0.008122836803525603</v>
+        <v>0.003473582036379141</v>
       </c>
       <c r="C178" t="n">
-        <v>0.3673381244262701</v>
+        <v>0.3839304656607718</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4485003673826458</v>
+        <v>0.4774578056794111</v>
       </c>
       <c r="E178" t="n">
-        <v>2.24320027761697</v>
+        <v>2.272837099540028</v>
       </c>
       <c r="F178" t="n">
-        <v>0.3512988661659266</v>
+        <v>0.1537348354066209</v>
       </c>
       <c r="G178" t="n">
-        <v>0.319164083692952</v>
+        <v>0.2300718391899887</v>
       </c>
     </row>
     <row r="179">
@@ -4541,22 +4541,22 @@
         <v>1.97</v>
       </c>
       <c r="B179" t="n">
-        <v>0.007971887154769226</v>
+        <v>0.003416793947868172</v>
       </c>
       <c r="C179" t="n">
-        <v>0.3670651451232529</v>
+        <v>0.383569008855203</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4505823123201761</v>
+        <v>0.479648850432325</v>
       </c>
       <c r="E179" t="n">
-        <v>2.235323614593197</v>
+        <v>2.263877107970541</v>
       </c>
       <c r="F179" t="n">
-        <v>0.3430110145950987</v>
+        <v>0.1491928950521319</v>
       </c>
       <c r="G179" t="n">
-        <v>0.3122002237126707</v>
+        <v>0.2233800350426682</v>
       </c>
     </row>
     <row r="180">
@@ -4564,22 +4564,22 @@
         <v>1.98</v>
       </c>
       <c r="B180" t="n">
-        <v>0.007816418340833294</v>
+        <v>0.00335902962809943</v>
       </c>
       <c r="C180" t="n">
-        <v>0.3667922284874341</v>
+        <v>0.383200774419461</v>
       </c>
       <c r="D180" t="n">
-        <v>0.45270771992617</v>
+        <v>0.4818788369896967</v>
       </c>
       <c r="E180" t="n">
-        <v>2.227255877468512</v>
+        <v>2.254698587251381</v>
       </c>
       <c r="F180" t="n">
-        <v>0.3345424122345594</v>
+        <v>0.1445989268696755</v>
       </c>
       <c r="G180" t="n">
-        <v>0.3049496033230359</v>
+        <v>0.2164353098635569</v>
       </c>
     </row>
     <row r="181">
@@ -4587,22 +4587,22 @@
         <v>1.99</v>
       </c>
       <c r="B181" t="n">
-        <v>0.007656409904026194</v>
+        <v>0.003300319991316856</v>
       </c>
       <c r="C181" t="n">
-        <v>0.3665193747128219</v>
+        <v>0.3828259290461484</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4548758643321194</v>
+        <v>0.4841475202104452</v>
       </c>
       <c r="E181" t="n">
-        <v>2.218998384983793</v>
+        <v>2.245302974807203</v>
       </c>
       <c r="F181" t="n">
-        <v>0.3258955292953359</v>
+        <v>0.1399539086636713</v>
       </c>
       <c r="G181" t="n">
-        <v>0.2974071038270759</v>
+        <v>0.2092339522836631</v>
       </c>
     </row>
     <row r="182">
@@ -4610,22 +4610,22 @@
         <v>2</v>
       </c>
       <c r="B182" t="n">
-        <v>0.007491841386656307</v>
+        <v>0.003240695951764388</v>
       </c>
       <c r="C182" t="n">
-        <v>0.3662465839934246</v>
+        <v>0.3824446394278675</v>
       </c>
       <c r="D182" t="n">
-        <v>0.4570860077373419</v>
+        <v>0.4864546509176604</v>
       </c>
       <c r="E182" t="n">
-        <v>2.210552455879917</v>
+        <v>2.235691708062665</v>
       </c>
       <c r="F182" t="n">
-        <v>0.3170728359884556</v>
+        <v>0.1352588182385391</v>
       </c>
       <c r="G182" t="n">
-        <v>0.2895676065278186</v>
+        <v>0.2017722509339958</v>
       </c>
     </row>
     <row r="183">
@@ -4633,22 +4633,22 @@
         <v>2.01</v>
       </c>
       <c r="B183" t="n">
-        <v>0.007322692331032008</v>
+        <v>0.003180188423685964</v>
       </c>
       <c r="C183" t="n">
-        <v>0.3659738565232505</v>
+        <v>0.3820570722572208</v>
       </c>
       <c r="D183" t="n">
-        <v>0.4593373994434775</v>
+        <v>0.4887999754892358</v>
       </c>
       <c r="E183" t="n">
-        <v>2.201919408897762</v>
+        <v>2.225866224442423</v>
       </c>
       <c r="F183" t="n">
-        <v>0.3080768025249457</v>
+        <v>0.1305146333986985</v>
       </c>
       <c r="G183" t="n">
-        <v>0.281425992728292</v>
+        <v>0.1940464944455633</v>
       </c>
     </row>
     <row r="184">
@@ -4656,22 +4656,22 @@
         <v>2.02</v>
       </c>
       <c r="B184" t="n">
-        <v>0.007148942279461694</v>
+        <v>0.003118828321325527</v>
       </c>
       <c r="C184" t="n">
-        <v>0.3657011924963077</v>
+        <v>0.3816633942268106</v>
       </c>
       <c r="D184" t="n">
-        <v>0.4616292749003479</v>
+        <v>0.4911832354489027</v>
       </c>
       <c r="E184" t="n">
-        <v>2.193100562778205</v>
+        <v>2.215827961371132</v>
       </c>
       <c r="F184" t="n">
-        <v>0.298909899115834</v>
+        <v>0.1257223319485694</v>
       </c>
       <c r="G184" t="n">
-        <v>0.2729771437315247</v>
+        <v>0.1860529714493749</v>
       </c>
     </row>
     <row r="185">
@@ -4679,22 +4679,22 @@
         <v>2.03</v>
       </c>
       <c r="B185" t="n">
-        <v>0.006970570774253728</v>
+        <v>0.003056646558927011</v>
       </c>
       <c r="C185" t="n">
-        <v>0.3654285921066048</v>
+        <v>0.3812637720292393</v>
       </c>
       <c r="D185" t="n">
-        <v>0.4639608547633996</v>
+        <v>0.4936041670576356</v>
       </c>
       <c r="E185" t="n">
-        <v>2.184097236262123</v>
+        <v>2.205578356273449</v>
       </c>
       <c r="F185" t="n">
-        <v>0.2895745959721471</v>
+        <v>0.120882891692571</v>
       </c>
       <c r="G185" t="n">
-        <v>0.2642159408405439</v>
+        <v>0.1777879705764386</v>
       </c>
     </row>
     <row r="186">
@@ -4702,22 +4702,22 @@
         <v>2.04</v>
       </c>
       <c r="B186" t="n">
-        <v>0.00678755735771651</v>
+        <v>0.00299367405073436</v>
       </c>
       <c r="C186" t="n">
-        <v>0.3651560555481498</v>
+        <v>0.3808583723571095</v>
       </c>
       <c r="D186" t="n">
-        <v>0.4663313439630066</v>
+        <v>0.4960625009053976</v>
       </c>
       <c r="E186" t="n">
-        <v>2.174910748090396</v>
+        <v>2.195118846574031</v>
       </c>
       <c r="F186" t="n">
-        <v>0.2800733633049129</v>
+        <v>0.1159972904351236</v>
       </c>
       <c r="G186" t="n">
-        <v>0.2551372653583787</v>
+        <v>0.1692477804577638</v>
       </c>
     </row>
     <row r="187">
@@ -4725,22 +4725,22 @@
         <v>2.05</v>
       </c>
       <c r="B187" t="n">
-        <v>0.006599881572158407</v>
+        <v>0.002929941710991508</v>
       </c>
       <c r="C187" t="n">
-        <v>0.3648835830149512</v>
+        <v>0.3804473619030234</v>
       </c>
       <c r="D187" t="n">
-        <v>0.4687399307859761</v>
+        <v>0.4985579615032196</v>
       </c>
       <c r="E187" t="n">
-        <v>2.165542417003898</v>
+        <v>2.184450869697534</v>
       </c>
       <c r="F187" t="n">
-        <v>0.2704086713251583</v>
+        <v>0.1110665059806464</v>
       </c>
       <c r="G187" t="n">
-        <v>0.2457359985880562</v>
+        <v>0.1604286897243585</v>
       </c>
     </row>
     <row r="188">
@@ -4748,22 +4748,22 @@
         <v>2.06</v>
       </c>
       <c r="B188" t="n">
-        <v>0.006407522959887815</v>
+        <v>0.0028654804539424</v>
       </c>
       <c r="C188" t="n">
-        <v>0.3646111747010172</v>
+        <v>0.3800309073595836</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4711857859696549</v>
+        <v>0.5010902668756103</v>
       </c>
       <c r="E188" t="n">
-        <v>2.155993561743509</v>
+        <v>2.173575863068612</v>
       </c>
       <c r="F188" t="n">
-        <v>0.2605829902439111</v>
+        <v>0.1060915161335595</v>
       </c>
       <c r="G188" t="n">
-        <v>0.2360070218326053</v>
+        <v>0.151326987007232</v>
       </c>
     </row>
     <row r="189">
@@ -4771,22 +4771,22 @@
         <v>2.07</v>
       </c>
       <c r="B189" t="n">
-        <v>0.006210461063213099</v>
+        <v>0.002800321193830968</v>
       </c>
       <c r="C189" t="n">
-        <v>0.3643388308003559</v>
+        <v>0.3796091754193923</v>
       </c>
       <c r="D189" t="n">
-        <v>0.4736680618091014</v>
+        <v>0.5036591281533126</v>
       </c>
       <c r="E189" t="n">
-        <v>2.146265501050105</v>
+        <v>2.162495264111924</v>
       </c>
       <c r="F189" t="n">
-        <v>0.2505987902721978</v>
+        <v>0.1010732986982822</v>
       </c>
       <c r="G189" t="n">
-        <v>0.2259452163950534</v>
+        <v>0.1419389609373924</v>
       </c>
     </row>
     <row r="190">
@@ -4794,22 +4794,22 @@
         <v>2.08</v>
       </c>
       <c r="B190" t="n">
-        <v>0.00600867542444266</v>
+        <v>0.002734494844901158</v>
       </c>
       <c r="C190" t="n">
-        <v>0.3640665515069759</v>
+        <v>0.379182332775052</v>
       </c>
       <c r="D190" t="n">
-        <v>0.4761858912778374</v>
+        <v>0.5062642491664282</v>
       </c>
       <c r="E190" t="n">
-        <v>2.136359553664565</v>
+        <v>2.151210510252125</v>
       </c>
       <c r="F190" t="n">
-        <v>0.2404585416210468</v>
+        <v>0.09601283147923446</v>
       </c>
       <c r="G190" t="n">
-        <v>0.2155454635784292</v>
+        <v>0.132260900145849</v>
       </c>
     </row>
     <row r="191">
@@ -4817,22 +4817,22 @@
         <v>2.09</v>
       </c>
       <c r="B191" t="n">
-        <v>0.005802145585884861</v>
+        <v>0.002668032321396904</v>
       </c>
       <c r="C191" t="n">
-        <v>0.3637943370148853</v>
+        <v>0.3787505461191652</v>
       </c>
       <c r="D191" t="n">
-        <v>0.4787383871627656</v>
+        <v>0.5089053260379542</v>
       </c>
       <c r="E191" t="n">
-        <v>2.126277038327765</v>
+        <v>2.139723038913871</v>
       </c>
       <c r="F191" t="n">
-        <v>0.2301647145014843</v>
+        <v>0.09091109228083569</v>
       </c>
       <c r="G191" t="n">
-        <v>0.2048026446857601</v>
+        <v>0.1222890932636099</v>
       </c>
     </row>
     <row r="192">
@@ -4840,22 +4840,22 @@
         <v>2.1</v>
       </c>
       <c r="B192" t="n">
-        <v>0.005590851089848104</v>
+        <v>0.002600964537562148</v>
       </c>
       <c r="C192" t="n">
-        <v>0.3635221875180924</v>
+        <v>0.3783139821443343</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4813246412138829</v>
+        <v>0.5115820467777756</v>
       </c>
       <c r="E192" t="n">
-        <v>2.116019273780583</v>
+        <v>2.128034287521819</v>
       </c>
       <c r="F192" t="n">
-        <v>0.2197197791245387</v>
+        <v>0.08576905890750597</v>
       </c>
       <c r="G192" t="n">
-        <v>0.1937116410200751</v>
+        <v>0.1120198289216845</v>
       </c>
     </row>
     <row r="193">
@@ -4863,22 +4863,22 @@
         <v>2.11</v>
       </c>
       <c r="B193" t="n">
-        <v>0.005374771478640749</v>
+        <v>0.002533322407640827</v>
       </c>
       <c r="C193" t="n">
-        <v>0.3632501032106054</v>
+        <v>0.3778728075431615</v>
       </c>
       <c r="D193" t="n">
-        <v>0.4839437233094924</v>
+        <v>0.5142940908771821</v>
       </c>
       <c r="E193" t="n">
-        <v>2.105587578763897</v>
+        <v>2.116145693500624</v>
       </c>
       <c r="F193" t="n">
-        <v>0.2091262057012363</v>
+        <v>0.08058770916366453</v>
       </c>
       <c r="G193" t="n">
-        <v>0.1822673338844012</v>
+        <v>0.1014493957510806</v>
       </c>
     </row>
     <row r="194">
@@ -4886,22 +4886,22 @@
         <v>2.12</v>
       </c>
       <c r="B194" t="n">
-        <v>0.0051538862945712</v>
+        <v>0.002465136845876882</v>
       </c>
       <c r="C194" t="n">
-        <v>0.3629780842864328</v>
+        <v>0.3774271890082495</v>
       </c>
       <c r="D194" t="n">
-        <v>0.4865946806376596</v>
+        <v>0.5170411289039835</v>
       </c>
       <c r="E194" t="n">
-        <v>2.094983272018584</v>
+        <v>2.104058694274944</v>
       </c>
       <c r="F194" t="n">
-        <v>0.1983864644426053</v>
+        <v>0.07536802085373151</v>
       </c>
       <c r="G194" t="n">
-        <v>0.1704646045817674</v>
+        <v>0.09057408238280779</v>
       </c>
     </row>
     <row r="195">
@@ -4909,22 +4909,22 @@
         <v>2.13</v>
       </c>
       <c r="B195" t="n">
-        <v>0.004928175079947829</v>
+        <v>0.002396438766514252</v>
       </c>
       <c r="C195" t="n">
-        <v>0.3627061309395827</v>
+        <v>0.3769772932322006</v>
       </c>
       <c r="D195" t="n">
-        <v>0.4892765368947267</v>
+        <v>0.519822822098311</v>
       </c>
       <c r="E195" t="n">
-        <v>2.084207672285522</v>
+        <v>2.091774727269435</v>
       </c>
       <c r="F195" t="n">
-        <v>0.1875030255596726</v>
+        <v>0.0701109717821264</v>
       </c>
       <c r="G195" t="n">
-        <v>0.1582983344152016</v>
+        <v>0.07939017744787437</v>
       </c>
     </row>
     <row r="196">
@@ -4932,22 +4932,22 @@
         <v>2.14</v>
       </c>
       <c r="B196" t="n">
-        <v>0.004697617377079006</v>
+        <v>0.002327259083796873</v>
       </c>
       <c r="C196" t="n">
-        <v>0.3624342433640634</v>
+        <v>0.3765232869076171</v>
       </c>
       <c r="D196" t="n">
-        <v>0.4919882915017481</v>
+        <v>0.5226388219692097</v>
       </c>
       <c r="E196" t="n">
-        <v>2.073262098305587</v>
+        <v>2.079295229908752</v>
       </c>
       <c r="F196" t="n">
-        <v>0.1764783592634652</v>
+        <v>0.06481753975326864</v>
       </c>
       <c r="G196" t="n">
-        <v>0.1457634046877311</v>
+        <v>0.06789396957728853</v>
       </c>
     </row>
     <row r="197">
@@ -4955,22 +4955,22 @@
         <v>2.15</v>
       </c>
       <c r="B197" t="n">
-        <v>0.004462192728273136</v>
+        <v>0.002257628711968688</v>
       </c>
       <c r="C197" t="n">
-        <v>0.3621624217538833</v>
+        <v>0.3760653367271016</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4947289188397674</v>
+        <v>0.5254887698921329</v>
       </c>
       <c r="E197" t="n">
-        <v>2.062147868819658</v>
+        <v>2.066621639617551</v>
       </c>
       <c r="F197" t="n">
-        <v>0.1653149357650111</v>
+        <v>0.05948870257157833</v>
       </c>
       <c r="G197" t="n">
-        <v>0.132854696702385</v>
+        <v>0.05608174740205991</v>
       </c>
     </row>
     <row r="198">
@@ -4978,22 +4978,22 @@
         <v>2.16</v>
       </c>
       <c r="B198" t="n">
-        <v>0.004221880675838577</v>
+        <v>0.002187578565273632</v>
       </c>
       <c r="C198" t="n">
-        <v>0.3618906663030506</v>
+        <v>0.3756036093832564</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4974973675049114</v>
+        <v>0.5283722967074692</v>
       </c>
       <c r="E198" t="n">
-        <v>2.050866302568612</v>
+        <v>2.05375539382049</v>
       </c>
       <c r="F198" t="n">
-        <v>0.1540152252753368</v>
+        <v>0.05412543804147478</v>
       </c>
       <c r="G198" t="n">
-        <v>0.1195670917621905</v>
+        <v>0.04394979955319628</v>
       </c>
     </row>
     <row r="199">
@@ -5001,22 +5001,22 @@
         <v>2.17</v>
       </c>
       <c r="B199" t="n">
-        <v>0.003976660762083735</v>
+        <v>0.002117139557955649</v>
       </c>
       <c r="C199" t="n">
-        <v>0.3616189772055735</v>
+        <v>0.3751382715686839</v>
       </c>
       <c r="D199" t="n">
-        <v>0.5002925595843254</v>
+        <v>0.5312890223202409</v>
       </c>
       <c r="E199" t="n">
-        <v>2.039418718293327</v>
+        <v>2.040697929942224</v>
       </c>
       <c r="F199" t="n">
-        <v>0.1425816980054707</v>
+        <v>0.0487287239673781</v>
       </c>
       <c r="G199" t="n">
-        <v>0.1058954711701766</v>
+        <v>0.03149441466170727</v>
       </c>
     </row>
     <row r="200">
@@ -5024,22 +5024,22 @@
         <v>2.18</v>
       </c>
       <c r="B200" t="n">
-        <v>0.003726512529316969</v>
+        <v>0.002046342604258673</v>
       </c>
       <c r="C200" t="n">
-        <v>0.3613473546554604</v>
+        <v>0.3746694899759866</v>
       </c>
       <c r="D200" t="n">
-        <v>0.503113389954035</v>
+        <v>0.5342385553011296</v>
       </c>
       <c r="E200" t="n">
-        <v>2.02780643473468</v>
+        <v>2.027450685407409</v>
       </c>
       <c r="F200" t="n">
-        <v>0.1310168241664388</v>
+        <v>0.04329953815370746</v>
       </c>
       <c r="G200" t="n">
-        <v>0.09183471622937031</v>
+        <v>0.01871188135860051</v>
       </c>
     </row>
     <row r="201">
@@ -5047,22 +5047,22 @@
         <v>2.19</v>
       </c>
       <c r="B201" t="n">
-        <v>0.003471415519846683</v>
+        <v>0.001975218618426648</v>
       </c>
       <c r="C201" t="n">
-        <v>0.3610757988467196</v>
+        <v>0.3741974312977668</v>
       </c>
       <c r="D201" t="n">
-        <v>0.5059587255998601</v>
+        <v>0.5372204924889941</v>
       </c>
       <c r="E201" t="n">
-        <v>2.016030770633549</v>
+        <v>2.014015097640702</v>
       </c>
       <c r="F201" t="n">
-        <v>0.1193230739692697</v>
+        <v>0.0378388584048831</v>
       </c>
       <c r="G201" t="n">
-        <v>0.07737970824280085</v>
+        <v>0.005598488274885821</v>
       </c>
     </row>
     <row r="202">
@@ -5070,22 +5070,22 @@
         <v>2.2</v>
       </c>
       <c r="B202" t="n">
-        <v>0.003211349275981237</v>
+        <v>0.001903798514703507</v>
       </c>
       <c r="C202" t="n">
-        <v>0.3608043099733593</v>
+        <v>0.373722262226627</v>
       </c>
       <c r="D202" t="n">
-        <v>0.5088274049625656</v>
+        <v>0.5402344185950634</v>
       </c>
       <c r="E202" t="n">
-        <v>2.00409304473081</v>
+        <v>2.000392604066759</v>
       </c>
       <c r="F202" t="n">
-        <v>0.1075029176249896</v>
+        <v>0.03234766252532421</v>
       </c>
       <c r="G202" t="n">
-        <v>0.06252532851349527</v>
+        <v>-0.007849475958429192</v>
       </c>
     </row>
   </sheetData>

--- a/01_Thermal/B_results/single_annular_bemt_params_pchip.xlsx
+++ b/01_Thermal/B_results/single_annular_bemt_params_pchip.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G202"/>
+  <dimension ref="A1:G352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,4625 +467,8075 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.06797329609303578</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2915344141975234</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1788218862659403</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E2" t="n">
-        <v>7.167467894583679</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4378798599304675</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1828318586006233</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.21</v>
+        <v>0.01</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06152968036192982</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2917448556584337</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1849548055877714</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E3" t="n">
-        <v>6.990271983850854</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4378522457369501</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1823418779670907</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.22</v>
+        <v>0.02</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05522079825589636</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2923626854742379</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1908625174022587</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E4" t="n">
-        <v>6.816625639523846</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4377694730950648</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1809139568221489</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.23</v>
+        <v>0.03</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04909254392997003</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2933676617945468</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1965091511650544</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E5" t="n">
-        <v>6.646884518424427</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4376316469128121</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1786111262992818</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="B6" t="n">
-        <v>0.04319081153918544</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2947395427689706</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2018594289437717</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E6" t="n">
-        <v>6.481404277374363</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4374388720981928</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1754964175319734</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03756149523857726</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2964580865471199</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2068790218141968</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E7" t="n">
-        <v>6.320540573195425</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4371912535592073</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1716328616537074</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.26</v>
+        <v>0.06</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0322504891831801</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2985030512786049</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2115349077658135</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E8" t="n">
-        <v>6.164649062709379</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4368888962038561</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1670834897979678</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.27</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02730368752802858</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3008541951130363</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2157957260546939</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E9" t="n">
-        <v>6.014085402737996</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4365319049401399</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1619113330982385</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.28</v>
+        <v>0.08</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02276698442815734</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3034912762000245</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D10" t="n">
-        <v>0.219632122816334</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E10" t="n">
-        <v>5.869205250103041</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4361203846760593</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1561794226880035</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.29</v>
+        <v>0.09</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01868627403860103</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3063940526891799</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2230170827200622</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E11" t="n">
-        <v>5.730364261626288</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4356544403196147</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1499507897007465</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01510745051439427</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3095422827301128</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2259262415144025</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E12" t="n">
-        <v>5.597918094129504</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4351341767788067</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1432884652699516</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.31</v>
+        <v>0.11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01207640801057169</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3129157244724338</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D13" t="n">
-        <v>0.228338174481192</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E13" t="n">
-        <v>5.472222404434456</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F13" t="n">
-        <v>0.434559698961636</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1362554805291026</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.009639040682167912</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3164941360657534</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2302346560849494</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E14" t="n">
-        <v>5.353632849362914</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F14" t="n">
-        <v>0.433931111776103</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1289148666116834</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.33</v>
+        <v>0.13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.007841242684217577</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3202572756596819</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2316008864701806</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E15" t="n">
-        <v>5.242505085736647</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4332485201302084</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1213296546511779</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.34</v>
+        <v>0.14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.006728908171755314</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3241849014038298</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2324256809177603</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E16" t="n">
-        <v>5.139194770377421</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4325120289319526</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1135628757810701</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.006347931299815749</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3282567714478075</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2327016189146754</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E17" t="n">
-        <v>5.044057560107008</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4317217430893363</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1056775611348438</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.36</v>
+        <v>0.16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.006475267873536688</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3344108583673852</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2319448765114562</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E18" t="n">
-        <v>4.955441024838044</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4147130705969681</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G18" t="n">
-        <v>0.09547999132234394</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.37</v>
+        <v>0.17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.006833587069356076</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3441977455521746</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2298286182644702</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E19" t="n">
-        <v>4.87125031125215</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3683387937098757</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08120663396109426</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.38</v>
+        <v>0.18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.007387353099258765</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3570161073725492</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2265959533210997</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E20" t="n">
-        <v>4.79117744132457</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F20" t="n">
-        <v>0.297125078726688</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G20" t="n">
-        <v>0.06356580069609682</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.39</v>
+        <v>0.19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.008101030175229612</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C21" t="n">
-        <v>0.372264618198882</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2224967607340952</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E21" t="n">
-        <v>4.71491443703055</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F21" t="n">
-        <v>0.205598091946034</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G21" t="n">
-        <v>0.04326580317235378</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="B22" t="n">
-        <v>0.008939082509253468</v>
+        <v>0.06843130419263244</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3893419524015466</v>
+        <v>0.3234119355523905</v>
       </c>
       <c r="D22" t="n">
-        <v>0.217777753074012</v>
+        <v>0.1641512027920073</v>
       </c>
       <c r="E22" t="n">
-        <v>4.642153320345336</v>
+        <v>6.086974999998803</v>
       </c>
       <c r="F22" t="n">
-        <v>0.09828399966654283</v>
+        <v>0.3417922806996451</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02101495303486722</v>
+        <v>0.1211473581035549</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.009865974313315189</v>
+        <v>0.06194200004136102</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4076467843509159</v>
+        <v>0.3234343918779719</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2126749737337219</v>
+        <v>0.1712381888386632</v>
       </c>
       <c r="E23" t="n">
-        <v>4.572586113244171</v>
+        <v>6.017556306967998</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.02029103181315667</v>
+        <v>0.3584596312995524</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.002478438071360778</v>
+        <v>0.1210702835678767</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.42</v>
+        <v>0.22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.01084616979939963</v>
+        <v>0.05558782984306992</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4265777884173634</v>
+        <v>0.3235014900593278</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2074087604996193</v>
+        <v>0.1782108916150856</v>
       </c>
       <c r="E24" t="n">
-        <v>4.505904837702301</v>
+        <v>5.947964636448914</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1456008361944354</v>
+        <v>0.3729081903774435</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.02650605850132806</v>
+        <v>0.1208411833679875</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.43</v>
+        <v>0.23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.01184413317949164</v>
+        <v>0.04941509542228786</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4455336389712624</v>
+        <v>0.3236128239033751</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2021810349777272</v>
+        <v>0.185015835589639</v>
       </c>
       <c r="E25" t="n">
-        <v>4.44180151569497</v>
+        <v>5.878239336939206</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2731192471786643</v>
+        <v>0.385296443042034</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.05035959661003257</v>
+        <v>0.1204632426146051</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.44</v>
+        <v>0.24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01282432866557608</v>
+        <v>0.04347009860354354</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4639130103829858</v>
+        <v>0.3237679872170314</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1971746704610571</v>
+        <v>0.1915969454965895</v>
       </c>
       <c r="E26" t="n">
-        <v>4.379968169197426</v>
+        <v>5.808418835620682</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3983200984672141</v>
+        <v>0.395782874402039</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0733307407524721</v>
+        <v>0.1199396464184474</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01375122046963779</v>
+        <v>0.03779914121136559</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4811145770229074</v>
+        <v>0.3239665738072138</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1925546446748821</v>
+        <v>0.1978961121750373</v>
       </c>
       <c r="E27" t="n">
-        <v>4.32009682018491</v>
+        <v>5.738540623228458</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.5166772237614566</v>
+        <v>0.4045259695661743</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0947111792836447</v>
+        <v>0.1192735798902323</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.01458927280366165</v>
+        <v>0.03244852507028274</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4965370132614001</v>
+        <v>0.3242081774808396</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1884706892941055</v>
+        <v>0.2038538532671034</v>
       </c>
       <c r="E28" t="n">
-        <v>4.261879490632669</v>
+        <v>5.668641240786578</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.6236644567627627</v>
+        <v>0.4116842136431551</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.1137926005585482</v>
+        <v>0.1184682281406777</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0153029498796325</v>
+        <v>0.02746455200482366</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5095789934688372</v>
+        <v>0.3244923920448258</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1850611948124135</v>
+        <v>0.2094100639601341</v>
       </c>
       <c r="E29" t="n">
-        <v>4.205008202515948</v>
+        <v>5.598756268164601</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.7147556311725025</v>
+        <v>0.4174160917416969</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.1298666929321806</v>
+        <v>0.1175267762805015</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.48</v>
+        <v>0.28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01585671590953518</v>
+        <v>0.02289352383951705</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5196391920155921</v>
+        <v>0.32481881130609</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1824582081114278</v>
+        <v>0.214504849886401</v>
       </c>
       <c r="E30" t="n">
-        <v>4.149174977809992</v>
+        <v>5.528920314407586</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7854245806920486</v>
+        <v>0.4218800889705152</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1422251447595396</v>
+        <v>0.1164524094204215</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.49</v>
+        <v>0.29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.01621503510535457</v>
+        <v>0.0187817423988916</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5261162832720379</v>
+        <v>0.3251870290715492</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1807934647747625</v>
+        <v>0.2190794310898651</v>
       </c>
       <c r="E31" t="n">
-        <v>4.094071838490045</v>
+        <v>5.459167009790085</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8311451390227695</v>
+        <v>0.4252346904383254</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1501596443956231</v>
+        <v>0.1152483126711556</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="B32" t="n">
-        <v>0.01634237167907551</v>
+        <v>0.01517550950747595</v>
       </c>
       <c r="C32" t="n">
-        <v>0.528408941608548</v>
+        <v>0.3255966391481207</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1802055269612738</v>
+        <v>0.2230771027359011</v>
       </c>
       <c r="E32" t="n">
-        <v>4.039390806531354</v>
+        <v>5.389528999543075</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8473911398660394</v>
+        <v>0.427638381253843</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1529618801954292</v>
+        <v>0.1139176711434218</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.0162946423322595</v>
+        <v>0.01212112698979884</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5275427073397032</v>
+        <v>0.3260472353427218</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1808509440993696</v>
+        <v>0.2264442350952729</v>
       </c>
       <c r="E33" t="n">
-        <v>3.98495921905333</v>
+        <v>5.320037939201277</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8452224545634464</v>
+        <v>0.4292496465257832</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.152939686886667</v>
+        <v>0.1124636699479378</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.52</v>
+        <v>0.32</v>
       </c>
       <c r="B34" t="n">
-        <v>0.01615654286864298</v>
+        <v>0.009664896670388919</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5250389343160562</v>
+        <v>0.3265384114622697</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1827303195802273</v>
+        <v>0.2291312924095358</v>
       </c>
       <c r="E34" t="n">
-        <v>3.930851557868982</v>
+        <v>5.250724491517142</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8389106477735785</v>
+        <v>0.4302269713628618</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.1528743935630462</v>
+        <v>0.1108894941954217</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="B35" t="n">
-        <v>0.01593570615347324</v>
+        <v>0.007853120373774884</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5210400172119373</v>
+        <v>0.3270697613136817</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1857741688741759</v>
+        <v>0.2310938476809276</v>
       </c>
       <c r="E35" t="n">
-        <v>3.877130561993947</v>
+        <v>5.181618324886614</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8287470931733026</v>
+        <v>0.4307288408737939</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1527679301285654</v>
+        <v>0.1091983289965913</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.54</v>
+        <v>0.34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.01563976505199756</v>
+        <v>0.006732099924485431</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5156883507016774</v>
+        <v>0.3276408787038749</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1899295939165543</v>
+        <v>0.2322935683675515</v>
       </c>
       <c r="E36" t="n">
-        <v>3.823858970443865</v>
+        <v>5.112748113230937</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8150231644394859</v>
+        <v>0.4309137401672954</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.152622226487223</v>
+        <v>0.1073933594621644</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.0152763524294632</v>
+        <v>0.006348137147049251</v>
       </c>
       <c r="C37" t="n">
-        <v>0.509126329459607</v>
+        <v>0.3282513574397667</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1951552645891703</v>
+        <v>0.232699146541859</v>
       </c>
       <c r="E37" t="n">
-        <v>3.771099522234373</v>
+        <v>5.044141537278102</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.798030235248995</v>
+        <v>0.4309401543520813</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.1524392125430176</v>
+        <v>0.105477770702859</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.01485310115111746</v>
+        <v>0.006475463197829962</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5014963481600567</v>
+        <v>0.3313504208206851</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2014169160532863</v>
+        <v>0.2319424317808924</v>
       </c>
       <c r="E38" t="n">
-        <v>3.718914956381107</v>
+        <v>4.975068224708271</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.7780596792786969</v>
+        <v>0.4146589360725742</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.1522208181999478</v>
+        <v>0.1004693174817961</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.5700000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.0143776440822076</v>
+        <v>0.00683375278258499</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4929408014773573</v>
+        <v>0.3389242996538605</v>
       </c>
       <c r="D39" t="n">
-        <v>0.208683144025425</v>
+        <v>0.2298262504957758</v>
       </c>
       <c r="E39" t="n">
-        <v>3.667368011899708</v>
+        <v>4.905016576355599</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.7554028702054586</v>
+        <v>0.3688443451000077</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.1519689733620122</v>
+        <v>0.08996117120614461</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.5800000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.01385761408798091</v>
+        <v>0.007387473049933668</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4836020840858394</v>
+        <v>0.3502780990080629</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2169213399615852</v>
+        <v>0.2265937021369939</v>
       </c>
       <c r="E40" t="n">
-        <v>3.616521427805812</v>
+        <v>4.834329878915568</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.730351181706147</v>
+        <v>0.2980399772333142</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1516856079332092</v>
+        <v>0.07481964195269435</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.5900000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.01330064403368468</v>
+        <v>0.008101091148495332</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4736225906598336</v>
+        <v>0.3647169239520627</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2260936596895782</v>
+        <v>0.2224946556626229</v>
       </c>
       <c r="E41" t="n">
-        <v>3.566437943115058</v>
+        <v>4.763335262682909</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.703195987457629</v>
+        <v>0.2067894282714256</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1513726518175375</v>
+        <v>0.05591103979823503</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="B42" t="n">
-        <v>0.01271436678456617</v>
+        <v>0.008939074226889322</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4631447158736705</v>
+        <v>0.3815458795546303</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2361529670181133</v>
+        <v>0.2177758137793875</v>
       </c>
       <c r="E42" t="n">
-        <v>3.517180296843082</v>
+        <v>4.692343374595903</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.6742286611367714</v>
+        <v>0.09963629401327433</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.1510320349189956</v>
+        <v>0.03410167481955639</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.6100000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.01210641520587266</v>
+        <v>0.009865889433734971</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4523108544016808</v>
+        <v>0.4000700708845356</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2470387416145174</v>
+        <v>0.2126732107102583</v>
       </c>
       <c r="E43" t="n">
-        <v>3.468811228005524</v>
+        <v>4.621648258772318</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.6437405764204414</v>
+        <v>-0.01887582974220739</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.150665687141582</v>
+        <v>0.01025785709344822</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.62</v>
+        <v>0.42</v>
       </c>
       <c r="B44" t="n">
-        <v>0.01148442216285144</v>
+        <v>0.01084600391765161</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4412634009181954</v>
+        <v>0.419594603010549</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2586729901556082</v>
+        <v>0.2074071760610749</v>
       </c>
       <c r="E44" t="n">
-        <v>3.421393475618021</v>
+        <v>4.551527427703703</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.612023106985506</v>
+        <v>-0.1442033471960867</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.1502755383892954</v>
+        <v>-0.01475410330329963</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.63</v>
+        <v>0.43</v>
       </c>
       <c r="B45" t="n">
-        <v>0.01085602052074978</v>
+        <v>0.01184388482725858</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4301447500975444</v>
+        <v>0.4394245810014409</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2709562524242994</v>
+        <v>0.202179624387567</v>
       </c>
       <c r="E45" t="n">
-        <v>3.374989778696211</v>
+        <v>4.482242107197539</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.5793676265088316</v>
+        <v>-0.271802662549433</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.1498635185661342</v>
+        <v>-0.04006789629389772</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.64</v>
+        <v>0.44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.01022884314481496</v>
+        <v>0.01282399931117523</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4190972966140588</v>
+        <v>0.4588651099259815</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2837638493956167</v>
+        <v>0.1971734230713405</v>
       </c>
       <c r="E46" t="n">
-        <v>3.329662876255732</v>
+        <v>4.414037638394363</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.5460655086672853</v>
+        <v>-0.397130180003313</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.149431557576097</v>
+        <v>-0.06481721180155607</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="B47" t="n">
-        <v>0.009610522900294263</v>
+        <v>0.01375081451802088</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4082634351420691</v>
+        <v>0.477221294852941</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2969425767747055</v>
+        <v>0.1925535449670908</v>
       </c>
       <c r="E47" t="n">
-        <v>3.285475507312221</v>
+        <v>4.347144020700727</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.5124081271377342</v>
+        <v>-0.5156423037587948</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.1489815853231823</v>
+        <v>-0.08813573974948505</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="B48" t="n">
-        <v>0.009008692652434962</v>
+        <v>0.01458879759641486</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3977855603559061</v>
+        <v>0.4937982408510898</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3103081017138736</v>
+        <v>0.1884697177396452</v>
       </c>
       <c r="E48" t="n">
-        <v>3.242490410881318</v>
+        <v>4.281776580230439</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.4786868555970449</v>
+        <v>-0.622795438016946</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.1485155317113888</v>
+        <v>-0.1091571700608949</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="B49" t="n">
-        <v>0.008430985266484338</v>
+        <v>0.01530241569497653</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3878060669299003</v>
+        <v>0.507901052989198</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3236433677183853</v>
+        <v>0.1850603284903388</v>
       </c>
       <c r="E49" t="n">
-        <v>3.200770325978658</v>
+        <v>4.218136749300403</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.4451930677220849</v>
+        <v>-0.7140459869788343</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.1480353266447149</v>
+        <v>-0.1270151926589957</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="B50" t="n">
-        <v>0.007885033607689676</v>
+        <v>0.01585613596232521</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3784673495383825</v>
+        <v>0.5188348363360358</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3366983466614017</v>
+        <v>0.1824574210337424</v>
       </c>
       <c r="E50" t="n">
-        <v>3.160377991619881</v>
+        <v>4.156412943649889</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.4122181371897209</v>
+        <v>-0.7848503548455275</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.1475429000271593</v>
+        <v>-0.1408434974669979</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="B51" t="n">
-        <v>0.007378470541298242</v>
+        <v>0.01621442554708022</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3699118028556831</v>
+        <v>0.5259046959603737</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3491914896964313</v>
+        <v>0.180792727873644</v>
       </c>
       <c r="E51" t="n">
-        <v>3.121376146820624</v>
+        <v>4.096781525313461</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.3800534376768194</v>
+        <v>-0.8306649458180937</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.1470401817627204</v>
+        <v>-0.1497757744081117</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="B52" t="n">
-        <v>0.006918928932557326</v>
+        <v>0.01634175159786094</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3622818215561329</v>
+        <v>0.5284157369309818</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3608132123049669</v>
+        <v>0.1802048076861808</v>
       </c>
       <c r="E52" t="n">
-        <v>3.083827530596526</v>
+        <v>4.039407840451303</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.3489903428602475</v>
+        <v>-0.846946164097601</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.1465291017553969</v>
+        <v>-0.1529457134055473</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="B53" t="n">
-        <v>0.006514041646714194</v>
+        <v>0.01629402920999484</v>
       </c>
       <c r="C53" t="n">
-        <v>0.3557198003140625</v>
+        <v>0.5275496181637128</v>
       </c>
       <c r="D53" t="n">
-        <v>0.371231694585772</v>
+        <v>0.1808501354758607</v>
       </c>
       <c r="E53" t="n">
-        <v>3.047794881963223</v>
+        <v>3.983434592331665</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3193202264168721</v>
+        <v>-0.8447775270151444</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.1460115899091873</v>
+        <v>-0.1529228551942183</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.72</v>
+        <v>0.52</v>
       </c>
       <c r="B54" t="n">
-        <v>0.006171441549016141</v>
+        <v>0.01615594978468268</v>
       </c>
       <c r="C54" t="n">
-        <v>0.3503681338038024</v>
+        <v>0.5250461789870863</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3801011795032067</v>
+        <v>0.1827292510871348</v>
       </c>
       <c r="E54" t="n">
-        <v>3.013340939936354</v>
+        <v>3.927953886069143</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2913344620235604</v>
+        <v>-0.8384658890002338</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.14548957612809</v>
+        <v>-0.1528556204932251</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="B55" t="n">
-        <v>0.005898761504710437</v>
+        <v>0.01593514492935367</v>
       </c>
       <c r="C55" t="n">
-        <v>0.3463692166996836</v>
+        <v>0.5210477950888722</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3870728055347544</v>
+        <v>0.1857726780286748</v>
       </c>
       <c r="E55" t="n">
-        <v>2.980528443531557</v>
+        <v>3.873044149963679</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2653244233571793</v>
+        <v>-0.8283026599015577</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.1449649903161038</v>
+        <v>-0.152746019202058</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.74</v>
+        <v>0.54</v>
       </c>
       <c r="B56" t="n">
-        <v>0.005703634379044357</v>
+        <v>0.01563924625143701</v>
       </c>
       <c r="C56" t="n">
-        <v>0.3438654436760365</v>
+        <v>0.515696842156841</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3918078171176564</v>
+        <v>0.1899275219081908</v>
       </c>
       <c r="E56" t="n">
-        <v>2.94942013176447</v>
+        <v>3.818779347263714</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2415814840945955</v>
+        <v>-0.8145792495678048</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.1444397623772271</v>
+        <v>-0.1525960612202077</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="B57" t="n">
-        <v>0.005593693037265187</v>
+        <v>0.01527588535836191</v>
       </c>
       <c r="C57" t="n">
-        <v>0.3429992094071918</v>
+        <v>0.5091356958787627</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3939927639831015</v>
+        <v>0.1951524532917523</v>
       </c>
       <c r="E57" t="n">
-        <v>2.920078743650731</v>
+        <v>3.765229098407041</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2203970179126757</v>
+        <v>-0.7975870678476633</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.1439158222154585</v>
+        <v>-0.1524077564471647</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B58" t="n">
-        <v>0.005529743629648109</v>
+        <v>0.01485269385755759</v>
       </c>
       <c r="C58" t="n">
-        <v>0.343104541962123</v>
+        <v>0.5015067319424077</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3947858979570568</v>
+        <v>0.2014132062655495</v>
       </c>
       <c r="E58" t="n">
-        <v>2.891545047302296</v>
+        <v>3.712458816485165</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.2003559711591471</v>
+        <v>-0.7776175245898221</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.1433845817729934</v>
+        <v>-0.1521831147824194</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.77</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B59" t="n">
-        <v>0.005467509245747987</v>
+        <v>0.01437730335645325</v>
       </c>
       <c r="C59" t="n">
-        <v>0.3434124863293022</v>
+        <v>0.4929523260355462</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3955363161429449</v>
+        <v>0.208678374879887</v>
       </c>
       <c r="E59" t="n">
-        <v>2.862857047043099</v>
+        <v>3.660529854457421</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.1798891121007686</v>
+        <v>-0.7549620296429698</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.1428354428538349</v>
+        <v>-0.1519241461254625</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.78</v>
+        <v>0.58</v>
       </c>
       <c r="B60" t="n">
-        <v>0.005406998159731621</v>
+        <v>0.0138573454624781</v>
       </c>
       <c r="C60" t="n">
-        <v>0.3439109625623075</v>
+        <v>0.4836148538459485</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3962456879301783</v>
+        <v>0.2169153495047728</v>
       </c>
       <c r="E60" t="n">
-        <v>2.834073336206751</v>
+        <v>3.609499662719437</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.1590565472929554</v>
+        <v>-0.729911992855795</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.142267320154693</v>
+        <v>-0.1516328603757844</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.79</v>
+        <v>0.59</v>
       </c>
       <c r="B61" t="n">
-        <v>0.00534821864576581</v>
+        <v>0.01330045178306135</v>
       </c>
       <c r="C61" t="n">
-        <v>0.3445878907147172</v>
+        <v>0.4736366910613846</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3969157096226718</v>
+        <v>0.226086286679361</v>
       </c>
       <c r="E61" t="n">
-        <v>2.805252508126857</v>
+        <v>3.559421955714008</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.1379183832911231</v>
+        <v>-0.7027588240769859</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.1416791283722779</v>
+        <v>-0.1513112674328757</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="B62" t="n">
-        <v>0.005291178978017351</v>
+        <v>0.0127142539256322</v>
       </c>
       <c r="C62" t="n">
-        <v>0.3454311908401098</v>
+        <v>0.463160213369625</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3975481026069751</v>
+        <v>0.2361440540061119</v>
       </c>
       <c r="E62" t="n">
-        <v>2.776453156137026</v>
+        <v>3.510346886359989</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.1165347266506869</v>
+        <v>-0.6737939331552312</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.1410697822032996</v>
+        <v>-0.1509613771962267</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="B63" t="n">
-        <v>0.005235887430653046</v>
+        <v>0.01210638349761987</v>
       </c>
       <c r="C63" t="n">
-        <v>0.3464287829920633</v>
+        <v>0.4523277964584397</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3981446115871652</v>
+        <v>0.247028139382536</v>
       </c>
       <c r="E63" t="n">
-        <v>2.747733873570865</v>
+        <v>3.462321227165353</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.09496568392706227</v>
+        <v>-0.6433087299392195</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.1404381963444682</v>
+        <v>-0.1505851995653282</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.8200000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="B64" t="n">
-        <v>0.005182352277839693</v>
+        <v>0.01148447210645356</v>
       </c>
       <c r="C64" t="n">
-        <v>0.3475685872241561</v>
+        <v>0.4412818160155991</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3987070028894285</v>
+        <v>0.258660563552623</v>
       </c>
       <c r="E64" t="n">
-        <v>2.719153253761984</v>
+        <v>3.415388556983475</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.07327136167566457</v>
+        <v>-0.6115946242776393</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.1397832854924937</v>
+        <v>-0.1501847444396705</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.8300000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="B65" t="n">
-        <v>0.005130581793744091</v>
+        <v>0.01085615135956247</v>
       </c>
       <c r="C65" t="n">
-        <v>0.3488385235899664</v>
+        <v>0.4301646477288734</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3992370628390471</v>
+        <v>0.2709418876020805</v>
       </c>
       <c r="E65" t="n">
-        <v>2.690769890043988</v>
+        <v>3.369589452466053</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.05151186645190917</v>
+        <v>-0.5789430260191796</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.1391039643440863</v>
+        <v>-0.1497620217187443</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.8400000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="B66" t="n">
-        <v>0.00508058425253304</v>
+        <v>0.01022905286437583</v>
       </c>
       <c r="C66" t="n">
-        <v>0.3502265121430724</v>
+        <v>0.4191186672860329</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3997365962122919</v>
+        <v>0.2837474623642343</v>
       </c>
       <c r="E66" t="n">
-        <v>2.662642375750486</v>
+        <v>3.324961683361264</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.02974730481121145</v>
+        <v>-0.5456453450125285</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.138399147595956</v>
+        <v>-0.14931904130204</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.8500000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="B67" t="n">
-        <v>0.005032367928373337</v>
+        <v>0.009610808228322835</v>
       </c>
       <c r="C67" t="n">
-        <v>0.3517204729370526</v>
+        <v>0.4082862503748476</v>
       </c>
       <c r="D67" t="n">
-        <v>0.4002074247655201</v>
+        <v>0.2969241230928379</v>
       </c>
       <c r="E67" t="n">
-        <v>2.634829304215085</v>
+        <v>3.28154041090125</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.008037783308986758</v>
+        <v>-0.5119929911063745</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.1376677499448129</v>
+        <v>-0.1488578130890481</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.8600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="B68" t="n">
-        <v>0.004985941095431782</v>
+        <v>0.009009049058832694</v>
       </c>
       <c r="C68" t="n">
-        <v>0.3533083260254851</v>
+        <v>0.397809772683088</v>
       </c>
       <c r="D68" t="n">
-        <v>0.4006513858435796</v>
+        <v>0.3102875869941846</v>
       </c>
       <c r="E68" t="n">
-        <v>2.607389268771393</v>
+        <v>3.239358388618386</v>
       </c>
       <c r="F68" t="n">
-        <v>0.01355659149934947</v>
+        <v>-0.4782773741494065</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.1369086860873671</v>
+        <v>-0.1483803469792593</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.8700000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="B69" t="n">
-        <v>0.004941312027875176</v>
+        <v>0.008431406963334619</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3549779914619481</v>
+        <v>0.3878316098985242</v>
       </c>
       <c r="D69" t="n">
-        <v>0.4010703310694382</v>
+        <v>0.323620858469841</v>
       </c>
       <c r="E69" t="n">
-        <v>2.580380862753019</v>
+        <v>3.198446165024459</v>
       </c>
       <c r="F69" t="n">
-        <v>0.03497571305838188</v>
+        <v>-0.444789903990313</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.1361208707203286</v>
+        <v>-0.1478886528721639</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.8800000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="B70" t="n">
-        <v>0.004898488999870315</v>
+        <v>0.007885513549257813</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3567173893000201</v>
+        <v>0.3784941377089264</v>
       </c>
       <c r="D70" t="n">
-        <v>0.4014661251167756</v>
+        <v>0.3366739808173507</v>
       </c>
       <c r="E70" t="n">
-        <v>2.553862679493569</v>
+        <v>3.158832287680822</v>
       </c>
       <c r="F70" t="n">
-        <v>0.05615947481269511</v>
+        <v>-0.4118219904777823</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.1353032185404075</v>
+        <v>-0.1473847406672525</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.8900000000000001</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B71" t="n">
-        <v>0.004857480285584</v>
+        <v>0.007379000424031491</v>
       </c>
       <c r="C71" t="n">
-        <v>0.3585144395932791</v>
+        <v>0.3699397318020649</v>
       </c>
       <c r="D71" t="n">
-        <v>0.4018406445671139</v>
+        <v>0.3491654860039504</v>
       </c>
       <c r="E71" t="n">
-        <v>2.527893312326651</v>
+        <v>3.120543508280449</v>
       </c>
       <c r="F71" t="n">
-        <v>0.07704777020687377</v>
+        <v>-0.3796650434605034</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.1344546442443139</v>
+        <v>-0.1468706202640156</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B72" t="n">
-        <v>0.00481829415918303</v>
+        <v>0.006919499195084857</v>
       </c>
       <c r="C72" t="n">
-        <v>0.3603570623953036</v>
+        <v>0.3623107678657099</v>
       </c>
       <c r="D72" t="n">
-        <v>0.4021957768529001</v>
+        <v>0.3607858775973937</v>
       </c>
       <c r="E72" t="n">
-        <v>2.502531354585874</v>
+        <v>3.083604988454459</v>
       </c>
       <c r="F72" t="n">
-        <v>0.09758049268550249</v>
+        <v>-0.3486104727871644</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.1335740625287578</v>
+        <v>-0.1463483015619438</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.9099999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="B73" t="n">
-        <v>0.004780938894834204</v>
+        <v>0.006514641469847125</v>
       </c>
       <c r="C73" t="n">
-        <v>0.3622331777596716</v>
+        <v>0.3557496215876317</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4025334192878143</v>
+        <v>0.3712034278516116</v>
       </c>
       <c r="E73" t="n">
-        <v>2.477835399604845</v>
+        <v>3.04804050610615</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1176975356931654</v>
+        <v>-0.3189496883064545</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.1326603880904494</v>
+        <v>-0.1458197944605275</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="B74" t="n">
-        <v>0.004745422766704322</v>
+        <v>0.006172058855747491</v>
       </c>
       <c r="C74" t="n">
-        <v>0.3641307057399616</v>
+        <v>0.3503986686556004</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4028554781854371</v>
+        <v>0.3800724716293759</v>
       </c>
       <c r="E74" t="n">
-        <v>2.453864040717171</v>
+        <v>3.01387266216492</v>
       </c>
       <c r="F74" t="n">
-        <v>0.1373387926744481</v>
+        <v>-0.2909740998670615</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.1317125356260987</v>
+        <v>-0.1452871088592573</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.9299999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="B75" t="n">
-        <v>0.00471175404896018</v>
+        <v>0.005899382960215178</v>
       </c>
       <c r="C75" t="n">
-        <v>0.3660375663897519</v>
+        <v>0.3464002847573864</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4031638680672905</v>
+        <v>0.3870442336697051</v>
       </c>
       <c r="E75" t="n">
-        <v>2.430675871256461</v>
+        <v>2.981123087740674</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1564441570739347</v>
+        <v>-0.2649751173176745</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.1307294198324158</v>
+        <v>-0.1447522546576237</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="B76" t="n">
-        <v>0.004679941015768581</v>
+        <v>0.005704245390679381</v>
       </c>
       <c r="C76" t="n">
-        <v>0.3679416797626206</v>
+        <v>0.3438968455807598</v>
       </c>
       <c r="D76" t="n">
-        <v>0.403460510961152</v>
+        <v>0.3917800327960871</v>
       </c>
       <c r="E76" t="n">
-        <v>2.408329484556321</v>
+        <v>2.949812651746727</v>
       </c>
       <c r="F76" t="n">
-        <v>0.17495352233621</v>
+        <v>-0.2412441505069816</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.1297099554061108</v>
+        <v>-0.1442172417551172</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="B77" t="n">
-        <v>0.004649991941296321</v>
+        <v>0.005594277754569317</v>
       </c>
       <c r="C77" t="n">
-        <v>0.369830965912146</v>
+        <v>0.3430307268134909</v>
       </c>
       <c r="D77" t="n">
-        <v>0.4037473357904421</v>
+        <v>0.3939664744956399</v>
       </c>
       <c r="E77" t="n">
-        <v>2.38688347395036</v>
+        <v>2.919961669146067</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1928067819058583</v>
+        <v>-0.2200726092836718</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.1286530570438937</v>
+        <v>-0.1436840800512284</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.96</v>
+        <v>0.76</v>
       </c>
       <c r="B78" t="n">
-        <v>0.004621915099710201</v>
+        <v>0.005530294008671035</v>
       </c>
       <c r="C78" t="n">
-        <v>0.3716933448919064</v>
+        <v>0.3431359492376275</v>
       </c>
       <c r="D78" t="n">
-        <v>0.4040262778553991</v>
+        <v>0.3947614332800109</v>
       </c>
       <c r="E78" t="n">
-        <v>2.366396432772186</v>
+        <v>2.890690581063597</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2099438292274645</v>
+        <v>-0.2000456005723377</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.1275576394424746</v>
+        <v>-0.1431445978544154</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.97</v>
+        <v>0.77</v>
       </c>
       <c r="B79" t="n">
-        <v>0.004595718765177018</v>
+        <v>0.005468025902685943</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3735167367554801</v>
+        <v>0.3434435721253895</v>
       </c>
       <c r="D79" t="n">
-        <v>0.4042992784066758</v>
+        <v>0.3955136047318228</v>
       </c>
       <c r="E79" t="n">
-        <v>2.346926954355407</v>
+        <v>2.861171507861118</v>
       </c>
       <c r="F79" t="n">
-        <v>0.226304557745613</v>
+        <v>-0.1795939656930404</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.1264226172985636</v>
+        <v>-0.142588525258046</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.98</v>
+        <v>0.78</v>
       </c>
       <c r="B80" t="n">
-        <v>0.004571411211863575</v>
+        <v>0.005407481733416278</v>
       </c>
       <c r="C80" t="n">
-        <v>0.3752890615564453</v>
+        <v>0.3439415288998046</v>
       </c>
       <c r="D80" t="n">
-        <v>0.4045682843119314</v>
+        <v>0.3962246596807349</v>
       </c>
       <c r="E80" t="n">
-        <v>2.328533632033629</v>
+        <v>2.831499450258968</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2418288609048885</v>
+        <v>-0.158777716087671</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.1252469053088708</v>
+        <v>-0.1420147248389748</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.99</v>
+        <v>0.79</v>
       </c>
       <c r="B81" t="n">
-        <v>0.004549000713936666</v>
+        <v>0.005348669797664278</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3769982393483803</v>
+        <v>0.3446177529839006</v>
       </c>
       <c r="D81" t="n">
-        <v>0.4048352478159409</v>
+        <v>0.3968962959675703</v>
       </c>
       <c r="E81" t="n">
-        <v>2.311275059140462</v>
+        <v>2.801765969547256</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2564566321498757</v>
+        <v>-0.1376568631981206</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.1240294181701062</v>
+        <v>-0.1414220591740564</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="B82" t="n">
-        <v>0.004528495545563095</v>
+        <v>0.005291598392232183</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3786321901848634</v>
+        <v>0.3454601778007056</v>
       </c>
       <c r="D82" t="n">
-        <v>0.4051021263947031</v>
+        <v>0.3975302366071693</v>
       </c>
       <c r="E82" t="n">
-        <v>2.295209829009511</v>
+        <v>2.772059151482525</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2701277649251593</v>
+        <v>-0.1162914184662802</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.1227690705789799</v>
+        <v>-0.1408093908401455</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1.01</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B83" t="n">
-        <v>0.004509903980909658</v>
+        <v>0.005236275813922228</v>
       </c>
       <c r="C83" t="n">
-        <v>0.3801788341194728</v>
+        <v>0.3464567367732473</v>
       </c>
       <c r="D83" t="n">
-        <v>0.4053708827040051</v>
+        <v>0.3981282280181004</v>
       </c>
       <c r="E83" t="n">
-        <v>2.280396534974385</v>
+        <v>2.742463598506272</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2827821526753237</v>
+        <v>-0.09474139333404107</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.1214647772322021</v>
+        <v>-0.1401755824140968</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1.02</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B84" t="n">
-        <v>0.004493234294143156</v>
+        <v>0.005182710359536653</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3816260912057868</v>
+        <v>0.3475953633245536</v>
       </c>
       <c r="D84" t="n">
-        <v>0.4056434846228859</v>
+        <v>0.3986920383221769</v>
       </c>
       <c r="E84" t="n">
-        <v>2.266893770368694</v>
+        <v>2.713060448504777</v>
       </c>
       <c r="F84" t="n">
-        <v>0.2943596888449537</v>
+        <v>-0.07306679924329411</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.1201154528264827</v>
+        <v>-0.1395194964727649</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1.03</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B85" t="n">
-        <v>0.004478494759430385</v>
+        <v>0.005130910325877698</v>
       </c>
       <c r="C85" t="n">
-        <v>0.3829618814973836</v>
+        <v>0.3488639908776525</v>
       </c>
       <c r="D85" t="n">
-        <v>0.4059219053924419</v>
+        <v>0.3992234557165049</v>
       </c>
       <c r="E85" t="n">
-        <v>2.254760128526042</v>
+        <v>2.683927418332532</v>
       </c>
       <c r="F85" t="n">
-        <v>0.3048002668786336</v>
+        <v>-0.05132764763593049</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.1187200120585318</v>
+        <v>-0.1388399955930045</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1.04</v>
+        <v>0.84</v>
       </c>
       <c r="B86" t="n">
-        <v>0.004465693650938149</v>
+        <v>0.005080884009747598</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3841741250478417</v>
+        <v>0.3502505528555717</v>
       </c>
       <c r="D86" t="n">
-        <v>0.40620812385043</v>
+        <v>0.3997242869205793</v>
       </c>
       <c r="E86" t="n">
-        <v>2.244054202780039</v>
+        <v>2.655138870346136</v>
       </c>
       <c r="F86" t="n">
-        <v>0.3140437802209486</v>
+        <v>-0.02958394995384149</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.1172773696250596</v>
+        <v>-0.1381359423516703</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1.05</v>
+        <v>0.85</v>
       </c>
       <c r="B87" t="n">
-        <v>0.004454839242833243</v>
+        <v>0.005032639707948591</v>
       </c>
       <c r="C87" t="n">
-        <v>0.385250741910739</v>
+        <v>0.3517429826813391</v>
       </c>
       <c r="D87" t="n">
-        <v>0.406504124762147</v>
+        <v>0.4001963557007354</v>
       </c>
       <c r="E87" t="n">
-        <v>2.234834586464292</v>
+        <v>2.626765900239749</v>
       </c>
       <c r="F87" t="n">
-        <v>0.3220301223164829</v>
+        <v>-0.007895717638917712</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.115786440222776</v>
+        <v>-0.1374061993256168</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="B88" t="n">
-        <v>0.004445939809282466</v>
+        <v>0.004986185717282918</v>
       </c>
       <c r="C88" t="n">
-        <v>0.386179652139654</v>
+        <v>0.3533292137779828</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4068118992481072</v>
+        <v>0.4006415014740712</v>
       </c>
       <c r="E88" t="n">
-        <v>2.227159872912409</v>
+        <v>2.598876444535204</v>
       </c>
       <c r="F88" t="n">
-        <v>0.3286991866098211</v>
+        <v>0.01367703786694948</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.1142461385483912</v>
+        <v>-0.1366496290916988</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1.07</v>
+        <v>0.87</v>
       </c>
       <c r="B89" t="n">
-        <v>0.00443900362445262</v>
+        <v>0.004941530334552814</v>
       </c>
       <c r="C89" t="n">
-        <v>0.386948775788165</v>
+        <v>0.3549971795685303</v>
       </c>
       <c r="D89" t="n">
-        <v>0.407133445309085</v>
+        <v>0.4010615779937677</v>
       </c>
       <c r="E89" t="n">
-        <v>2.221088655457998</v>
+        <v>2.57153540615752</v>
       </c>
       <c r="F89" t="n">
-        <v>0.3339908665455479</v>
+        <v>0.03507430512186903</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.1126553792986153</v>
+        <v>-0.135865094226771</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1.08</v>
+        <v>0.88</v>
       </c>
       <c r="B90" t="n">
-        <v>0.004434038962510502</v>
+        <v>0.004898681856560517</v>
       </c>
       <c r="C90" t="n">
-        <v>0.3875460329098502</v>
+        <v>0.3567348134760098</v>
       </c>
       <c r="D90" t="n">
-        <v>0.4074707684491622</v>
+        <v>0.4014584521175553</v>
       </c>
       <c r="E90" t="n">
-        <v>2.216679527434666</v>
+        <v>2.544804796618272</v>
       </c>
       <c r="F90" t="n">
-        <v>0.3378450555682481</v>
+        <v>0.05623607268394985</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.1110130771701583</v>
+        <v>-0.1350514573076879</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1.09</v>
+        <v>0.89</v>
       </c>
       <c r="B91" t="n">
-        <v>0.004431054097622912</v>
+        <v>0.00485764858010827</v>
       </c>
       <c r="C91" t="n">
-        <v>0.3879593435582878</v>
+        <v>0.358530048923449</v>
       </c>
       <c r="D91" t="n">
-        <v>0.4078258823974898</v>
+        <v>0.4018340026609079</v>
       </c>
       <c r="E91" t="n">
-        <v>2.213991082176021</v>
+        <v>2.5187438934332</v>
       </c>
       <c r="F91" t="n">
-        <v>0.3402016471225061</v>
+        <v>0.07710232911130084</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.1093181468597303</v>
+        <v>-0.1342075809113042</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="B92" t="n">
-        <v>0.004430057303956649</v>
+        <v>0.004818438801998305</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3881766277870562</v>
+        <v>0.3603708193338758</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4082008099295733</v>
+        <v>0.4021901193363907</v>
       </c>
       <c r="E92" t="n">
-        <v>2.213081913015671</v>
+        <v>2.493409411515086</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3410005346529067</v>
+        <v>0.09761306296203098</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.1075695030640413</v>
+        <v>-0.1333323276144746</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="B93" t="n">
-        <v>0.004430266793030347</v>
+        <v>0.004781060819032863</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3882906783363895</v>
+        <v>0.3622450581303182</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4085811812093132</v>
+        <v>0.4025287017804377</v>
       </c>
       <c r="E93" t="n">
-        <v>2.213347896667924</v>
+        <v>2.468855687407029</v>
       </c>
       <c r="F93" t="n">
-        <v>0.3409603010668458</v>
+        <v>0.1177082627942491</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.1053413354733361</v>
+        <v>-0.1324245599940538</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1.12</v>
+        <v>0.92</v>
       </c>
       <c r="B94" t="n">
-        <v>0.004430883936517725</v>
+        <v>0.004745522928014183</v>
       </c>
       <c r="C94" t="n">
-        <v>0.3884023434807359</v>
+        <v>0.3641406987358038</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4089516441850401</v>
+        <v>0.4028516586687024</v>
       </c>
       <c r="E94" t="n">
-        <v>2.214131470129967</v>
+        <v>2.445134875353452</v>
       </c>
       <c r="F94" t="n">
-        <v>0.3408407081887339</v>
+        <v>0.1373279171660642</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.1022339661732606</v>
+        <v>-0.1314831406268963</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1.13</v>
+        <v>0.93</v>
       </c>
       <c r="B95" t="n">
-        <v>0.004431891748818216</v>
+        <v>0.004711833425744502</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3885116265749947</v>
+        <v>0.3660456745733608</v>
       </c>
       <c r="D95" t="n">
-        <v>0.4093127577701773</v>
+        <v>0.4031609069209997</v>
       </c>
       <c r="E95" t="n">
-        <v>2.215411067159726</v>
+        <v>2.422297154345634</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3406434178386761</v>
+        <v>0.1564120146355851</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.09828550845362707</v>
+        <v>-0.1305069320898569</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1.14</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B96" t="n">
-        <v>0.004433273244331247</v>
+        <v>0.004680000609026056</v>
       </c>
       <c r="C96" t="n">
-        <v>0.3886185309740655</v>
+        <v>0.3679479190660168</v>
       </c>
       <c r="D96" t="n">
-        <v>0.4096650836161547</v>
+        <v>0.4034583709967448</v>
       </c>
       <c r="E96" t="n">
-        <v>2.217165121515125</v>
+        <v>2.400390945424369</v>
       </c>
       <c r="F96" t="n">
-        <v>0.3403700918367785</v>
+        <v>0.1749005437609208</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.09353407560424765</v>
+        <v>-0.1294947969597903</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1.15</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B97" t="n">
-        <v>0.004435011437456249</v>
+        <v>0.004650032774661088</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3887230600328474</v>
+        <v>0.3698353656367999</v>
       </c>
       <c r="D97" t="n">
-        <v>0.4100091859852613</v>
+        <v>0.4037459822816957</v>
       </c>
       <c r="E97" t="n">
-        <v>2.219372066954091</v>
+        <v>2.379463138673986</v>
       </c>
       <c r="F97" t="n">
-        <v>0.3400223920031465</v>
+        <v>0.1927334931001803</v>
       </c>
       <c r="G97" t="n">
-        <v>-0.08801778091493447</v>
+        <v>-0.128445597813551</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1.16</v>
+        <v>0.96</v>
       </c>
       <c r="B98" t="n">
-        <v>0.004437089342592653</v>
+        <v>0.004621938219451832</v>
       </c>
       <c r="C98" t="n">
-        <v>0.3888252171062397</v>
+        <v>0.3716959477087378</v>
       </c>
       <c r="D98" t="n">
-        <v>0.410345631631168</v>
+        <v>0.4040256785667133</v>
       </c>
       <c r="E98" t="n">
-        <v>2.222010337234548</v>
+        <v>2.359559329498966</v>
       </c>
       <c r="F98" t="n">
-        <v>0.3396019801578858</v>
+        <v>0.2098508512114722</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.08177473767549985</v>
+        <v>-0.1273581972279938</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1.17</v>
+        <v>0.97</v>
       </c>
       <c r="B99" t="n">
-        <v>0.004439489974139888</v>
+        <v>0.004595725240200527</v>
       </c>
       <c r="C99" t="n">
-        <v>0.3889250055491421</v>
+        <v>0.3735175987048584</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4106749896871953</v>
+        <v>0.4042994036191819</v>
       </c>
       <c r="E99" t="n">
-        <v>2.225058366114422</v>
+        <v>2.340724063936661</v>
       </c>
       <c r="F99" t="n">
-        <v>0.339110518121102</v>
+        <v>0.2261926066529057</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.07484305917575569</v>
+        <v>-0.1262314577799732</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1.18</v>
+        <v>0.98</v>
       </c>
       <c r="B100" t="n">
-        <v>0.004442196346497384</v>
+        <v>0.004571402133709411</v>
       </c>
       <c r="C100" t="n">
-        <v>0.3890224287164536</v>
+        <v>0.3752882520481897</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4109978315623985</v>
+        <v>0.4045691068476651</v>
       </c>
       <c r="E100" t="n">
-        <v>2.228494587351639</v>
+        <v>2.32300109292717</v>
       </c>
       <c r="F100" t="n">
-        <v>0.3385496677129007</v>
+        <v>0.2416987479825898</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.06726085870551428</v>
+        <v>-0.125064242046344</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1.19</v>
+        <v>0.99</v>
       </c>
       <c r="B101" t="n">
-        <v>0.004445191474064571</v>
+        <v>0.004548977196780725</v>
       </c>
       <c r="C101" t="n">
-        <v>0.3891174899630736</v>
+        <v>0.3769958411617594</v>
       </c>
       <c r="D101" t="n">
-        <v>0.4113147308455377</v>
+        <v>0.4048367430603214</v>
       </c>
       <c r="E101" t="n">
-        <v>2.232297434704124</v>
+        <v>2.306433635634505</v>
       </c>
       <c r="F101" t="n">
-        <v>0.3379210907533877</v>
+        <v>0.2563092637586331</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.05906624955458775</v>
+        <v>-0.1238554126039608</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="B102" t="n">
-        <v>0.004448458371240878</v>
+        <v>0.004528458726216702</v>
       </c>
       <c r="C102" t="n">
-        <v>0.3892101926439016</v>
+        <v>0.3786282994685955</v>
       </c>
       <c r="D102" t="n">
-        <v>0.4116262632169995</v>
+        <v>0.4051042723175656</v>
       </c>
       <c r="E102" t="n">
-        <v>2.236445341929802</v>
+        <v>2.291064652092377</v>
       </c>
       <c r="F102" t="n">
-        <v>0.3372264490626684</v>
+        <v>0.2699641425391447</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.05029734501278831</v>
+        <v>-0.1226038320296783</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="B103" t="n">
-        <v>0.004451980052425738</v>
+        <v>0.004509855018819583</v>
       </c>
       <c r="C103" t="n">
-        <v>0.3893005401138369</v>
+        <v>0.3801735603917258</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4119330063687273</v>
+        <v>0.4053736598794344</v>
       </c>
       <c r="E103" t="n">
-        <v>2.240916742786598</v>
+        <v>2.276937125633977</v>
       </c>
       <c r="F103" t="n">
-        <v>0.3364674044608485</v>
+        <v>0.2826033728822337</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.04099225836992808</v>
+        <v>-0.1213083629003511</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="B104" t="n">
-        <v>0.004455739532018577</v>
+        <v>0.004493174371391608</v>
       </c>
       <c r="C104" t="n">
-        <v>0.3893885357277788</v>
+        <v>0.3816195573541783</v>
       </c>
       <c r="D104" t="n">
-        <v>0.4122355399322208</v>
+        <v>0.4056468762481032</v>
       </c>
       <c r="E104" t="n">
-        <v>2.24569007103244</v>
+        <v>2.264094355758975</v>
       </c>
       <c r="F104" t="n">
-        <v>0.3356456187680337</v>
+        <v>0.2941669433460087</v>
       </c>
       <c r="G104" t="n">
-        <v>-0.03118910291581924</v>
+        <v>-0.1199678677928338</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="B105" t="n">
-        <v>0.004459719824418827</v>
+        <v>0.004478425080735011</v>
       </c>
       <c r="C105" t="n">
-        <v>0.3894741828406265</v>
+        <v>0.3829542237789807</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4125344454146564</v>
+        <v>0.4059258973059972</v>
       </c>
       <c r="E105" t="n">
-        <v>2.25074376042525</v>
+        <v>2.252580262294003</v>
       </c>
       <c r="F105" t="n">
-        <v>0.3347627538043297</v>
+        <v>0.3045948424885786</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.02092599194027397</v>
+        <v>-0.1185812092839812</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="B106" t="n">
-        <v>0.004463903944025918</v>
+        <v>0.004465615443652033</v>
       </c>
       <c r="C106" t="n">
-        <v>0.3895574848072796</v>
+        <v>0.384165493089161</v>
       </c>
       <c r="D106" t="n">
-        <v>0.4128303061431813</v>
+        <v>0.4062127045499551</v>
       </c>
       <c r="E106" t="n">
-        <v>2.256056244722955</v>
+        <v>2.242439701916649</v>
       </c>
       <c r="F106" t="n">
-        <v>0.3338204713898419</v>
+        <v>0.3138270588680527</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.01024103873310439</v>
+        <v>-0.1171472499506479</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="B107" t="n">
-        <v>0.004468274905239279</v>
+        <v>0.004454753756944911</v>
       </c>
       <c r="C107" t="n">
-        <v>0.3896384449826374</v>
+        <v>0.385241298707747</v>
       </c>
       <c r="D107" t="n">
-        <v>0.4131237072174308</v>
+        <v>0.4065092854219283</v>
       </c>
       <c r="E107" t="n">
-        <v>2.261605957683481</v>
+        <v>2.233718798339357</v>
       </c>
       <c r="F107" t="n">
-        <v>0.3328204333446761</v>
+        <v>0.3218035810425395</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0008276434158773181</v>
+        <v>-0.1156648523696885</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="B108" t="n">
-        <v>0.004472815722458341</v>
+        <v>0.004445848317415884</v>
       </c>
       <c r="C108" t="n">
-        <v>0.3897170667215992</v>
+        <v>0.3861695740577666</v>
       </c>
       <c r="D108" t="n">
-        <v>0.4134152354703138</v>
+        <v>0.4068176337367354</v>
       </c>
       <c r="E108" t="n">
-        <v>2.267371333064753</v>
+        <v>2.226465287690786</v>
       </c>
       <c r="F108" t="n">
-        <v>0.3317643014889379</v>
+        <v>0.3284643975701482</v>
       </c>
       <c r="G108" t="n">
-        <v>0.01224194121685896</v>
+        <v>-0.1141328791179578</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="B109" t="n">
-        <v>0.004477509410082534</v>
+        <v>0.004438907421867189</v>
       </c>
       <c r="C109" t="n">
-        <v>0.3897933533790643</v>
+        <v>0.3869382525622478</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4137054794371151</v>
+        <v>0.4071397502074462</v>
       </c>
       <c r="E109" t="n">
-        <v>2.273330804624696</v>
+        <v>2.220728880890884</v>
       </c>
       <c r="F109" t="n">
-        <v>0.3306537376427329</v>
+        <v>0.3337494970089874</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02396374138002844</v>
+        <v>-0.1125501927723103</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="B110" t="n">
-        <v>0.004482338982511287</v>
+        <v>0.004433939367101064</v>
       </c>
       <c r="C110" t="n">
-        <v>0.389867308309932</v>
+        <v>0.3875352676442182</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4139950293329547</v>
+        <v>0.4074776430690309</v>
       </c>
       <c r="E110" t="n">
-        <v>2.279462806121236</v>
+        <v>2.216561645094948</v>
       </c>
       <c r="F110" t="n">
-        <v>0.3294904036261667</v>
+        <v>0.3375988679171665</v>
       </c>
       <c r="G110" t="n">
-        <v>0.03595493061557353</v>
+        <v>-0.1109156559096007</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="B111" t="n">
-        <v>0.004487287454144031</v>
+        <v>0.004430952449919747</v>
       </c>
       <c r="C111" t="n">
-        <v>0.3899389348691019</v>
+        <v>0.3879485527267059</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4142844770386507</v>
+        <v>0.4078333288009939</v>
       </c>
       <c r="E111" t="n">
-        <v>2.285745771312298</v>
+        <v>2.214018406584945</v>
       </c>
       <c r="F111" t="n">
-        <v>0.328275961259345</v>
+        <v>0.3399524988527939</v>
       </c>
       <c r="G111" t="n">
-        <v>0.04817739563368211</v>
+        <v>-0.1092281311066838</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="B112" t="n">
-        <v>0.004492337839380195</v>
+        <v>0.004429954967125478</v>
       </c>
       <c r="C112" t="n">
-        <v>0.3900082364114731</v>
+        <v>0.3881660412327387</v>
       </c>
       <c r="D112" t="n">
-        <v>0.4145744160950253</v>
+        <v>0.4082088329497971</v>
       </c>
       <c r="E112" t="n">
-        <v>2.292158133955806</v>
+        <v>2.213157177817227</v>
       </c>
       <c r="F112" t="n">
-        <v>0.3270120723623733</v>
+        <v>0.3407503783739789</v>
       </c>
       <c r="G112" t="n">
-        <v>0.06059302314454199</v>
+        <v>-0.107486480940414</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="B113" t="n">
-        <v>0.004497473152619209</v>
+        <v>0.00443015839563013</v>
       </c>
       <c r="C113" t="n">
-        <v>0.3900752162919451</v>
+        <v>0.3882804127124687</v>
       </c>
       <c r="D113" t="n">
-        <v>0.4148654417056966</v>
+        <v>0.4085897689152545</v>
       </c>
       <c r="E113" t="n">
-        <v>2.298678327809689</v>
+        <v>2.213410499788008</v>
       </c>
       <c r="F113" t="n">
-        <v>0.3257003987553575</v>
+        <v>0.3407100725085144</v>
       </c>
       <c r="G113" t="n">
-        <v>0.07316369985834109</v>
+        <v>-0.1052654076616029</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="B114" t="n">
-        <v>0.004502676408260503</v>
+        <v>0.0044307576850087</v>
       </c>
       <c r="C114" t="n">
-        <v>0.3901398778654171</v>
+        <v>0.388392393309642</v>
       </c>
       <c r="D114" t="n">
-        <v>0.4151581507483976</v>
+        <v>0.4089607666190418</v>
       </c>
       <c r="E114" t="n">
-        <v>2.305284786631869</v>
+        <v>2.214156941164196</v>
       </c>
       <c r="F114" t="n">
-        <v>0.324342602258403</v>
+        <v>0.3405902660493846</v>
       </c>
       <c r="G114" t="n">
-        <v>0.08585131248526712</v>
+        <v>-0.1021657594901699</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="B115" t="n">
-        <v>0.004507930620703508</v>
+        <v>0.004431736341058111</v>
       </c>
       <c r="C115" t="n">
-        <v>0.3902022244867885</v>
+        <v>0.3885019863376773</v>
       </c>
       <c r="D115" t="n">
-        <v>0.4154531417948656</v>
+        <v>0.4093223858762707</v>
       </c>
       <c r="E115" t="n">
-        <v>2.311955944180273</v>
+        <v>2.215376441702519</v>
       </c>
       <c r="F115" t="n">
-        <v>0.3229403446916155</v>
+        <v>0.3403926257024851</v>
       </c>
       <c r="G115" t="n">
-        <v>0.09861774773550797</v>
+        <v>-0.09822561795663173</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="B116" t="n">
-        <v>0.004513218804347653</v>
+        <v>0.004433077869575279</v>
       </c>
       <c r="C116" t="n">
-        <v>0.3902622595109588</v>
+        <v>0.3886091951099931</v>
       </c>
       <c r="D116" t="n">
-        <v>0.4157510151393424</v>
+        <v>0.4096751892506347</v>
       </c>
       <c r="E116" t="n">
-        <v>2.318670234212826</v>
+        <v>2.217049208081888</v>
       </c>
       <c r="F116" t="n">
-        <v>0.3214952878751006</v>
+        <v>0.3401188181737116</v>
       </c>
       <c r="G116" t="n">
-        <v>0.1114248923192515</v>
+        <v>-0.09348306459150517</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="B117" t="n">
-        <v>0.004518523973592368</v>
+        <v>0.004434765776357126</v>
       </c>
       <c r="C117" t="n">
-        <v>0.3903199862928272</v>
+        <v>0.388714022940008</v>
       </c>
       <c r="D117" t="n">
-        <v>0.4160523728357312</v>
+        <v>0.41001974192665</v>
       </c>
       <c r="E117" t="n">
-        <v>2.325406090487454</v>
+        <v>2.219155671706885</v>
       </c>
       <c r="F117" t="n">
-        <v>0.320009093628964</v>
+        <v>0.3397705101689597</v>
       </c>
       <c r="G117" t="n">
-        <v>0.1242346329466856</v>
+        <v>-0.08797618092530693</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="B118" t="n">
-        <v>0.004523829142837082</v>
+        <v>0.00443678356720057</v>
       </c>
       <c r="C118" t="n">
-        <v>0.390375408187293</v>
+        <v>0.3888164731411407</v>
       </c>
       <c r="D118" t="n">
-        <v>0.4163578187434531</v>
+        <v>0.4103566115895891</v>
       </c>
       <c r="E118" t="n">
-        <v>2.332141946762082</v>
+        <v>2.221676448541578</v>
       </c>
       <c r="F118" t="n">
-        <v>0.3184834237733112</v>
+        <v>0.339349368394125</v>
       </c>
       <c r="G118" t="n">
-        <v>0.1370088563279976</v>
+        <v>-0.0817430484885539</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="B119" t="n">
-        <v>0.004529117326481227</v>
+        <v>0.004439114747902535</v>
       </c>
       <c r="C119" t="n">
-        <v>0.3904285285492556</v>
+        <v>0.3889165490268099</v>
       </c>
       <c r="D119" t="n">
-        <v>0.4166679585820519</v>
+        <v>0.4106863683131846</v>
       </c>
       <c r="E119" t="n">
-        <v>2.338856236794635</v>
+        <v>2.224592300898495</v>
       </c>
       <c r="F119" t="n">
-        <v>0.316919940128248</v>
+        <v>0.338857059555103</v>
       </c>
       <c r="G119" t="n">
-        <v>0.1497094491733763</v>
+        <v>-0.07482174881176255</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="B120" t="n">
-        <v>0.004534371538924231</v>
+        <v>0.004441742824259938</v>
       </c>
       <c r="C120" t="n">
-        <v>0.3904793507336144</v>
+        <v>0.3890142539104341</v>
       </c>
       <c r="D120" t="n">
-        <v>0.4169833999945928</v>
+        <v>0.4110095844551757</v>
       </c>
       <c r="E120" t="n">
-        <v>2.34552739434304</v>
+        <v>2.227884101117867</v>
       </c>
       <c r="F120" t="n">
-        <v>0.3153203045138799</v>
+        <v>0.3382952503577895</v>
       </c>
       <c r="G120" t="n">
-        <v>0.1622982981930089</v>
+        <v>-0.06725036342544977</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="B121" t="n">
-        <v>0.004539574794565526</v>
+        <v>0.0044446513020697</v>
       </c>
       <c r="C121" t="n">
-        <v>0.3905278780952688</v>
+        <v>0.389109591105432</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4173047526199098</v>
+        <v>0.411326834560766</v>
       </c>
       <c r="E121" t="n">
-        <v>2.35213385316522</v>
+        <v>2.231532797081888</v>
       </c>
       <c r="F121" t="n">
-        <v>0.3136861787503125</v>
+        <v>0.33766560750808</v>
       </c>
       <c r="G121" t="n">
-        <v>0.1747372900970833</v>
+        <v>-0.05906697386013224</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="B122" t="n">
-        <v>0.00454471010780454</v>
+        <v>0.00444782368712874</v>
       </c>
       <c r="C122" t="n">
-        <v>0.390574113989118</v>
+        <v>0.3892025639252222</v>
       </c>
       <c r="D122" t="n">
-        <v>0.4176326281737525</v>
+        <v>0.4116386952740574</v>
       </c>
       <c r="E122" t="n">
-        <v>2.358654047019102</v>
+        <v>2.235519379517862</v>
       </c>
       <c r="F122" t="n">
-        <v>0.3120192246576516</v>
+        <v>0.3369697977118702</v>
       </c>
       <c r="G122" t="n">
-        <v>0.1869883115957875</v>
+        <v>-0.05030966164632675</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="B123" t="n">
-        <v>0.004549760493040704</v>
+        <v>0.00445124348523398</v>
       </c>
       <c r="C123" t="n">
-        <v>0.3906180617700614</v>
+        <v>0.3892931756832234</v>
       </c>
       <c r="D123" t="n">
-        <v>0.4179676405388899</v>
+        <v>0.4119457452575209</v>
       </c>
       <c r="E123" t="n">
-        <v>2.365066409662612</v>
+        <v>2.239824851052684</v>
       </c>
       <c r="F123" t="n">
-        <v>0.3103211040560027</v>
+        <v>0.3362094876750557</v>
       </c>
       <c r="G123" t="n">
-        <v>0.1990132493993092</v>
+        <v>-0.04101650831455007</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="B124" t="n">
-        <v>0.004554708964673447</v>
+        <v>0.00445489420218234</v>
       </c>
       <c r="C124" t="n">
-        <v>0.3906597247929983</v>
+        <v>0.3893814296928541</v>
       </c>
       <c r="D124" t="n">
-        <v>0.4183104058642326</v>
+        <v>0.4122485651195611</v>
       </c>
       <c r="E124" t="n">
-        <v>2.371349374853673</v>
+        <v>2.244430196989188</v>
       </c>
       <c r="F124" t="n">
-        <v>0.3085934787654714</v>
+        <v>0.3353863441035321</v>
       </c>
       <c r="G124" t="n">
-        <v>0.2107739902178362</v>
+        <v>-0.03122559539531888</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="B125" t="n">
-        <v>0.004559538537102201</v>
+        <v>0.004458759343770737</v>
       </c>
       <c r="C125" t="n">
-        <v>0.3906991064128282</v>
+        <v>0.389467329267533</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4186615426730361</v>
+        <v>0.4125477373502308</v>
       </c>
       <c r="E125" t="n">
-        <v>2.377481376350213</v>
+        <v>2.249316357782509</v>
       </c>
       <c r="F125" t="n">
-        <v>0.3068380106061635</v>
+        <v>0.3345020337031949</v>
       </c>
       <c r="G125" t="n">
-        <v>0.2222324207615566</v>
+        <v>-0.02097500441914994</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="B126" t="n">
-        <v>0.004564232224726393</v>
+        <v>0.004462822415796095</v>
       </c>
       <c r="C126" t="n">
-        <v>0.3907362099844502</v>
+        <v>0.3895508777206787</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4190216719802552</v>
+        <v>0.4128438462651451</v>
       </c>
       <c r="E126" t="n">
-        <v>2.383440847910156</v>
+        <v>2.254464203201755</v>
       </c>
       <c r="F126" t="n">
-        <v>0.3050563613981845</v>
+        <v>0.33355822317994</v>
       </c>
       <c r="G126" t="n">
-        <v>0.2333504277406579</v>
+        <v>-0.01030281691655999</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="B127" t="n">
-        <v>0.004568773041945456</v>
+        <v>0.004467066924055332</v>
       </c>
       <c r="C127" t="n">
-        <v>0.3907710388627639</v>
+        <v>0.3896320783657099</v>
       </c>
       <c r="D127" t="n">
-        <v>0.4193914174191198</v>
+        <v>0.4131374779576462</v>
       </c>
       <c r="E127" t="n">
-        <v>2.389206223291428</v>
+        <v>2.259854508169009</v>
       </c>
       <c r="F127" t="n">
-        <v>0.30325019296164</v>
+        <v>0.3325565792396628</v>
       </c>
       <c r="G127" t="n">
-        <v>0.2440898978653282</v>
+        <v>0.0007528855819342109</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="B128" t="n">
-        <v>0.004573144003158816</v>
+        <v>0.004471476374345368</v>
       </c>
       <c r="C128" t="n">
-        <v>0.3908035964026686</v>
+        <v>0.3897109345160452</v>
       </c>
       <c r="D128" t="n">
-        <v>0.419771405377014</v>
+        <v>0.4134292202592657</v>
       </c>
       <c r="E128" t="n">
-        <v>2.394755936251953</v>
+        <v>2.265467930273944</v>
       </c>
       <c r="F128" t="n">
-        <v>0.3014211671166357</v>
+        <v>0.3314987685882589</v>
       </c>
       <c r="G128" t="n">
-        <v>0.2544127178457551</v>
+        <v>0.01215402154581592</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="B129" t="n">
-        <v>0.004577328122765907</v>
+        <v>0.004476034272463124</v>
       </c>
       <c r="C129" t="n">
-        <v>0.3908338859590635</v>
+        <v>0.3897874494851032</v>
       </c>
       <c r="D129" t="n">
-        <v>0.4201622651407373</v>
+        <v>0.4137196627085289</v>
       </c>
       <c r="E129" t="n">
-        <v>2.400068420549659</v>
+        <v>2.271284988968203</v>
       </c>
       <c r="F129" t="n">
-        <v>0.2995709456832772</v>
+        <v>0.330386457931624</v>
       </c>
       <c r="G129" t="n">
-        <v>0.2642807743921267</v>
+        <v>0.02386250944456841</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="B130" t="n">
-        <v>0.004581308415166158</v>
+        <v>0.004480724124205518</v>
       </c>
       <c r="C130" t="n">
-        <v>0.3908619108868481</v>
+        <v>0.3898616265863025</v>
       </c>
       <c r="D130" t="n">
-        <v>0.4205646290512416</v>
+        <v>0.4140093965281483</v>
       </c>
       <c r="E130" t="n">
-        <v>2.405122109942469</v>
+        <v>2.277286046449114</v>
       </c>
       <c r="F130" t="n">
-        <v>0.2977011904816702</v>
+        <v>0.3292213139756537</v>
       </c>
       <c r="G130" t="n">
-        <v>0.2736559542146306</v>
+        <v>0.03584026774767495</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="B131" t="n">
-        <v>0.004585067894758997</v>
+        <v>0.004485529435369472</v>
       </c>
       <c r="C131" t="n">
-        <v>0.3908876745409217</v>
+        <v>0.3899334691330619</v>
       </c>
       <c r="D131" t="n">
-        <v>0.4209791326679347</v>
+        <v>0.4142990146106451</v>
       </c>
       <c r="E131" t="n">
-        <v>2.40989543818831</v>
+        <v>2.283451290247363</v>
       </c>
       <c r="F131" t="n">
-        <v>0.2958135633319202</v>
+        <v>0.3280050034262437</v>
       </c>
       <c r="G131" t="n">
-        <v>0.2825001440234548</v>
+        <v>0.0480492149246188</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="B132" t="n">
-        <v>0.004588589575943857</v>
+        <v>0.004490433711751907</v>
       </c>
       <c r="C132" t="n">
-        <v>0.3909111802761835</v>
+        <v>0.3900029804387997</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4214064149426566</v>
+        <v>0.414589111512444</v>
       </c>
       <c r="E132" t="n">
-        <v>2.414366839045107</v>
+        <v>2.289760717537784</v>
       </c>
       <c r="F132" t="n">
-        <v>0.2939097260541329</v>
+        <v>0.3267391929892894</v>
       </c>
       <c r="G132" t="n">
-        <v>0.2907752305287869</v>
+        <v>0.06045126944488318</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="B133" t="n">
-        <v>0.004591856473120164</v>
+        <v>0.004495420459149741</v>
       </c>
       <c r="C133" t="n">
-        <v>0.3909324314475331</v>
+        <v>0.3900701638169349</v>
       </c>
       <c r="D133" t="n">
-        <v>0.4218471184034329</v>
+        <v>0.4148802834564838</v>
       </c>
       <c r="E133" t="n">
-        <v>2.418514746270785</v>
+        <v>2.296194121196678</v>
       </c>
       <c r="F133" t="n">
-        <v>0.291991340468414</v>
+        <v>0.3254255493706867</v>
       </c>
       <c r="G133" t="n">
-        <v>0.2984431004408151</v>
+        <v>0.0730083497779514</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="B134" t="n">
-        <v>0.004594851600687351</v>
+        <v>0.004500473183359895</v>
       </c>
       <c r="C134" t="n">
-        <v>0.3909514314098697</v>
+        <v>0.3901350225808859</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4223018893481258</v>
+        <v>0.415173128343382</v>
       </c>
       <c r="E134" t="n">
-        <v>2.42231759362327</v>
+        <v>2.302731077632753</v>
       </c>
       <c r="F134" t="n">
-        <v>0.290060068394869</v>
+        <v>0.324065739276331</v>
       </c>
       <c r="G134" t="n">
-        <v>0.3054656404697272</v>
+        <v>0.0856823743933067</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="B135" t="n">
-        <v>0.004597557973044846</v>
+        <v>0.004505575390179288</v>
       </c>
       <c r="C135" t="n">
-        <v>0.3909681835180926</v>
+        <v>0.3901975600440713</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4227713780481037</v>
+        <v>0.4154682457712</v>
       </c>
       <c r="E135" t="n">
-        <v>2.425753814860487</v>
+        <v>2.309350936422129</v>
       </c>
       <c r="F135" t="n">
-        <v>0.2881175716536036</v>
+        <v>0.3226614294121181</v>
       </c>
       <c r="G135" t="n">
-        <v>0.3118047373257107</v>
+        <v>0.09843526176043225</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="B136" t="n">
-        <v>0.004599958604592082</v>
+        <v>0.00451071058540484</v>
       </c>
       <c r="C136" t="n">
-        <v>0.3909826911271013</v>
+        <v>0.3902577795199099</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4232562389620627</v>
+        <v>0.4157662370638488</v>
       </c>
       <c r="E136" t="n">
-        <v>2.428801843740361</v>
+        <v>2.316032811780712</v>
       </c>
       <c r="F136" t="n">
-        <v>0.2861655120647234</v>
+        <v>0.3212142864839434</v>
       </c>
       <c r="G136" t="n">
-        <v>0.3174222777189536</v>
+        <v>0.1112289303488115</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="B137" t="n">
-        <v>0.004602036509728485</v>
+        <v>0.004515862274833474</v>
       </c>
       <c r="C137" t="n">
-        <v>0.3909949575917951</v>
+        <v>0.3903156843218202</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4237571309601416</v>
+        <v>0.416067705308179</v>
       </c>
       <c r="E137" t="n">
-        <v>2.431440114020818</v>
+        <v>2.322755575909657</v>
       </c>
       <c r="F137" t="n">
-        <v>0.2842055514483341</v>
+        <v>0.3197259771977026</v>
       </c>
       <c r="G137" t="n">
-        <v>0.3222801483596438</v>
+        <v>0.1240252986279275</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="B138" t="n">
-        <v>0.004603774702853488</v>
+        <v>0.004521013964262108</v>
       </c>
       <c r="C138" t="n">
-        <v>0.3910049862670733</v>
+        <v>0.390371277763221</v>
       </c>
       <c r="D138" t="n">
-        <v>0.4242747175584796</v>
+        <v>0.4163732553998022</v>
       </c>
       <c r="E138" t="n">
-        <v>2.433647059459783</v>
+        <v>2.329497854251572</v>
       </c>
       <c r="F138" t="n">
-        <v>0.2822393516245412</v>
+        <v>0.3181981682592915</v>
       </c>
       <c r="G138" t="n">
-        <v>0.326340235957969</v>
+        <v>0.1367862850672637</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="B139" t="n">
-        <v>0.004605156198366519</v>
+        <v>0.00452614915948766</v>
       </c>
       <c r="C139" t="n">
-        <v>0.3910127805078352</v>
+        <v>0.3904245631575307</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4248096671643776</v>
+        <v>0.4166834940976882</v>
       </c>
       <c r="E139" t="n">
-        <v>2.435401113815184</v>
+        <v>2.336238022696612</v>
       </c>
       <c r="F139" t="n">
-        <v>0.2802685744134505</v>
+        <v>0.3166325263746055</v>
       </c>
       <c r="G139" t="n">
-        <v>0.3295644272241174</v>
+        <v>0.1494738081363032</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="B140" t="n">
-        <v>0.004606164010667009</v>
+        <v>0.004531251366307053</v>
       </c>
       <c r="C140" t="n">
-        <v>0.3910183436689803</v>
+        <v>0.3904755438181681</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4253626533322317</v>
+        <v>0.4169990300875882</v>
       </c>
       <c r="E140" t="n">
-        <v>2.436680710844942</v>
+        <v>2.342954206778568</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2782948816351675</v>
+        <v>0.3150307182495402</v>
       </c>
       <c r="G140" t="n">
-        <v>0.3319146088682765</v>
+        <v>0.1620497863045293</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="B141" t="n">
-        <v>0.004606781154154388</v>
+        <v>0.004536304090517207</v>
       </c>
       <c r="C141" t="n">
-        <v>0.3910216791054078</v>
+        <v>0.3905242230585517</v>
       </c>
       <c r="D141" t="n">
-        <v>0.425934355030421</v>
+        <v>0.417320474054335</v>
       </c>
       <c r="E141" t="n">
-        <v>2.437464284306985</v>
+        <v>2.349624282901508</v>
       </c>
       <c r="F141" t="n">
-        <v>0.2763199351097979</v>
+        <v>0.3133944105899914</v>
       </c>
       <c r="G141" t="n">
-        <v>0.3333526676006341</v>
+        <v>0.1744761380414254</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="B142" t="n">
-        <v>0.004606990643228085</v>
+        <v>0.00454129083791504</v>
       </c>
       <c r="C142" t="n">
-        <v>0.3910227901720171</v>
+        <v>0.3905706041921002</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4265254569193407</v>
+        <v>0.4176484387630729</v>
       </c>
       <c r="E142" t="n">
-        <v>2.437730267959238</v>
+        <v>2.35622588163751</v>
       </c>
       <c r="F142" t="n">
-        <v>0.2743453966574473</v>
+        <v>0.3117252701018546</v>
       </c>
       <c r="G142" t="n">
-        <v>0.3338404901313784</v>
+        <v>0.1867147818164746</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="B143" t="n">
-        <v>0.004605935766460317</v>
+        <v>0.004546195114297475</v>
       </c>
       <c r="C143" t="n">
-        <v>0.3910163453258863</v>
+        <v>0.3906146905322322</v>
       </c>
       <c r="D143" t="n">
-        <v>0.4271509436804268</v>
+        <v>0.4179835391494758</v>
       </c>
       <c r="E143" t="n">
-        <v>2.437594650599037</v>
+        <v>2.362736393135388</v>
       </c>
       <c r="F143" t="n">
-        <v>0.2723276758532968</v>
+        <v>0.3100249634910254</v>
       </c>
       <c r="G143" t="n">
-        <v>0.3337820713803235</v>
+        <v>0.1987276360991599</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="B144" t="n">
-        <v>0.00460279174565297</v>
+        <v>0.004551000425461429</v>
       </c>
       <c r="C144" t="n">
-        <v>0.3909971219158956</v>
+        <v>0.3906564853923664</v>
       </c>
       <c r="D144" t="n">
-        <v>0.4278250761097339</v>
+        <v>0.4183263924190141</v>
       </c>
       <c r="E144" t="n">
-        <v>2.437188756801539</v>
+        <v>2.36913297467919</v>
       </c>
       <c r="F144" t="n">
-        <v>0.2702227262620701</v>
+        <v>0.3082951574633995</v>
       </c>
       <c r="G144" t="n">
-        <v>0.3336043408811648</v>
+        <v>0.2104766193589651</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="B145" t="n">
-        <v>0.004597589495049985</v>
+        <v>0.004555690277203824</v>
       </c>
       <c r="C145" t="n">
-        <v>0.3909652866346474</v>
+        <v>0.3906959920859213</v>
       </c>
       <c r="D145" t="n">
-        <v>0.4285474670615807</v>
+        <v>0.4186776181553328</v>
       </c>
       <c r="E145" t="n">
-        <v>2.436514023991399</v>
+        <v>2.375392560433522</v>
       </c>
       <c r="F145" t="n">
-        <v>0.268031525688187</v>
+        <v>0.3065375187248725</v>
       </c>
       <c r="G145" t="n">
-        <v>0.3333035872649107</v>
+        <v>0.2219236500653733</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="B146" t="n">
-        <v>0.004590359928895299</v>
+        <v>0.00456024817532158</v>
       </c>
       <c r="C146" t="n">
-        <v>0.390921006174744</v>
+        <v>0.3907332139263157</v>
       </c>
       <c r="D146" t="n">
-        <v>0.4293177417109042</v>
+        <v>0.4190378384378114</v>
       </c>
       <c r="E146" t="n">
-        <v>2.435571889593274</v>
+        <v>2.381491873410455</v>
       </c>
       <c r="F146" t="n">
-        <v>0.265755051936067</v>
+        <v>0.3047537139813399</v>
       </c>
       <c r="G146" t="n">
-        <v>0.3328760991625702</v>
+        <v>0.2330306466878677</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="B147" t="n">
-        <v>0.004581133961432852</v>
+        <v>0.004564657625611616</v>
       </c>
       <c r="C147" t="n">
-        <v>0.3908644472287879</v>
+        <v>0.390768154226968</v>
       </c>
       <c r="D147" t="n">
-        <v>0.4301355369958929</v>
+        <v>0.4194076779683784</v>
       </c>
       <c r="E147" t="n">
-        <v>2.43436379103182</v>
+        <v>2.387407439689878</v>
       </c>
       <c r="F147" t="n">
-        <v>0.26339428281013</v>
+        <v>0.3029454099386975</v>
       </c>
       <c r="G147" t="n">
-        <v>0.3323181652051517</v>
+        <v>0.2437595276959315</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="B148" t="n">
-        <v>0.004569942506906584</v>
+        <v>0.004568902133870852</v>
       </c>
       <c r="C148" t="n">
-        <v>0.3907957764893816</v>
+        <v>0.3908008163012971</v>
       </c>
       <c r="D148" t="n">
-        <v>0.4310005010713447</v>
+        <v>0.4197877642076573</v>
       </c>
       <c r="E148" t="n">
-        <v>2.432891165731693</v>
+        <v>2.393115604921663</v>
       </c>
       <c r="F148" t="n">
-        <v>0.2609501961147956</v>
+        <v>0.3011142733028408</v>
       </c>
       <c r="G148" t="n">
-        <v>0.3316260740236641</v>
+        <v>0.2540722115590479</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="B149" t="n">
-        <v>0.004556816479560433</v>
+        <v>0.00457296520589621</v>
       </c>
       <c r="C149" t="n">
-        <v>0.3907151606491274</v>
+        <v>0.3908312034627214</v>
       </c>
       <c r="D149" t="n">
-        <v>0.4319122927721676</v>
+        <v>0.4201787275205297</v>
       </c>
       <c r="E149" t="n">
-        <v>2.43115545111755</v>
+        <v>2.398592553133904</v>
       </c>
       <c r="F149" t="n">
-        <v>0.2584237696544835</v>
+        <v>0.2992619707796655</v>
       </c>
       <c r="G149" t="n">
-        <v>0.3307961142491161</v>
+        <v>0.2639306167467004</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="B150" t="n">
-        <v>0.004541786793638338</v>
+        <v>0.004576830347484608</v>
       </c>
       <c r="C150" t="n">
-        <v>0.3906227664006277</v>
+        <v>0.3908593190246597</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4328705810864632</v>
+        <v>0.4205812013312034</v>
       </c>
       <c r="E150" t="n">
-        <v>2.429158084614047</v>
+        <v>2.40381432786675</v>
       </c>
       <c r="F150" t="n">
-        <v>0.2558159812336133</v>
+        <v>0.297390169075067</v>
       </c>
       <c r="G150" t="n">
-        <v>0.3298245745125163</v>
+        <v>0.2732966617283721</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="B151" t="n">
-        <v>0.004524884363384238</v>
+        <v>0.004580481064432967</v>
       </c>
       <c r="C151" t="n">
-        <v>0.390518760436485</v>
+        <v>0.3908851663005306</v>
       </c>
       <c r="D151" t="n">
-        <v>0.4338750446376551</v>
+        <v>0.4209958222878812</v>
       </c>
       <c r="E151" t="n">
-        <v>2.42690050364584</v>
+        <v>2.408756855645986</v>
       </c>
       <c r="F151" t="n">
-        <v>0.2531278086566049</v>
+        <v>0.2955005348949413</v>
       </c>
       <c r="G151" t="n">
-        <v>0.3287077434448733</v>
+        <v>0.2821322649735462</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="B152" t="n">
-        <v>0.004506140103042074</v>
+        <v>0.004583900862538208</v>
       </c>
       <c r="C152" t="n">
-        <v>0.3904033094493016</v>
+        <v>0.3909087486037526</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4349253711751459</v>
+        <v>0.4214232304371336</v>
       </c>
       <c r="E152" t="n">
-        <v>2.424384145637585</v>
+        <v>2.413395971804545</v>
       </c>
       <c r="F152" t="n">
-        <v>0.2503602297278777</v>
+        <v>0.2935947349451836</v>
       </c>
       <c r="G152" t="n">
-        <v>0.3274419096771961</v>
+        <v>0.290399344951706</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="B153" t="n">
-        <v>0.004485584926855782</v>
+        <v>0.004587073247597248</v>
       </c>
       <c r="C153" t="n">
-        <v>0.39027658013168</v>
+        <v>0.3909300692477444</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4360212570730064</v>
+        <v>0.4218640694080832</v>
       </c>
       <c r="E153" t="n">
-        <v>2.421610448013939</v>
+        <v>2.417707448653474</v>
       </c>
       <c r="F153" t="n">
-        <v>0.2475142222518516</v>
+        <v>0.2916744359316898</v>
       </c>
       <c r="G153" t="n">
-        <v>0.326023361840493</v>
+        <v>0.2980598201323348</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="B154" t="n">
-        <v>0.004463249749069303</v>
+        <v>0.00458998172540701</v>
       </c>
       <c r="C154" t="n">
-        <v>0.3901387391762227</v>
+        <v>0.3909491315459246</v>
       </c>
       <c r="D154" t="n">
-        <v>0.4371624068362218</v>
+        <v>0.4223189866065185</v>
       </c>
       <c r="E154" t="n">
-        <v>2.418580848199557</v>
+        <v>2.421667025996685</v>
       </c>
       <c r="F154" t="n">
-        <v>0.2445907640329463</v>
+        <v>0.2897413045603555</v>
       </c>
       <c r="G154" t="n">
-        <v>0.324448388565773</v>
+        <v>0.305075608984916</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="B155" t="n">
-        <v>0.004439165483926576</v>
+        <v>0.004592609801764413</v>
       </c>
       <c r="C155" t="n">
-        <v>0.3899899532755318</v>
+        <v>0.3909659388117119</v>
       </c>
       <c r="D155" t="n">
-        <v>0.4383485326140364</v>
+        <v>0.4227886334190603</v>
       </c>
       <c r="E155" t="n">
-        <v>2.415296783619096</v>
+        <v>2.425250443975881</v>
       </c>
       <c r="F155" t="n">
-        <v>0.2415908328755813</v>
+        <v>0.2877970075370762</v>
       </c>
       <c r="G155" t="n">
-        <v>0.3227132784840446</v>
+        <v>0.3114086299789327</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="B156" t="n">
-        <v>0.004413363045671539</v>
+        <v>0.004594940982466377</v>
       </c>
       <c r="C156" t="n">
-        <v>0.38983038912221</v>
+        <v>0.3909804943585249</v>
       </c>
       <c r="D156" t="n">
-        <v>0.4395793537199601</v>
+        <v>0.4232736654275158</v>
       </c>
       <c r="E156" t="n">
-        <v>2.411759691697213</v>
+        <v>2.428433478223656</v>
       </c>
       <c r="F156" t="n">
-        <v>0.2385154065841765</v>
+        <v>0.2858432115677476</v>
       </c>
       <c r="G156" t="n">
-        <v>0.3208143202263167</v>
+        <v>0.3170208015838681</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="B157" t="n">
-        <v>0.004385873348548133</v>
+        <v>0.004596958773309822</v>
       </c>
       <c r="C157" t="n">
-        <v>0.3896602134088596</v>
+        <v>0.3909928014997822</v>
       </c>
       <c r="D157" t="n">
-        <v>0.4408545961580151</v>
+        <v>0.4237747426335585</v>
       </c>
       <c r="E157" t="n">
-        <v>2.407971009858563</v>
+        <v>2.431191977293615</v>
       </c>
       <c r="F157" t="n">
-        <v>0.2353654629631514</v>
+        <v>0.2838815833582652</v>
       </c>
       <c r="G157" t="n">
-        <v>0.3187478024235977</v>
+        <v>0.3218740422692054</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="B158" t="n">
-        <v>0.004356727306800295</v>
+        <v>0.004598646680091668</v>
       </c>
       <c r="C158" t="n">
-        <v>0.3894795928280831</v>
+        <v>0.3910028635489025</v>
       </c>
       <c r="D158" t="n">
-        <v>0.4421739921548202</v>
+        <v>0.4242925296938884</v>
       </c>
       <c r="E158" t="n">
-        <v>2.403932175527803</v>
+        <v>2.433501902326802</v>
       </c>
       <c r="F158" t="n">
-        <v>0.2321419798169258</v>
+        <v>0.2819137896145248</v>
       </c>
       <c r="G158" t="n">
-        <v>0.3165100137068966</v>
+        <v>0.3259302705044279</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="B159" t="n">
-        <v>0.004325955834671965</v>
+        <v>0.004599988208608837</v>
       </c>
       <c r="C159" t="n">
-        <v>0.3892886940724827</v>
+        <v>0.3910106838193044</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4435372796971266</v>
+        <v>0.4248276961660291</v>
       </c>
       <c r="E159" t="n">
-        <v>2.399644626129589</v>
+        <v>2.435339368903459</v>
       </c>
       <c r="F159" t="n">
-        <v>0.2288459349499194</v>
+        <v>0.2799414970424219</v>
       </c>
       <c r="G159" t="n">
-        <v>0.3140972427072219</v>
+        <v>0.3291514047590193</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="B160" t="n">
-        <v>0.004293589846407081</v>
+        <v>0.004600966864658247</v>
       </c>
       <c r="C160" t="n">
-        <v>0.3890876838346611</v>
+        <v>0.3910162656244065</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4449442020744362</v>
+        <v>0.4253809167649362</v>
       </c>
       <c r="E160" t="n">
-        <v>2.395109799088576</v>
+        <v>2.436680691018509</v>
       </c>
       <c r="F160" t="n">
-        <v>0.2254783061665518</v>
+        <v>0.2779663723478522</v>
       </c>
       <c r="G160" t="n">
-        <v>0.3115057780555824</v>
+        <v>0.3314993635024623</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="B161" t="n">
-        <v>0.004259660256249584</v>
+        <v>0.004601566154036818</v>
       </c>
       <c r="C161" t="n">
-        <v>0.3888767288072205</v>
+        <v>0.3910196122776274</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4463945074263475</v>
+        <v>0.4259528716305953</v>
       </c>
       <c r="E161" t="n">
-        <v>2.390329131829422</v>
+        <v>2.43750242710791</v>
       </c>
       <c r="F161" t="n">
-        <v>0.2220400712712427</v>
+        <v>0.2759900822367111</v>
       </c>
       <c r="G161" t="n">
-        <v>0.3087319083829866</v>
+        <v>0.3329360652042405</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="B162" t="n">
-        <v>0.004224197978443412</v>
+        <v>0.00460176958254147</v>
       </c>
       <c r="C162" t="n">
-        <v>0.3886559956827634</v>
+        <v>0.3910207270923858</v>
       </c>
       <c r="D162" t="n">
-        <v>0.4478879482942936</v>
+        <v>0.426544246606803</v>
       </c>
       <c r="E162" t="n">
-        <v>2.385304061776783</v>
+        <v>2.437781428041422</v>
       </c>
       <c r="F162" t="n">
-        <v>0.2185322080684119</v>
+        <v>0.2740142934148945</v>
       </c>
       <c r="G162" t="n">
-        <v>0.3057719223204434</v>
+        <v>0.3334234283338369</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="B163" t="n">
-        <v>0.004187233927232504</v>
+        <v>0.004600715885121506</v>
       </c>
       <c r="C163" t="n">
-        <v>0.3884256511538922</v>
+        <v>0.3910142843590856</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4494242811773468</v>
+        <v>0.4271700042273787</v>
       </c>
       <c r="E163" t="n">
-        <v>2.380036026355314</v>
+        <v>2.437629808811286</v>
       </c>
       <c r="F163" t="n">
-        <v>0.2149556943624789</v>
+        <v>0.2719955253027814</v>
       </c>
       <c r="G163" t="n">
-        <v>0.3026221084989615</v>
+        <v>0.3333650877581562</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="B164" t="n">
-        <v>0.004148799016860799</v>
+        <v>0.004597575420538548</v>
       </c>
       <c r="C164" t="n">
-        <v>0.3881858619132093</v>
+        <v>0.390995067171938</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4510032660917849</v>
+        <v>0.4278443826189213</v>
       </c>
       <c r="E164" t="n">
-        <v>2.374526462989673</v>
+        <v>2.437176208687792</v>
       </c>
       <c r="F164" t="n">
-        <v>0.2113115079578636</v>
+        <v>0.2698898349852757</v>
       </c>
       <c r="G164" t="n">
-        <v>0.2992787555495494</v>
+        <v>0.3331875943371238</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="B165" t="n">
-        <v>0.004108924161572236</v>
+        <v>0.004592379130308007</v>
       </c>
       <c r="C165" t="n">
-        <v>0.3879367946533172</v>
+        <v>0.3909632420500726</v>
       </c>
       <c r="D165" t="n">
-        <v>0.4526246661341242</v>
+        <v>0.4285669950335537</v>
       </c>
       <c r="E165" t="n">
-        <v>2.368776809104515</v>
+        <v>2.436422597177221</v>
       </c>
       <c r="F165" t="n">
-        <v>0.2076006266589855</v>
+        <v>0.2676981956650601</v>
       </c>
       <c r="G165" t="n">
-        <v>0.295738152103216</v>
+        <v>0.3328872405297545</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="B166" t="n">
-        <v>0.004067640275610755</v>
+        <v>0.004585157955945288</v>
       </c>
       <c r="C166" t="n">
-        <v>0.3876786160668181</v>
+        <v>0.3909189755126187</v>
       </c>
       <c r="D166" t="n">
-        <v>0.4542882470473408</v>
+        <v>0.4293374670284403</v>
       </c>
       <c r="E166" t="n">
-        <v>2.362788502124496</v>
+        <v>2.435371052790644</v>
       </c>
       <c r="F166" t="n">
-        <v>0.2038240282702645</v>
+        <v>0.2654215805448177</v>
       </c>
       <c r="G166" t="n">
-        <v>0.2919965867909698</v>
+        <v>0.3324603187950633</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="B167" t="n">
-        <v>0.004024978273220294</v>
+        <v>0.004575942838965799</v>
       </c>
       <c r="C167" t="n">
-        <v>0.3874114928463146</v>
+        <v>0.3908624340787061</v>
       </c>
       <c r="D167" t="n">
-        <v>0.4559937767900162</v>
+        <v>0.4301554359091893</v>
       </c>
       <c r="E167" t="n">
-        <v>2.356562979474274</v>
+        <v>2.434023760664084</v>
       </c>
       <c r="F167" t="n">
-        <v>0.19998269059612</v>
+        <v>0.2630609628272312</v>
       </c>
       <c r="G167" t="n">
-        <v>0.2880503482438196</v>
+        <v>0.3319031215920649</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="B168" t="n">
-        <v>0.003980969068644792</v>
+        <v>0.004564764720884947</v>
       </c>
       <c r="C168" t="n">
-        <v>0.387135591684409</v>
+        <v>0.3907937842674643</v>
       </c>
       <c r="D168" t="n">
-        <v>0.4577410251081558</v>
+        <v>0.4310205501839602</v>
       </c>
       <c r="E168" t="n">
-        <v>2.350101678578503</v>
+        <v>2.432383010130066</v>
       </c>
       <c r="F168" t="n">
-        <v>0.1960775914409719</v>
+        <v>0.2606173157149835</v>
       </c>
       <c r="G168" t="n">
-        <v>0.2838957250927741</v>
+        <v>0.331211941379774</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="B169" t="n">
-        <v>0.00393564357612819</v>
+        <v>0.00455165454321814</v>
       </c>
       <c r="C169" t="n">
-        <v>0.3868510792737039</v>
+        <v>0.3907131925980225</v>
       </c>
       <c r="D169" t="n">
-        <v>0.4595297631094417</v>
+        <v>0.4319324690276956</v>
       </c>
       <c r="E169" t="n">
-        <v>2.343406036861841</v>
+        <v>2.430451192243514</v>
       </c>
       <c r="F169" t="n">
-        <v>0.1921097086092399</v>
+        <v>0.2580916124107573</v>
       </c>
       <c r="G169" t="n">
-        <v>0.279529005968842</v>
+        <v>0.3303830706172054</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="B170" t="n">
-        <v>0.003889032709914425</v>
+        <v>0.004536643247480785</v>
       </c>
       <c r="C170" t="n">
-        <v>0.3865581223068015</v>
+        <v>0.3906208255895106</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4613597628396979</v>
+        <v>0.4328908617559162</v>
       </c>
       <c r="E170" t="n">
-        <v>2.336477491748942</v>
+        <v>2.428230797264962</v>
       </c>
       <c r="F170" t="n">
-        <v>0.1880800199053436</v>
+        <v>0.2554848261172357</v>
       </c>
       <c r="G170" t="n">
-        <v>0.274946479503032</v>
+        <v>0.329412801763374</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="B171" t="n">
-        <v>0.003841167384247436</v>
+        <v>0.004519761775188289</v>
       </c>
       <c r="C171" t="n">
-        <v>0.3862568874763043</v>
+        <v>0.3905168497610578</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4632307968613549</v>
+        <v>0.4338954073075461</v>
       </c>
       <c r="E171" t="n">
-        <v>2.329317480664466</v>
+        <v>2.425724412104044</v>
       </c>
       <c r="F171" t="n">
-        <v>0.1839895031337026</v>
+        <v>0.2527979300371013</v>
       </c>
       <c r="G171" t="n">
-        <v>0.2701444343263527</v>
+        <v>0.3282974272772946</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="B172" t="n">
-        <v>0.003792078513371163</v>
+        <v>0.004501041067856059</v>
       </c>
       <c r="C172" t="n">
-        <v>0.3859475414748146</v>
+        <v>0.3904014316317939</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4651426378337166</v>
+        <v>0.4349457937362488</v>
       </c>
       <c r="E172" t="n">
-        <v>2.321927441033065</v>
+        <v>2.422934717726219</v>
       </c>
       <c r="F172" t="n">
-        <v>0.1798391360987367</v>
+        <v>0.2500318973730369</v>
       </c>
       <c r="G172" t="n">
-        <v>0.2651191590698128</v>
+        <v>0.3270332396179819</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="B173" t="n">
-        <v>0.003741797011529545</v>
+        <v>0.004480512066999502</v>
       </c>
       <c r="C173" t="n">
-        <v>0.3856302509949351</v>
+        <v>0.3902747377208481</v>
       </c>
       <c r="D173" t="n">
-        <v>0.4670950580948449</v>
+        <v>0.4360417177097829</v>
       </c>
       <c r="E173" t="n">
-        <v>2.314308810279398</v>
+        <v>2.419864486525659</v>
       </c>
       <c r="F173" t="n">
-        <v>0.1756298966048657</v>
+        <v>0.2471877013277257</v>
       </c>
       <c r="G173" t="n">
-        <v>0.2598669423644211</v>
+        <v>0.3256165312444507</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="B174" t="n">
-        <v>0.00369035379296652</v>
+        <v>0.004458205714134027</v>
       </c>
       <c r="C174" t="n">
-        <v>0.3853051827292679</v>
+        <v>0.3901369345473503</v>
       </c>
       <c r="D174" t="n">
-        <v>0.4690878292448886</v>
+        <v>0.4371828840168991</v>
       </c>
       <c r="E174" t="n">
-        <v>2.30646302582812</v>
+        <v>2.416516579667252</v>
       </c>
       <c r="F174" t="n">
-        <v>0.1713627624565091</v>
+        <v>0.2442663151038501</v>
       </c>
       <c r="G174" t="n">
-        <v>0.2543840728411861</v>
+        <v>0.3240435946157159</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="B175" t="n">
-        <v>0.003637779771926028</v>
+        <v>0.004434152950775041</v>
       </c>
       <c r="C175" t="n">
-        <v>0.3849725033704156</v>
+        <v>0.3899881886304297</v>
       </c>
       <c r="D175" t="n">
-        <v>0.4711207217306975</v>
+        <v>0.4383690050813233</v>
       </c>
       <c r="E175" t="n">
-        <v>2.298391525103888</v>
+        <v>2.412893944400597</v>
       </c>
       <c r="F175" t="n">
-        <v>0.1670387114580866</v>
+        <v>0.2412687119040932</v>
       </c>
       <c r="G175" t="n">
-        <v>0.2486668391311167</v>
+        <v>0.3223107221907923</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="B176" t="n">
-        <v>0.003584105862652008</v>
+        <v>0.004408384718437949</v>
       </c>
       <c r="C176" t="n">
-        <v>0.3846323796109805</v>
+        <v>0.3898286664892159</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4731935044315739</v>
+        <v>0.4395998004823899</v>
       </c>
       <c r="E176" t="n">
-        <v>2.290095745531358</v>
+        <v>2.408999611348912</v>
       </c>
       <c r="F176" t="n">
-        <v>0.1626587214140179</v>
+        <v>0.2381958649311378</v>
       </c>
       <c r="G176" t="n">
-        <v>0.2427115298652216</v>
+        <v>0.3204142064286946</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="B177" t="n">
-        <v>0.0035293629793884</v>
+        <v>0.00438093195863816</v>
       </c>
       <c r="C177" t="n">
-        <v>0.3842849781435652</v>
+        <v>0.3896585346428386</v>
       </c>
       <c r="D177" t="n">
-        <v>0.4753059442460276</v>
+        <v>0.4408749964819028</v>
       </c>
       <c r="E177" t="n">
-        <v>2.281577124535186</v>
+        <v>2.404836691775681</v>
       </c>
       <c r="F177" t="n">
-        <v>0.1582237701287228</v>
+        <v>0.2350487473876667</v>
       </c>
       <c r="G177" t="n">
-        <v>0.2365144336745094</v>
+        <v>0.3183503397884376</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="B178" t="n">
-        <v>0.003473582036379141</v>
+        <v>0.004351825612891083</v>
       </c>
       <c r="C178" t="n">
-        <v>0.3839304656607718</v>
+        <v>0.3894779596104271</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4774578056794111</v>
+        <v>0.4421943255568248</v>
       </c>
       <c r="E178" t="n">
-        <v>2.272837099540028</v>
+        <v>2.4004083748319</v>
       </c>
       <c r="F178" t="n">
-        <v>0.1537348354066209</v>
+        <v>0.2318283324763628</v>
       </c>
       <c r="G178" t="n">
-        <v>0.2300718391899887</v>
+        <v>0.3161154147290361</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="B179" t="n">
-        <v>0.003416793947868172</v>
+        <v>0.004321096622712121</v>
       </c>
       <c r="C179" t="n">
-        <v>0.383569008855203</v>
+        <v>0.389287107911111</v>
       </c>
       <c r="D179" t="n">
-        <v>0.479648850432325</v>
+        <v>0.443557525937407</v>
       </c>
       <c r="E179" t="n">
-        <v>2.263877107970541</v>
+        <v>2.395717924786708</v>
       </c>
       <c r="F179" t="n">
-        <v>0.1491928950521319</v>
+        <v>0.2285355933999089</v>
       </c>
       <c r="G179" t="n">
-        <v>0.2233800350426682</v>
+        <v>0.313705723709505</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="B180" t="n">
-        <v>0.00335902962809943</v>
+        <v>0.004288775929616685</v>
       </c>
       <c r="C180" t="n">
-        <v>0.383200774419461</v>
+        <v>0.3890861460640199</v>
       </c>
       <c r="D180" t="n">
-        <v>0.4818788369896967</v>
+        <v>0.4449643411503938</v>
       </c>
       <c r="E180" t="n">
-        <v>2.254698587251381</v>
+        <v>2.390768678244181</v>
       </c>
       <c r="F180" t="n">
-        <v>0.1445989268696755</v>
+        <v>0.2251715033609879</v>
       </c>
       <c r="G180" t="n">
-        <v>0.2164353098635569</v>
+        <v>0.311117559188859</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="B181" t="n">
-        <v>0.003300319991316856</v>
+        <v>0.00425489447512018</v>
       </c>
       <c r="C181" t="n">
-        <v>0.3828259290461484</v>
+        <v>0.3888752405882832</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4841475202104452</v>
+        <v>0.4464145195669443</v>
       </c>
       <c r="E181" t="n">
-        <v>2.245302974807203</v>
+        <v>2.385564041349</v>
       </c>
       <c r="F181" t="n">
-        <v>0.1399539086636713</v>
+        <v>0.2217370355622825</v>
       </c>
       <c r="G181" t="n">
-        <v>0.2092339522836631</v>
+        <v>0.3083472136261129</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="B182" t="n">
-        <v>0.003240695951764388</v>
+        <v>0.004219483200738015</v>
       </c>
       <c r="C182" t="n">
-        <v>0.3824446394278675</v>
+        <v>0.3886545580030303</v>
       </c>
       <c r="D182" t="n">
-        <v>0.4864546509176604</v>
+        <v>0.44790781395494</v>
       </c>
       <c r="E182" t="n">
-        <v>2.235691708062665</v>
+        <v>2.380107486983716</v>
       </c>
       <c r="F182" t="n">
-        <v>0.1352588182385391</v>
+        <v>0.2182331632064757</v>
       </c>
       <c r="G182" t="n">
-        <v>0.2017722509339958</v>
+        <v>0.3053909794802816</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="B183" t="n">
-        <v>0.003180188423685964</v>
+        <v>0.004182573047985597</v>
       </c>
       <c r="C183" t="n">
-        <v>0.3820570722572208</v>
+        <v>0.388424264827391</v>
       </c>
       <c r="D183" t="n">
-        <v>0.4887999754892358</v>
+        <v>0.449443981035351</v>
       </c>
       <c r="E183" t="n">
-        <v>2.225866224442423</v>
+        <v>2.374402551960223</v>
       </c>
       <c r="F183" t="n">
-        <v>0.1305146333986985</v>
+        <v>0.2146608594962502</v>
       </c>
       <c r="G183" t="n">
-        <v>0.1940464944455633</v>
+        <v>0.3022451492103798</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="B184" t="n">
-        <v>0.003118828321325527</v>
+        <v>0.004144194958378332</v>
       </c>
       <c r="C184" t="n">
-        <v>0.3816633942268106</v>
+        <v>0.3881845275804947</v>
       </c>
       <c r="D184" t="n">
-        <v>0.4911832354489027</v>
+        <v>0.4510227810423572</v>
       </c>
       <c r="E184" t="n">
-        <v>2.215827961371132</v>
+        <v>2.368452834208069</v>
       </c>
       <c r="F184" t="n">
-        <v>0.1257223319485694</v>
+        <v>0.211021097634289</v>
       </c>
       <c r="G184" t="n">
-        <v>0.1860529714493749</v>
+        <v>0.2989060152754223</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="B185" t="n">
-        <v>0.003056646558927011</v>
+        <v>0.004104379873431628</v>
       </c>
       <c r="C185" t="n">
-        <v>0.3812637720292393</v>
+        <v>0.3879355127814708</v>
       </c>
       <c r="D185" t="n">
-        <v>0.4936041670576356</v>
+        <v>0.4526439772869296</v>
       </c>
       <c r="E185" t="n">
-        <v>2.205578356273449</v>
+        <v>2.362261989962158</v>
       </c>
       <c r="F185" t="n">
-        <v>0.120882891692571</v>
+        <v>0.2073148508232748</v>
       </c>
       <c r="G185" t="n">
-        <v>0.1777879705764386</v>
+        <v>0.2953698701344239</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="B186" t="n">
-        <v>0.00299367405073436</v>
+        <v>0.004063158734660893</v>
       </c>
       <c r="C186" t="n">
-        <v>0.3808583723571095</v>
+        <v>0.387677386949449</v>
       </c>
       <c r="D186" t="n">
-        <v>0.4960625009053976</v>
+        <v>0.4543073357235956</v>
       </c>
       <c r="E186" t="n">
-        <v>2.195118846574031</v>
+        <v>2.355833730952332</v>
       </c>
       <c r="F186" t="n">
-        <v>0.1159972904351236</v>
+        <v>0.2035430922658905</v>
       </c>
       <c r="G186" t="n">
-        <v>0.1692477804577638</v>
+        <v>0.2916330062463994</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="B187" t="n">
-        <v>0.002929941710991508</v>
+        <v>0.004020562483581533</v>
       </c>
       <c r="C187" t="n">
-        <v>0.3804473619030234</v>
+        <v>0.3874103166035587</v>
       </c>
       <c r="D187" t="n">
-        <v>0.4985579615032196</v>
+        <v>0.4560126245201219</v>
       </c>
       <c r="E187" t="n">
-        <v>2.184450869697534</v>
+        <v>2.349171821597319</v>
       </c>
       <c r="F187" t="n">
-        <v>0.1110665059806464</v>
+        <v>0.1997067951648189</v>
       </c>
       <c r="G187" t="n">
-        <v>0.1604286897243585</v>
+        <v>0.2876917160703636</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="B188" t="n">
-        <v>0.0028654804539424</v>
+        <v>0.003976622061708956</v>
       </c>
       <c r="C188" t="n">
-        <v>0.3800309073595836</v>
+        <v>0.3871344682629295</v>
       </c>
       <c r="D188" t="n">
-        <v>0.5010902668756103</v>
+        <v>0.4577596136298657</v>
       </c>
       <c r="E188" t="n">
-        <v>2.173575863068612</v>
+        <v>2.342280076205431</v>
       </c>
       <c r="F188" t="n">
-        <v>0.1060915161335595</v>
+        <v>0.1958069327227429</v>
       </c>
       <c r="G188" t="n">
-        <v>0.151326987007232</v>
+        <v>0.2835422920653313</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="B189" t="n">
-        <v>0.002800321193830968</v>
+        <v>0.003931368410558571</v>
       </c>
       <c r="C189" t="n">
-        <v>0.3796091754193923</v>
+        <v>0.3868500084466909</v>
       </c>
       <c r="D189" t="n">
-        <v>0.5036591281533126</v>
+        <v>0.4595480743665569</v>
       </c>
       <c r="E189" t="n">
-        <v>2.162495264111924</v>
+        <v>2.335162356184354</v>
       </c>
       <c r="F189" t="n">
-        <v>0.1010732986982822</v>
+        <v>0.1918444781423453</v>
       </c>
       <c r="G189" t="n">
-        <v>0.1419389609373924</v>
+        <v>0.2791810266903174</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="B190" t="n">
-        <v>0.002734494844901158</v>
+        <v>0.003884832471645782</v>
       </c>
       <c r="C190" t="n">
-        <v>0.379182332775052</v>
+        <v>0.3865571036739724</v>
       </c>
       <c r="D190" t="n">
-        <v>0.5062642491664282</v>
+        <v>0.4613777789812873</v>
       </c>
       <c r="E190" t="n">
-        <v>2.151210510252125</v>
+        <v>2.327822567262347</v>
       </c>
       <c r="F190" t="n">
-        <v>0.09601283147923446</v>
+        <v>0.187820404626309</v>
       </c>
       <c r="G190" t="n">
-        <v>0.132260900145849</v>
+        <v>0.2746042124043365</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="B191" t="n">
-        <v>0.002668032321396904</v>
+        <v>0.003837045186485998</v>
       </c>
       <c r="C191" t="n">
-        <v>0.3787505461191652</v>
+        <v>0.3862559204639035</v>
       </c>
       <c r="D191" t="n">
-        <v>0.5089053260379542</v>
+        <v>0.463248500241497</v>
       </c>
       <c r="E191" t="n">
-        <v>2.139723038913871</v>
+        <v>2.320264656723062</v>
       </c>
       <c r="F191" t="n">
-        <v>0.09091109228083569</v>
+        <v>0.1837356853773168</v>
       </c>
       <c r="G191" t="n">
-        <v>0.1222890932636099</v>
+        <v>0.2698081416664035</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="B192" t="n">
-        <v>0.002600964537562148</v>
+        <v>0.003788037496594627</v>
       </c>
       <c r="C192" t="n">
-        <v>0.3783139821443343</v>
+        <v>0.3859466253356137</v>
       </c>
       <c r="D192" t="n">
-        <v>0.5115820467777756</v>
+        <v>0.4651600110117588</v>
       </c>
       <c r="E192" t="n">
-        <v>2.128034287521819</v>
+        <v>2.312492610656168</v>
       </c>
       <c r="F192" t="n">
-        <v>0.08576905890750597</v>
+        <v>0.1795912935980515</v>
       </c>
       <c r="G192" t="n">
-        <v>0.1120198289216845</v>
+        <v>0.2647891069355333</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="B193" t="n">
-        <v>0.002533322407640827</v>
+        <v>0.003737840343487074</v>
       </c>
       <c r="C193" t="n">
-        <v>0.3778728075431615</v>
+        <v>0.3856293848082326</v>
       </c>
       <c r="D193" t="n">
-        <v>0.5142940908771821</v>
+        <v>0.4671120838361776</v>
       </c>
       <c r="E193" t="n">
-        <v>2.116145693500624</v>
+        <v>2.304510451225887</v>
       </c>
       <c r="F193" t="n">
-        <v>0.08058770916366453</v>
+        <v>0.175388202491196</v>
       </c>
       <c r="G193" t="n">
-        <v>0.1014493957510806</v>
+        <v>0.2595434006707405</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="B194" t="n">
-        <v>0.002465136845876882</v>
+        <v>0.00368648466867875</v>
       </c>
       <c r="C194" t="n">
-        <v>0.3774271890082495</v>
+        <v>0.3853043654008896</v>
       </c>
       <c r="D194" t="n">
-        <v>0.5170411289039835</v>
+        <v>0.4691044905222316</v>
       </c>
       <c r="E194" t="n">
-        <v>2.104058694274944</v>
+        <v>2.296322233959506</v>
       </c>
       <c r="F194" t="n">
-        <v>0.07536802085373151</v>
+        <v>0.1711273852594332</v>
       </c>
       <c r="G194" t="n">
-        <v>0.09057408238280779</v>
+        <v>0.2540673153310402</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="B195" t="n">
-        <v>0.002396438766514252</v>
+        <v>0.003634001413685058</v>
       </c>
       <c r="C195" t="n">
-        <v>0.3769772932322006</v>
+        <v>0.3849717336327144</v>
       </c>
       <c r="D195" t="n">
-        <v>0.519822822098311</v>
+        <v>0.4711370017258962</v>
       </c>
       <c r="E195" t="n">
-        <v>2.091774727269435</v>
+        <v>2.287932045057824</v>
       </c>
       <c r="F195" t="n">
-        <v>0.0701109717821264</v>
+        <v>0.1668098151054458</v>
       </c>
       <c r="G195" t="n">
-        <v>0.07939017744787437</v>
+        <v>0.2483571433754467</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="B196" t="n">
-        <v>0.002327259083796873</v>
+        <v>0.003580421520021409</v>
       </c>
       <c r="C196" t="n">
-        <v>0.3765232869076171</v>
+        <v>0.3846316560228363</v>
       </c>
       <c r="D196" t="n">
-        <v>0.5226388219692097</v>
+        <v>0.4732093865379031</v>
       </c>
       <c r="E196" t="n">
-        <v>2.079295229908752</v>
+        <v>2.279343998729499</v>
       </c>
       <c r="F196" t="n">
-        <v>0.06481753975326864</v>
+        <v>0.1624364652319166</v>
       </c>
       <c r="G196" t="n">
-        <v>0.06789396957728853</v>
+        <v>0.2424091772629752</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="B197" t="n">
-        <v>0.002257628711968688</v>
+        <v>0.003525775929203207</v>
       </c>
       <c r="C197" t="n">
-        <v>0.3760653367271016</v>
+        <v>0.384284299090385</v>
       </c>
       <c r="D197" t="n">
-        <v>0.5254887698921329</v>
+        <v>0.4753214120710007</v>
       </c>
       <c r="E197" t="n">
-        <v>2.066621639617551</v>
+        <v>2.270562234551109</v>
       </c>
       <c r="F197" t="n">
-        <v>0.05948870257157833</v>
+        <v>0.1580083088415287</v>
       </c>
       <c r="G197" t="n">
-        <v>0.05608174740205991</v>
+        <v>0.2362197094526404</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="B198" t="n">
-        <v>0.002187578565273632</v>
+        <v>0.003470095582745861</v>
       </c>
       <c r="C198" t="n">
-        <v>0.3756036093832564</v>
+        <v>0.3839298293544899</v>
       </c>
       <c r="D198" t="n">
-        <v>0.5283722967074692</v>
+        <v>0.4774728430480934</v>
       </c>
       <c r="E198" t="n">
-        <v>2.05375539382049</v>
+        <v>2.261590914854753</v>
       </c>
       <c r="F198" t="n">
-        <v>0.05412543804147478</v>
+        <v>0.1535263191369646</v>
       </c>
       <c r="G198" t="n">
-        <v>0.04394979955319628</v>
+        <v>0.229785032403457</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="B199" t="n">
-        <v>0.002117139557955649</v>
+        <v>0.003413411422164779</v>
       </c>
       <c r="C199" t="n">
-        <v>0.3751382715686839</v>
+        <v>0.3835684133342806</v>
       </c>
       <c r="D199" t="n">
-        <v>0.5312890223202409</v>
+        <v>0.4796634413911488</v>
       </c>
       <c r="E199" t="n">
-        <v>2.040697929942224</v>
+        <v>2.2524342221449</v>
       </c>
       <c r="F199" t="n">
-        <v>0.0487287239673781</v>
+        <v>0.1489914693209075</v>
       </c>
       <c r="G199" t="n">
-        <v>0.03149441466170727</v>
+        <v>0.22310143857444</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="B200" t="n">
-        <v>0.002046342604258673</v>
+        <v>0.003355754388975367</v>
       </c>
       <c r="C200" t="n">
-        <v>0.3746694899759866</v>
+        <v>0.3832002175488866</v>
       </c>
       <c r="D200" t="n">
-        <v>0.5342385553011296</v>
+        <v>0.4818929658107772</v>
       </c>
       <c r="E200" t="n">
-        <v>2.027450685407409</v>
+        <v>2.243096356546145</v>
       </c>
       <c r="F200" t="n">
-        <v>0.04329953815370746</v>
+        <v>0.1444047325960399</v>
       </c>
       <c r="G200" t="n">
-        <v>0.01871188135860051</v>
+        <v>0.2161652204246039</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="B201" t="n">
-        <v>0.001975218618426648</v>
+        <v>0.003297155424693032</v>
       </c>
       <c r="C201" t="n">
-        <v>0.3741974312977668</v>
+        <v>0.3828254085174374</v>
       </c>
       <c r="D201" t="n">
-        <v>0.5372204924889941</v>
+        <v>0.4841611713963962</v>
       </c>
       <c r="E201" t="n">
-        <v>2.014015097640702</v>
+        <v>2.233581533283474</v>
       </c>
       <c r="F201" t="n">
-        <v>0.0378388584048831</v>
+        <v>0.139767082165045</v>
       </c>
       <c r="G201" t="n">
-        <v>0.005598488274885821</v>
+        <v>0.2089726704129638</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
+        <v>2</v>
+      </c>
+      <c r="B202" t="n">
+        <v>0.003237645470833183</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0.3824441527590625</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0.4864678092069071</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2.223893980196542</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0.1350794912306053</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0.2015200809985344</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="B203" t="n">
+        <v>0.003177255468911224</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.3820566167928914</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0.4888126258618243</v>
+      </c>
+      <c r="E203" t="n">
+        <v>2.214037935289444</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0.1303429329954037</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0.1938037446403302</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="B204" t="n">
+        <v>0.003116016360442568</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0.3816629671380537</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.4911953631328062</v>
+      </c>
+      <c r="E204" t="n">
+        <v>2.204017644317339</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0.1255583806621233</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0.1858199537973666</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="B205" t="n">
+        <v>0.003053959086942616</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.3812633703136789</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.4936157575355529</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2.193837358411261</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0.1207268074334467</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0.1775650009286577</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="B206" t="n">
+        <v>0.002991114589926781</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.3808579928388964</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.4960735399220466</v>
+      </c>
+      <c r="E206" t="n">
+        <v>2.18350133174237</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0.1158491865120569</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0.1690351784932191</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="B207" t="n">
+        <v>0.002927513810910467</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0.3804470012328359</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0.4985684350731211</v>
+      </c>
+      <c r="E207" t="n">
+        <v>2.173013819226805</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0.1109264911006367</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0.1602267789500651</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="B208" t="n">
+        <v>0.00286318769140908</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.3800305620146268</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.5011001612913631</v>
+      </c>
+      <c r="E208" t="n">
+        <v>2.162379074272283</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0.1059596944018687</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0.1511360947582102</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="B209" t="n">
+        <v>0.002798167172938031</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.3796088417033986</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.5036684299943567</v>
+      </c>
+      <c r="E209" t="n">
+        <v>2.151601346567463</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.1009497696184361</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0.1417594183766699</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="B210" t="n">
+        <v>0.002732483197012722</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0.379182006818281</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.5062729453082966</v>
+      </c>
+      <c r="E210" t="n">
+        <v>2.140684879915063</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.09589768995302132</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0.1320930422644583</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="B211" t="n">
+        <v>0.002666166705148567</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0.3787502238784033</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.5089134036620093</v>
+      </c>
+      <c r="E211" t="n">
+        <v>2.129633910109663</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0.09080442860830773</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0.1221332588805909</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="B212" t="n">
+        <v>0.002599248638860968</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0.3783136594028951</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.5115894933814306</v>
+      </c>
+      <c r="E212" t="n">
+        <v>2.118452662861004</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0.08567095878697764</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0.1118763606840818</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="B213" t="n">
+        <v>0.002531759939665336</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.3778724799108861</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.5143008942846031</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2.107145351763599</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.08049825369171441</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0.1013186401339465</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="B214" t="n">
+        <v>0.002463731549077073</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.3774268519215054</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.5170472772772727</v>
+      </c>
+      <c r="E214" t="n">
+        <v>2.095716176313349</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0.07528728652520034</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0.09045638968919895</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="B215" t="n">
+        <v>0.002395194408611594</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.3769769419538828</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.5198283039491657</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2.084169319971841</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0.07003903049011881</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0.07928590180885493</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="B216" t="n">
+        <v>0.002326179459784299</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0.3765229165271478</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0.522643626171056</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2.072508948278887</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0.06475445878915215</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0.06780346895192832</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="B217" t="n">
+        <v>0.0022567176441106</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0.37606494216043</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.5254928856927308</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2.060739207013864</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0.0594345446249837</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0.05600538357743479</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="B218" t="n">
+        <v>0.002186839903105901</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.3756031853728587</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0.5283757137419859</v>
+      </c>
+      <c r="E218" t="n">
+        <v>2.048864220406306</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0.0540802612002958</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0.04388793814438817</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="B219" t="n">
+        <v>0.002116577178285613</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.3751378126835636</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0.5312917306247874</v>
+      </c>
+      <c r="E219" t="n">
+        <v>2.03688808939615</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0.04869258171777177</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0.0314474251118043</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="B220" t="n">
+        <v>0.002045960411165139</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.3746689906116741</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0.5342405453267579</v>
+      </c>
+      <c r="E220" t="n">
+        <v>2.024814889944003</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0.04327247938009401</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0.0186801369386969</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="B221" t="n">
+        <v>0.001975020543259891</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0.3741968856763198</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0.53722175511615</v>
+      </c>
+      <c r="E221" t="n">
+        <v>2.0126486713917</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0.03782092738994575</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0.005582366084081858</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
         <v>2.2</v>
       </c>
-      <c r="B202" t="n">
-        <v>0.001903798514703507</v>
-      </c>
-      <c r="C202" t="n">
-        <v>0.373722262226627</v>
-      </c>
-      <c r="D202" t="n">
-        <v>0.5402344185950634</v>
-      </c>
-      <c r="E202" t="n">
-        <v>2.000392604066759</v>
-      </c>
-      <c r="F202" t="n">
-        <v>0.03234766252532421</v>
-      </c>
-      <c r="G202" t="n">
-        <v>-0.007849475958429192</v>
+      <c r="B222" t="n">
+        <v>0.001903788516085271</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.3737216643966301</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0.5402349451484891</v>
+      </c>
+      <c r="E222" t="n">
+        <v>2.000393454873399</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0.03233889895000948</v>
+      </c>
+      <c r="G222" t="n">
+        <v>-0.007849594993027093</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="B223" t="n">
+        <v>0.001832295271156691</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0.3732434932917347</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0.5432796880730787</v>
+      </c>
+      <c r="E223" t="n">
+        <v>1.988053231777394</v>
+      </c>
+      <c r="F223" t="n">
+        <v>0.026383949884318</v>
+      </c>
+      <c r="G223" t="n">
+        <v>-0.02126211569257381</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="B224" t="n">
+        <v>0.001760571749989555</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.3727625388807631</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.5463555436415746</v>
+      </c>
+      <c r="E224" t="n">
+        <v>1.975631962258753</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0.02058942464595126</v>
+      </c>
+      <c r="G224" t="n">
+        <v>-0.03455951915396722</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="B225" t="n">
+        <v>0.001688648894099273</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.3722789676828446</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.5494620583188476</v>
+      </c>
+      <c r="E225" t="n">
+        <v>1.963133573802875</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0.01495302877867738</v>
+      </c>
+      <c r="G225" t="n">
+        <v>-0.04774001220253644</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="B226" t="n">
+        <v>0.001616557645001249</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.3717929462171089</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.5525987648963708</v>
+      </c>
+      <c r="E226" t="n">
+        <v>1.950561959839961</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0.009472461706754472</v>
+      </c>
+      <c r="G226" t="n">
+        <v>-0.06080186607137539</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="B227" t="n">
+        <v>0.001544328944210895</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0.3713046410026855</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.5557651821083731</v>
+      </c>
+      <c r="E227" t="n">
+        <v>1.937920978410401</v>
+      </c>
+      <c r="F227" t="n">
+        <v>0.004145418447373757</v>
+      </c>
+      <c r="G227" t="n">
+        <v>-0.07374341616057041</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="B228" t="n">
+        <v>0.001471993733243612</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.3708142185587039</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.5589608142510275</v>
+      </c>
+      <c r="E228" t="n">
+        <v>1.925214450880952</v>
+      </c>
+      <c r="F228" t="n">
+        <v>-0.001030408750617523</v>
+      </c>
+      <c r="G228" t="n">
+        <v>-0.08656306174776082</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="B229" t="n">
+        <v>0.001399582953614815</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.3703218454042936</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.5621851508049396</v>
+      </c>
+      <c r="E229" t="n">
+        <v>1.912446160711635</v>
+      </c>
+      <c r="F229" t="n">
+        <v>-0.00605732883935753</v>
+      </c>
+      <c r="G229" t="n">
+        <v>-0.09925926565259709</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="B230" t="n">
+        <v>0.001327127546839903</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.3698276880585842</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.565437666061231</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1.899619852273121</v>
+      </c>
+      <c r="F230" t="n">
+        <v>-0.01093765047369963</v>
+      </c>
+      <c r="G230" t="n">
+        <v>-0.1118305538576072</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="B231" t="n">
+        <v>0.001254658454434291</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.3693319130407052</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.5687178187515133</v>
+      </c>
+      <c r="E231" t="n">
+        <v>1.88673922971444</v>
+      </c>
+      <c r="F231" t="n">
+        <v>-0.01567368057980268</v>
+      </c>
+      <c r="G231" t="n">
+        <v>-0.1242755150878555</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="B232" t="n">
+        <v>0.001182206617913379</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0.3688346868697859</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.5720250516820715</v>
+      </c>
+      <c r="E232" t="n">
+        <v>1.873807955880713</v>
+      </c>
+      <c r="F232" t="n">
+        <v>-0.02026772298843024</v>
+      </c>
+      <c r="G232" t="n">
+        <v>-0.1365928003517304</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="B233" t="n">
+        <v>0.001109802978792581</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.3683361760649562</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.5753587913725806</v>
+      </c>
+      <c r="E233" t="n">
+        <v>1.860829651280634</v>
+      </c>
+      <c r="F233" t="n">
+        <v>-0.02472207713085327</v>
+      </c>
+      <c r="G233" t="n">
+        <v>-0.1487811224450746</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="B234" t="n">
+        <v>0.001037478478587302</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.3678365471453453</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.578718447699701</v>
+      </c>
+      <c r="E234" t="n">
+        <v>1.847807893103333</v>
+      </c>
+      <c r="F234" t="n">
+        <v>-0.02903903679532273</v>
+      </c>
+      <c r="G234" t="n">
+        <v>-0.1608392554208292</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="B235" t="n">
+        <v>0.0009652640588129449</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.3673359666300828</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.582103413545903</v>
+      </c>
+      <c r="E235" t="n">
+        <v>1.834746214284262</v>
+      </c>
+      <c r="F235" t="n">
+        <v>-0.03322088894212408</v>
+      </c>
+      <c r="G235" t="n">
+        <v>-0.1727660340262509</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="B236" t="n">
+        <v>0.0008931906609849233</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.3668346010382983</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.5855130644538912</v>
+      </c>
+      <c r="E236" t="n">
+        <v>1.821648102619682</v>
+      </c>
+      <c r="F236" t="n">
+        <v>-0.0372699125752882</v>
+      </c>
+      <c r="G236" t="n">
+        <v>-0.1845603531097054</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="B237" t="n">
+        <v>0.000821289226618639</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.3663326168891212</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.5889467582870082</v>
+      </c>
+      <c r="E237" t="n">
+        <v>1.808516999929273</v>
+      </c>
+      <c r="F237" t="n">
+        <v>-0.04118837766908742</v>
+      </c>
+      <c r="G237" t="n">
+        <v>-0.1962211669989655</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="B238" t="n">
+        <v>0.000749590697229506</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.3658301807016812</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.5924038348960119</v>
+      </c>
+      <c r="E238" t="n">
+        <v>1.795356301266423</v>
+      </c>
+      <c r="F238" t="n">
+        <v>-0.04497854414749188</v>
+      </c>
+      <c r="G238" t="n">
+        <v>-0.2077474888528537</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="B239" t="n">
+        <v>0.0006781260143329236</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.3653274589951076</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0.5958836157926339</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1.782169354175626</v>
+      </c>
+      <c r="F239" t="n">
+        <v>-0.04864266091482259</v>
+      </c>
+      <c r="G239" t="n">
+        <v>-0.2191383899880265</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="B240" t="n">
+        <v>0.0006069261194443063</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.3648246182885301</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.5993854038303349</v>
+      </c>
+      <c r="E240" t="n">
+        <v>1.768959457996486</v>
+      </c>
+      <c r="F240" t="n">
+        <v>-0.05218296493587714</v>
+      </c>
+      <c r="G240" t="n">
+        <v>-0.2303929991825999</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="B241" t="n">
+        <v>0.0005360219540790551</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.3643218251010781</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.6029084828926945</v>
+      </c>
+      <c r="E241" t="n">
+        <v>1.755729863213704</v>
+      </c>
+      <c r="F241" t="n">
+        <v>-0.05560168036386255</v>
+      </c>
+      <c r="G241" t="n">
+        <v>-0.241510501958281</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="B242" t="n">
+        <v>0.0004654444597525838</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.3638192459518811</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.6064521175898733</v>
+      </c>
+      <c r="E242" t="n">
+        <v>1.74248377085247</v>
+      </c>
+      <c r="F242" t="n">
+        <v>-0.0589010177145094</v>
+      </c>
+      <c r="G242" t="n">
+        <v>-0.2524901398425764</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="B243" t="n">
+        <v>0.0003952245779802925</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.3633170473600688</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.6100155529636093</v>
+      </c>
+      <c r="E243" t="n">
+        <v>1.729224331918598</v>
+      </c>
+      <c r="F243" t="n">
+        <v>-0.06208317308479426</v>
+      </c>
+      <c r="G243" t="n">
+        <v>-0.2633312096126186</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="B244" t="n">
+        <v>0.0003253932502775962</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.3628153958447705</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.6135980142012106</v>
+      </c>
+      <c r="E244" t="n">
+        <v>1.715954646882776</v>
+      </c>
+      <c r="F244" t="n">
+        <v>-0.06515032741473567</v>
+      </c>
+      <c r="G244" t="n">
+        <v>-0.2740330625220588</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="B245" t="n">
+        <v>0.0002559814181598958</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.3623144579251159</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.6171987063590301</v>
+      </c>
+      <c r="E245" t="n">
+        <v>1.702677765208202</v>
+      </c>
+      <c r="F245" t="n">
+        <v>-0.0681046457907815</v>
+      </c>
+      <c r="G245" t="n">
+        <v>-0.2845951035124499</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="B246" t="n">
+        <v>0.0001870200231426024</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.3618144001202344</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.6208168140959051</v>
+      </c>
+      <c r="E246" t="n">
+        <v>1.689396684920943</v>
+      </c>
+      <c r="F246" t="n">
+        <v>-0.0709482767893386</v>
+      </c>
+      <c r="G246" t="n">
+        <v>-0.2950167904104573</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="B247" t="n">
+        <v>0.0001185400067411197</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.3613153889492555</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.6244515014170725</v>
+      </c>
+      <c r="E247" t="n">
+        <v>1.676114352222263</v>
+      </c>
+      <c r="F247" t="n">
+        <v>-0.07368335185904651</v>
+      </c>
+      <c r="G247" t="n">
+        <v>-0.3052976331122084</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="B248" t="n">
+        <v>5.057231047086042e-05</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.3608175909313088</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.628101911429062</v>
+      </c>
+      <c r="E248" t="n">
+        <v>1.662833661142175</v>
+      </c>
+      <c r="F248" t="n">
+        <v>-0.07631198474043034</v>
+      </c>
+      <c r="G248" t="n">
+        <v>-0.3154371927560127</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="B249" t="n">
+        <v>-1.685212415277393e-05</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.3603211725855238</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0.6317671661060971</v>
+      </c>
+      <c r="E249" t="n">
+        <v>1.64955745323346</v>
+      </c>
+      <c r="F249" t="n">
+        <v>-0.07883627092161305</v>
+      </c>
+      <c r="G249" t="n">
+        <v>-0.3254350808846612</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="B250" t="n">
+        <v>-8.370235561437145e-05</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.35982630043103</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.6354463660685296</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1.63628851730537</v>
+      </c>
+      <c r="F250" t="n">
+        <v>-0.08125828712880107</v>
+      </c>
+      <c r="G250" t="n">
+        <v>-0.3352909585984361</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="B251" t="n">
+        <v>-0.0001499474423985289</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.359333140986957</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.6391385903738538</v>
+      </c>
+      <c r="E251" t="n">
+        <v>1.623029589196203</v>
+      </c>
+      <c r="F251" t="n">
+        <v>-0.08358009085029965</v>
+      </c>
+      <c r="G251" t="n">
+        <v>-0.3450045356999437</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="B252" t="n">
+        <v>-0.0002155564429898349</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.3588418607724341</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.6428428963208452</v>
+      </c>
+      <c r="E252" t="n">
+        <v>1.609783351583962</v>
+      </c>
+      <c r="F252" t="n">
+        <v>-0.08580371989284566</v>
+      </c>
+      <c r="G252" t="n">
+        <v>-0.3545755698318065</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="B253" t="n">
+        <v>-0.0002804984158728862</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.358352626306591</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.6465583192673856</v>
+      </c>
+      <c r="E253" t="n">
+        <v>1.596552433834254</v>
+      </c>
+      <c r="F253" t="n">
+        <v>-0.08793119196908668</v>
+      </c>
+      <c r="G253" t="n">
+        <v>-0.3640038656082374</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="B254" t="n">
+        <v>-0.0003447424195322695</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.3578656041085573</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.6502838724625365</v>
+      </c>
+      <c r="E254" t="n">
+        <v>1.583339411884601</v>
+      </c>
+      <c r="F254" t="n">
+        <v>-0.08996450431506378</v>
+      </c>
+      <c r="G254" t="n">
+        <v>-0.3732892737414463</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="B255" t="n">
+        <v>-0.0004082575124525877</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.3573809606974623</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.6540185468934375</v>
+      </c>
+      <c r="E255" t="n">
+        <v>1.570146808164321</v>
+      </c>
+      <c r="F255" t="n">
+        <v>-0.09190563333659574</v>
+      </c>
+      <c r="G255" t="n">
+        <v>-0.3824316901638122</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="B256" t="n">
+        <v>-0.0004710127531184233</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.3568988625924356</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.6577613111476045</v>
+      </c>
+      <c r="E256" t="n">
+        <v>1.556977091549114</v>
+      </c>
+      <c r="F256" t="n">
+        <v>-0.09375653428348835</v>
+      </c>
+      <c r="G256" t="n">
+        <v>-0.3914310551466936</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="B257" t="n">
+        <v>-0.0005329772000143753</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.3564194763126068</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0.6615111112912168</v>
+      </c>
+      <c r="E257" t="n">
+        <v>1.5438326773495</v>
+      </c>
+      <c r="F257" t="n">
+        <v>-0.09551914095053161</v>
+      </c>
+      <c r="G257" t="n">
+        <v>-0.4002873524167308</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="B258" t="n">
+        <v>-0.0005941199116250321</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.3559429683771053</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0.6652668707639797</v>
+      </c>
+      <c r="E258" t="n">
+        <v>1.530715927332235</v>
+      </c>
+      <c r="F258" t="n">
+        <v>-0.09719536540427152</v>
+      </c>
+      <c r="G258" t="n">
+        <v>-0.4090006082704307</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="B259" t="n">
+        <v>-0.0006544099464349858</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0.3554695053050607</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0.6690274902911606</v>
+      </c>
+      <c r="E259" t="n">
+        <v>1.51762914977383</v>
+      </c>
+      <c r="F259" t="n">
+        <v>-0.09878709773457996</v>
+      </c>
+      <c r="G259" t="n">
+        <v>-0.4175708906878186</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="B260" t="n">
+        <v>-0.000713816362928838</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.3549992536156025</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0.6727918478133927</v>
+      </c>
+      <c r="E260" t="n">
+        <v>1.504574599545294</v>
+      </c>
+      <c r="F260" t="n">
+        <v>-0.1002962058300706</v>
+      </c>
+      <c r="G260" t="n">
+        <v>-0.425998308445877</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="B261" t="n">
+        <v>-0.000772308219591171</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.3545323798278602</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0.6765587984348524</v>
+      </c>
+      <c r="E261" t="n">
+        <v>1.491554478227221</v>
+      </c>
+      <c r="F261" t="n">
+        <v>-0.1017245351764408</v>
+      </c>
+      <c r="G261" t="n">
+        <v>-0.4342830102324767</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="B262" t="n">
+        <v>-0.0008298545749065847</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.3540690504609634</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0.6803271743904095</v>
+      </c>
+      <c r="E262" t="n">
+        <v>1.478570934254332</v>
+      </c>
+      <c r="F262" t="n">
+        <v>-0.1030739086768455</v>
+      </c>
+      <c r="G262" t="n">
+        <v>-0.4424251837614669</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="B263" t="n">
+        <v>-0.0008864244873596668</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.3536094320340414</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0.6840957850323558</v>
+      </c>
+      <c r="E263" t="n">
+        <v>1.465626063088591</v>
+      </c>
+      <c r="F263" t="n">
+        <v>-0.100209438721653</v>
+      </c>
+      <c r="G263" t="n">
+        <v>-0.4325684474688244</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="B264" t="n">
+        <v>-0.0009419870154350127</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.353153691066224</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0.6878634168373192</v>
+      </c>
+      <c r="E264" t="n">
+        <v>1.452721907419995</v>
+      </c>
+      <c r="F264" t="n">
+        <v>-0.09714067712581528</v>
+      </c>
+      <c r="G264" t="n">
+        <v>-0.4217989285136419</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="B265" t="n">
+        <v>-0.0009965112176172127</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.3527019940766405</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0.691628833433964</v>
+      </c>
+      <c r="E265" t="n">
+        <v>1.439860457394183</v>
+      </c>
+      <c r="F265" t="n">
+        <v>-0.09414122105541313</v>
+      </c>
+      <c r="G265" t="n">
+        <v>-0.4112804300071782</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="B266" t="n">
+        <v>-0.001049966152390867</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.3522545075844205</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0.6953907756520814</v>
+      </c>
+      <c r="E266" t="n">
+        <v>1.427043650865935</v>
+      </c>
+      <c r="F266" t="n">
+        <v>-0.09121182379095374</v>
+      </c>
+      <c r="G266" t="n">
+        <v>-0.4010074161432302</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="B267" t="n">
+        <v>-0.001102320878240555</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.3518113981086936</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0.6991479615936705</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1.414273373677724</v>
+      </c>
+      <c r="F267" t="n">
+        <v>-0.08835291331993782</v>
+      </c>
+      <c r="G267" t="n">
+        <v>-0.3909745098475804</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="B268" t="n">
+        <v>-0.001153544453650882</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.3513728321685892</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0.7028990867266066</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1.401551459962405</v>
+      </c>
+      <c r="F268" t="n">
+        <v>-0.08556463727392825</v>
+      </c>
+      <c r="G268" t="n">
+        <v>-0.3811764811651222</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="B269" t="n">
+        <v>-0.001203605937106432</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.3509389762832369</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0.7066428240014851</v>
+      </c>
+      <c r="E269" t="n">
+        <v>1.3888796924692</v>
+      </c>
+      <c r="F269" t="n">
+        <v>-0.08284690183639441</v>
+      </c>
+      <c r="G269" t="n">
+        <v>-0.3716082371140338</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="B270" t="n">
+        <v>-0.001252474387091806</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.3505099969717661</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0.7103778239922324</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1.376259802912078</v>
+      </c>
+      <c r="F270" t="n">
+        <v>-0.0801994055102508</v>
+      </c>
+      <c r="G270" t="n">
+        <v>-0.362264812801412</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="B271" t="n">
+        <v>-0.001300118862091589</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.3500860607533065</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0.7141027150610552</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1.363693472339694</v>
+      </c>
+      <c r="F271" t="n">
+        <v>-0.07762166848799247</v>
+      </c>
+      <c r="G271" t="n">
+        <v>-0.3531413636255544</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="B272" t="n">
+        <v>-0.001346508420590379</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.3496673341469874</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0.7178161035483067</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1.351182331526005</v>
+      </c>
+      <c r="F272" t="n">
+        <v>-0.07511305824774057</v>
+      </c>
+      <c r="G272" t="n">
+        <v>-0.3442331584158304</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="B273" t="n">
+        <v>-0.001391612121072765</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.3492539836719385</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0.7215165739878244</v>
+      </c>
+      <c r="E273" t="n">
+        <v>1.338727961380736</v>
+      </c>
+      <c r="F273" t="n">
+        <v>-0.07267281190016886</v>
+      </c>
+      <c r="G273" t="n">
+        <v>-0.3355355733827997</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="B274" t="n">
+        <v>-0.001435399022023341</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.3488461758472892</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0.7252026893482932</v>
+      </c>
+      <c r="E274" t="n">
+        <v>1.326331893378834</v>
+      </c>
+      <c r="F274" t="n">
+        <v>-0.07030005573004865</v>
+      </c>
+      <c r="G274" t="n">
+        <v>-0.3270440867695026</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="B275" t="n">
+        <v>-0.001477838181926702</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.3484440771921691</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0.7288729913011716</v>
+      </c>
+      <c r="E275" t="n">
+        <v>1.313995610008086</v>
+      </c>
+      <c r="F275" t="n">
+        <v>-0.06799382230880366</v>
+      </c>
+      <c r="G275" t="n">
+        <v>-0.3187542741103346</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="B276" t="n">
+        <v>-0.001518898659267438</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.3480478542257077</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0.7325260005157073</v>
+      </c>
+      <c r="E276" t="n">
+        <v>1.301720545234076</v>
+      </c>
+      <c r="F276" t="n">
+        <v>-0.06575306549839793</v>
+      </c>
+      <c r="G276" t="n">
+        <v>-0.3106618040170064</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="B277" t="n">
+        <v>-0.001558549512530139</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.3476576734670345</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0.7361602169815511</v>
+      </c>
+      <c r="E277" t="n">
+        <v>1.289508084981656</v>
+      </c>
+      <c r="F277" t="n">
+        <v>-0.06357667362005065</v>
+      </c>
+      <c r="G277" t="n">
+        <v>-0.3027624344222561</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="B278" t="n">
+        <v>-0.001596759800199406</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.347273701435279</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0.7397741203594663</v>
+      </c>
+      <c r="E278" t="n">
+        <v>1.277359567632143</v>
+      </c>
+      <c r="F278" t="n">
+        <v>-0.06146348102199468</v>
+      </c>
+      <c r="G278" t="n">
+        <v>-0.2950520092214483</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="B279" t="n">
+        <v>-0.001633498580759825</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.3468961046495707</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0.7433661703606094</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1.265276284535421</v>
+      </c>
+      <c r="F279" t="n">
+        <v>-0.0594122782474695</v>
+      </c>
+      <c r="G279" t="n">
+        <v>-0.2875264552603213</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="B280" t="n">
+        <v>-0.001668734912695992</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.3465250496290392</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0.746934807154842</v>
+      </c>
+      <c r="E280" t="n">
+        <v>1.253259480536195</v>
+      </c>
+      <c r="F280" t="n">
+        <v>-0.05742182097624548</v>
+      </c>
+      <c r="G280" t="n">
+        <v>-0.2801817796240645</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="B281" t="n">
+        <v>-0.001702437854492493</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.3461607028928141</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0.7504784518085116</v>
+      </c>
+      <c r="E281" t="n">
+        <v>1.241310354513594</v>
+      </c>
+      <c r="F281" t="n">
+        <v>-0.05549083788937462</v>
+      </c>
+      <c r="G281" t="n">
+        <v>-0.2730140671888711</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="B282" t="n">
+        <v>-0.001734576464633932</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.3458032309600246</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0.7539955067521206</v>
+      </c>
+      <c r="E282" t="n">
+        <v>1.229430059933386</v>
+      </c>
+      <c r="F282" t="n">
+        <v>-0.0536180375868032</v>
+      </c>
+      <c r="G282" t="n">
+        <v>-0.266019478402213</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="B283" t="n">
+        <v>-0.001765119801604893</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.3454528003498006</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0.7574843562782729</v>
+      </c>
+      <c r="E283" t="n">
+        <v>1.217619705412045</v>
+      </c>
+      <c r="F283" t="n">
+        <v>-0.05180211467040503</v>
+      </c>
+      <c r="G283" t="n">
+        <v>-0.2591942472625079</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="B284" t="n">
+        <v>-0.00179403692388997</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.3451095775812714</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0.7609433670702743</v>
+      </c>
+      <c r="E284" t="n">
+        <v>1.205880355291928</v>
+      </c>
+      <c r="F284" t="n">
+        <v>-0.05004175509039519</v>
+      </c>
+      <c r="G284" t="n">
+        <v>-0.2525346794726309</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="B285" t="n">
+        <v>-0.001821296889973758</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0.3447737291735665</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0.7643708887617224</v>
+      </c>
+      <c r="E285" t="n">
+        <v>1.194213030226864</v>
+      </c>
+      <c r="F285" t="n">
+        <v>-0.04833564084058776</v>
+      </c>
+      <c r="G285" t="n">
+        <v>-0.2460371507450276</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="B286" t="n">
+        <v>-0.001846868758340852</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.3444454216458154</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0.7677652545274067</v>
+      </c>
+      <c r="E286" t="n">
+        <v>1.182618707777414</v>
+      </c>
+      <c r="F286" t="n">
+        <v>-0.04668245407722053</v>
+      </c>
+      <c r="G286" t="n">
+        <v>-0.2396981052390289</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="B287" t="n">
+        <v>-0.001870721587475838</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0.3441248215171478</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0.7711247817058048</v>
+      </c>
+      <c r="E287" t="n">
+        <v>1.171098323015126</v>
+      </c>
+      <c r="F287" t="n">
+        <v>-0.0450808807268207</v>
+      </c>
+      <c r="G287" t="n">
+        <v>-0.2335140541134291</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="B288" t="n">
+        <v>-0.001892824435863315</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0.3438120953066931</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0.7744477724534266</v>
+      </c>
+      <c r="E288" t="n">
+        <v>1.159652769135103</v>
+      </c>
+      <c r="F288" t="n">
+        <v>-0.04352961364060687</v>
+      </c>
+      <c r="G288" t="n">
+        <v>-0.2274815741795579</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="B289" t="n">
+        <v>-0.001913146361987869</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0.3435074095335808</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0.7777325144312358</v>
+      </c>
+      <c r="E289" t="n">
+        <v>1.148282898076203</v>
+      </c>
+      <c r="F289" t="n">
+        <v>-0.04202735534600667</v>
+      </c>
+      <c r="G289" t="n">
+        <v>-0.2215973066419238</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="B290" t="n">
+        <v>-0.001931656424334098</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0.3432109307169405</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0.7809772815233336</v>
+      </c>
+      <c r="E290" t="n">
+        <v>1.136989521148233</v>
+      </c>
+      <c r="F290" t="n">
+        <v>-0.04057282043988252</v>
+      </c>
+      <c r="G290" t="n">
+        <v>-0.2158579559151569</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="B291" t="n">
+        <v>-0.001948323681386595</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0.3429228253759016</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0.7841803345880607</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1.125773409665481</v>
+      </c>
+      <c r="F291" t="n">
+        <v>-0.03916473766284006</v>
+      </c>
+      <c r="G291" t="n">
+        <v>-0.2102602885073849</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="B292" t="n">
+        <v>-0.001963117191629952</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0.3426432600295937</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0.7873399222416345</v>
+      </c>
+      <c r="E292" t="n">
+        <v>1.114635295585981</v>
+      </c>
+      <c r="F292" t="n">
+        <v>-0.03780185168945875</v>
+      </c>
+      <c r="G292" t="n">
+        <v>-0.2048011319614367</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="B293" t="n">
+        <v>-0.00197600601354876</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0.3423724011971463</v>
+      </c>
+      <c r="D293" t="n">
+        <v>0.790454281674404</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1.10357587215588</v>
+      </c>
+      <c r="F293" t="n">
+        <v>-0.03648292466531342</v>
+      </c>
+      <c r="G293" t="n">
+        <v>-0.1994773738463384</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="B294" t="n">
+        <v>-0.00198695920562761</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0.3421104153976889</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0.7935216394997537</v>
+      </c>
+      <c r="E294" t="n">
+        <v>1.092595794558331</v>
+      </c>
+      <c r="F294" t="n">
+        <v>-0.03520673751818983</v>
+      </c>
+      <c r="G294" t="n">
+        <v>-0.19428596079254</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="B295" t="n">
+        <v>-0.001995945826351101</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.3418574691503511</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0.7965402126356642</v>
+      </c>
+      <c r="E295" t="n">
+        <v>1.081695680566311</v>
+      </c>
+      <c r="F295" t="n">
+        <v>-0.03397209106785048</v>
+      </c>
+      <c r="G295" t="n">
+        <v>-0.1892238975651272</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="B296" t="n">
+        <v>-0.002002934934203822</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.3416137289742623</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0.7995082092188748</v>
+      </c>
+      <c r="E296" t="n">
+        <v>1.07087611119883</v>
+      </c>
+      <c r="F296" t="n">
+        <v>-0.03277780695603782</v>
+      </c>
+      <c r="G296" t="n">
+        <v>-0.1842882461700257</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="B297" t="n">
+        <v>-0.002007895587670363</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0.3413793613885521</v>
+      </c>
+      <c r="D297" t="n">
+        <v>0.8024238295515689</v>
+      </c>
+      <c r="E297" t="n">
+        <v>1.060137631379937</v>
+      </c>
+      <c r="F297" t="n">
+        <v>-0.03162272841604441</v>
+      </c>
+      <c r="G297" t="n">
+        <v>-0.1794761249888323</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="B298" t="n">
+        <v>-0.00201079684523532</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.34115453291235</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0.8052852670804338</v>
+      </c>
+      <c r="E298" t="n">
+        <v>1.049480750600035</v>
+      </c>
+      <c r="F298" t="n">
+        <v>-0.03050572089910915</v>
+      </c>
+      <c r="G298" t="n">
+        <v>-0.1747847079384905</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="B299" t="n">
+        <v>-0.002011607765383283</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0.3409394100647855</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0.8080907094079276</v>
+      </c>
+      <c r="E299" t="n">
+        <v>1.038905943578946</v>
+      </c>
+      <c r="F299" t="n">
+        <v>-0.02942567257306101</v>
+      </c>
+      <c r="G299" t="n">
+        <v>-0.1702112236525107</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="B300" t="n">
+        <v>-0.002010297406598848</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.3407341593649882</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0.8108383393355091</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1.028413650930252</v>
+      </c>
+      <c r="F300" t="n">
+        <v>-0.02838149470701336</v>
+      </c>
+      <c r="G300" t="n">
+        <v>-0.1657529546808883</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="B301" t="n">
+        <v>-0.002006834827366608</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.3405389473320874</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0.8135263359385603</v>
+      </c>
+      <c r="E301" t="n">
+        <v>1.018004279826395</v>
+      </c>
+      <c r="F301" t="n">
+        <v>-0.02737212195447075</v>
+      </c>
+      <c r="G301" t="n">
+        <v>-0.1614072367062446</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>3</v>
+      </c>
+      <c r="B302" t="n">
+        <v>-0.002001189086171152</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.3403539404852129</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0.8161528756726596</v>
+      </c>
+      <c r="E302" t="n">
+        <v>1.007678204664084</v>
+      </c>
+      <c r="F302" t="n">
+        <v>-0.02639651254593554</v>
+      </c>
+      <c r="G302" t="n">
+        <v>-0.1571714577740692</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="B303" t="n">
+        <v>-0.001993329241497078</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0.3401793053434941</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0.8187161335108324</v>
+      </c>
+      <c r="E303" t="n">
+        <v>0.9974357677295335</v>
+      </c>
+      <c r="F303" t="n">
+        <v>-0.02545364840096426</v>
+      </c>
+      <c r="G303" t="n">
+        <v>-0.1530430575352272</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="B304" t="n">
+        <v>-0.00198322435182898</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.3400152084260604</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0.8212142841113332</v>
+      </c>
+      <c r="E304" t="n">
+        <v>0.9872772798631045</v>
+      </c>
+      <c r="F304" t="n">
+        <v>-0.02454253516861425</v>
+      </c>
+      <c r="G304" t="n">
+        <v>-0.1490195264991708</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="B305" t="n">
+        <v>-0.001970843475651437</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.3398618162520415</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0.8236455030154697</v>
+      </c>
+      <c r="E305" t="n">
+        <v>0.9772030211228973</v>
+      </c>
+      <c r="F305" t="n">
+        <v>-0.02366220220431709</v>
+      </c>
+      <c r="G305" t="n">
+        <v>-0.1450984052965155</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="B306" t="n">
+        <v>-0.001956155671449055</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.3397192953405668</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0.8260079678749215</v>
+      </c>
+      <c r="E306" t="n">
+        <v>0.9672132414469018</v>
+      </c>
+      <c r="F306" t="n">
+        <v>-0.02281170249041166</v>
+      </c>
+      <c r="G306" t="n">
+        <v>-0.1412772839498527</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="B307" t="n">
+        <v>-0.001939129997706422</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.3395878122107658</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0.8282998597079499</v>
+      </c>
+      <c r="E307" t="n">
+        <v>0.9573081613132908</v>
+      </c>
+      <c r="F307" t="n">
+        <v>-0.02199011250684679</v>
+      </c>
+      <c r="G307" t="n">
+        <v>-0.1375538011518426</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="B308" t="n">
+        <v>-0.001919735512908135</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.3394675333817682</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0.8305193641838325</v>
+      </c>
+      <c r="E308" t="n">
+        <v>0.9474879723984803</v>
+      </c>
+      <c r="F308" t="n">
+        <v>-0.02119653205792059</v>
+      </c>
+      <c r="G308" t="n">
+        <v>-0.1339256435497958</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="B309" t="n">
+        <v>-0.00189794127553878</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0.3393586253727034</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0.8326646729348064</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0.937752838232575</v>
+      </c>
+      <c r="F309" t="n">
+        <v>-0.02043008406034197</v>
+      </c>
+      <c r="G309" t="n">
+        <v>-0.1303905450360813</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="B310" t="n">
+        <v>-0.001873716344082951</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.3392612547027009</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0.8347339848947379</v>
+      </c>
+      <c r="E310" t="n">
+        <v>0.9281028948518552</v>
+      </c>
+      <c r="F310" t="n">
+        <v>-0.01968991429738265</v>
+      </c>
+      <c r="G310" t="n">
+        <v>-0.1269462860438281</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="B311" t="n">
+        <v>-0.001847029777025246</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0.3391755878908902</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0.8367255076636819</v>
+      </c>
+      <c r="E311" t="n">
+        <v>0.9185382514479443</v>
+      </c>
+      <c r="F311" t="n">
+        <v>-0.01897519114341889</v>
+      </c>
+      <c r="G311" t="n">
+        <v>-0.1235906928474837</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="B312" t="n">
+        <v>-0.001817850632850254</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0.3391017914564008</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0.8386374588974262</v>
+      </c>
+      <c r="E312" t="n">
+        <v>0.9090589910133489</v>
+      </c>
+      <c r="F312" t="n">
+        <v>-0.01828510526274327</v>
+      </c>
+      <c r="G312" t="n">
+        <v>-0.1203216368678954</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="B313" t="n">
+        <v>-0.001786147970042569</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0.3390400319183624</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0.8404680677210662</v>
+      </c>
+      <c r="E313" t="n">
+        <v>0.8996651709830384</v>
+      </c>
+      <c r="F313" t="n">
+        <v>-0.01761886928614691</v>
+      </c>
+      <c r="G313" t="n">
+        <v>-0.1171370339816513</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="B314" t="n">
+        <v>-0.001751890847086775</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0.3389904757959043</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0.8422155761655818</v>
+      </c>
+      <c r="E314" t="n">
+        <v>0.8903568238717714</v>
+      </c>
+      <c r="F314" t="n">
+        <v>-0.01697571746843145</v>
+      </c>
+      <c r="G314" t="n">
+        <v>-0.114034843834491</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="B315" t="n">
+        <v>-0.001715048322467484</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0.3389532896081561</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0.8438782406263403</v>
+      </c>
+      <c r="E315" t="n">
+        <v>0.8811339579068793</v>
+      </c>
+      <c r="F315" t="n">
+        <v>-0.01635490532970233</v>
+      </c>
+      <c r="G315" t="n">
+        <v>-0.1110130691586608</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="B316" t="n">
+        <v>-0.001675589454669269</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0.3389286398742474</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0.8454543333423723</v>
+      </c>
+      <c r="E316" t="n">
+        <v>0.8719965576562299</v>
+      </c>
+      <c r="F316" t="n">
+        <v>-0.01575570928301482</v>
+      </c>
+      <c r="G316" t="n">
+        <v>-0.1080697550941293</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="B317" t="n">
+        <v>-0.001633483302176733</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.3389166931133076</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0.846942143895219</v>
+      </c>
+      <c r="E317" t="n">
+        <v>0.8629445846511132</v>
+      </c>
+      <c r="F317" t="n">
+        <v>-0.01517742625069442</v>
+      </c>
+      <c r="G317" t="n">
+        <v>-0.1052029885136381</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="B318" t="n">
+        <v>-0.001588698923474473</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0.3389176158444662</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0.8483399807260823</v>
+      </c>
+      <c r="E318" t="n">
+        <v>0.8539779780037938</v>
+      </c>
+      <c r="F318" t="n">
+        <v>-0.01461937327142272</v>
+      </c>
+      <c r="G318" t="n">
+        <v>-0.1024108973515851</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="B319" t="n">
+        <v>-0.001541205377047071</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0.3389315745868529</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0.8496461726699438</v>
+      </c>
+      <c r="E319" t="n">
+        <v>0.845096655019502</v>
+      </c>
+      <c r="F319" t="n">
+        <v>-0.01408088709997578</v>
+      </c>
+      <c r="G319" t="n">
+        <v>-0.09969164993678452</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="B320" t="n">
+        <v>-0.00149097172137912</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0.338958735859597</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0.8508590705052673</v>
+      </c>
+      <c r="E320" t="n">
+        <v>0.8363005118026277</v>
+      </c>
+      <c r="F320" t="n">
+        <v>-0.01356132380131266</v>
+      </c>
+      <c r="G320" t="n">
+        <v>-0.09704345432916227</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="B321" t="n">
+        <v>-0.001437967014955223</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0.3389992661818282</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0.8519770485178274</v>
+      </c>
+      <c r="E321" t="n">
+        <v>0.8275894238569186</v>
+      </c>
+      <c r="F321" t="n">
+        <v>-0.01306005834054366</v>
+      </c>
+      <c r="G321" t="n">
+        <v>-0.09446455766047884</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="B322" t="n">
+        <v>-0.001382160316259956</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0.3390533320726759</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0.852998506077156</v>
+      </c>
+      <c r="E322" t="n">
+        <v>0.8189632466794695</v>
+      </c>
+      <c r="F322" t="n">
+        <v>-0.01257648417015213</v>
+      </c>
+      <c r="G322" t="n">
+        <v>-0.09195324547918064</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="B323" t="n">
+        <v>-0.001323520683777935</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0.3391211000512697</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0.853921869224034</v>
+      </c>
+      <c r="E323" t="n">
+        <v>0.8104218163483259</v>
+      </c>
+      <c r="F323" t="n">
+        <v>-0.01211001281570531</v>
+      </c>
+      <c r="G323" t="n">
+        <v>-0.08950784109950385</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="B324" t="n">
+        <v>-0.001262017175993731</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0.3392027366367391</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0.8547455922673998</v>
+      </c>
+      <c r="E324" t="n">
+        <v>0.8019649501035128</v>
+      </c>
+      <c r="F324" t="n">
+        <v>-0.01166007346116063</v>
+      </c>
+      <c r="G324" t="n">
+        <v>-0.08712670495495999</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="B325" t="n">
+        <v>-0.001197618851391951</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0.3392984083482135</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0.8554681593889829</v>
+      </c>
+      <c r="E325" t="n">
+        <v>0.7935924469213355</v>
+      </c>
+      <c r="F325" t="n">
+        <v>-0.01122611253476028</v>
+      </c>
+      <c r="G325" t="n">
+        <v>-0.08480823395634714</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="B326" t="n">
+        <v>-0.00113029476845718</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0.3394082817048225</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0.8560880862539262</v>
+      </c>
+      <c r="E326" t="n">
+        <v>0.7853040880817838</v>
+      </c>
+      <c r="F326" t="n">
+        <v>-0.01080759329639971</v>
+      </c>
+      <c r="G326" t="n">
+        <v>-0.08255086085443164</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="B327" t="n">
+        <v>-0.001060013985674013</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0.3395325232256957</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0.8566039216255894</v>
+      </c>
+      <c r="E327" t="n">
+        <v>0.7770996377289113</v>
+      </c>
+      <c r="F327" t="n">
+        <v>-0.0104039954272618</v>
+      </c>
+      <c r="G327" t="n">
+        <v>-0.08035305360745588</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="B328" t="n">
+        <v>-0.0009867455615270408</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0.3396712994299625</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0.8570142489826894</v>
+      </c>
+      <c r="E328" t="n">
+        <v>0.7689788434240376</v>
+      </c>
+      <c r="F328" t="n">
+        <v>-0.01001481462242002</v>
+      </c>
+      <c r="G328" t="n">
+        <v>-0.07821331475362321</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="B329" t="n">
+        <v>-0.0009104585545008648</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0.3398247768367525</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0.8573176881368665</v>
+      </c>
+      <c r="E329" t="n">
+        <v>0.7609414366916679</v>
+      </c>
+      <c r="F329" t="n">
+        <v>-0.009639562187035563</v>
+      </c>
+      <c r="G329" t="n">
+        <v>-0.07613018078871919</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="B330" t="n">
+        <v>-0.0008311220230800623</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0.3399931219651952</v>
+      </c>
+      <c r="D330" t="n">
+        <v>0.8575128968487246</v>
+      </c>
+      <c r="E330" t="n">
+        <v>0.7529871335580017</v>
+      </c>
+      <c r="F330" t="n">
+        <v>-0.00927776463670075</v>
+      </c>
+      <c r="G330" t="n">
+        <v>-0.07410222154902107</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="B331" t="n">
+        <v>-0.0007487050257492418</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0.3401765013344201</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0.8575985724403433</v>
+      </c>
+      <c r="E331" t="n">
+        <v>0.7451156350819369</v>
+      </c>
+      <c r="F331" t="n">
+        <v>-0.008928963302415752</v>
+      </c>
+      <c r="G331" t="n">
+        <v>-0.07212803959965165</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="B332" t="n">
+        <v>-0.0006631766209929842</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0.3403750814635567</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0.8575734534022096</v>
+      </c>
+      <c r="E332" t="n">
+        <v>0.7373266278784664</v>
+      </c>
+      <c r="F332" t="n">
+        <v>-0.008592713940625373</v>
+      </c>
+      <c r="G332" t="n">
+        <v>-0.07020626962852562</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="B333" t="n">
+        <v>-0.0005745058672958908</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0.3405890288717345</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0.857436320992476</v>
+      </c>
+      <c r="E333" t="n">
+        <v>0.7296197846343923</v>
+      </c>
+      <c r="F333" t="n">
+        <v>-0.008268586348688982</v>
+      </c>
+      <c r="G333" t="n">
+        <v>-0.06833557784603769</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="B334" t="n">
+        <v>-0.0004826618231425425</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0.3408185100780832</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0.8571860008264126</v>
+      </c>
+      <c r="E334" t="n">
+        <v>0.7219947646162675</v>
+      </c>
+      <c r="F334" t="n">
+        <v>-0.007956163986106006</v>
+      </c>
+      <c r="G334" t="n">
+        <v>-0.06651466139063179</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="B335" t="n">
+        <v>-0.0003876135470175478</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0.3410636916017321</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0.8568213644538755</v>
+      </c>
+      <c r="E335" t="n">
+        <v>0.7144512141705125</v>
+      </c>
+      <c r="F335" t="n">
+        <v>-0.007655043601775578</v>
+      </c>
+      <c r="G335" t="n">
+        <v>-0.06474224774039172</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="B336" t="n">
+        <v>-0.0002893300974054977</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0.3413247399618107</v>
+      </c>
+      <c r="D336" t="n">
+        <v>0.8563413309225821</v>
+      </c>
+      <c r="E336" t="n">
+        <v>0.7069887672156333</v>
+      </c>
+      <c r="F336" t="n">
+        <v>-0.007364834867526762</v>
+      </c>
+      <c r="G336" t="n">
+        <v>-0.06301709413078158</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="B337" t="n">
+        <v>-0.0001877805327909626</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0.3416018216774487</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0.8557448683249477</v>
+      </c>
+      <c r="E337" t="n">
+        <v>0.6996070457265002</v>
+      </c>
+      <c r="F337" t="n">
+        <v>-0.007085160018119241</v>
+      </c>
+      <c r="G337" t="n">
+        <v>-0.06133798697866318</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="B338" t="n">
+        <v>-8.293391165856492e-05</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0.3418951032677755</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0.8550309953262092</v>
+      </c>
+      <c r="E338" t="n">
+        <v>0.6923056602106414</v>
+      </c>
+      <c r="F338" t="n">
+        <v>-0.006815653497880133</v>
+      </c>
+      <c r="G338" t="n">
+        <v>-0.05970374131270872</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="B339" t="n">
+        <v>2.524070750712856e-05</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0.3422047512519207</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0.8541987826715347</v>
+      </c>
+      <c r="E339" t="n">
+        <v>0.6850842101765109</v>
+      </c>
+      <c r="F339" t="n">
+        <v>-0.00655596161411153</v>
+      </c>
+      <c r="G339" t="n">
+        <v>-0.05811320021031935</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="B340" t="n">
+        <v>0.0001367742662215024</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0.3425309321490138</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0.8532473546697892</v>
+      </c>
+      <c r="E340" t="n">
+        <v>0.6779422845937106</v>
+      </c>
+      <c r="F340" t="n">
+        <v>-0.006305742197376014</v>
+      </c>
+      <c r="G340" t="n">
+        <v>-0.05656523424115616</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="B341" t="n">
+        <v>0.0002516977059999793</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0.3428738124781843</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0.8521758906516105</v>
+      </c>
+      <c r="E341" t="n">
+        <v>0.6708794623451388</v>
+      </c>
+      <c r="F341" t="n">
+        <v>-0.006064664268741227</v>
+      </c>
+      <c r="G341" t="n">
+        <v>-0.05505874091737927</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="B342" t="n">
+        <v>0.0003700419683579544</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.3432335587585615</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0.8509836263994326</v>
+      </c>
+      <c r="E342" t="n">
+        <v>0.6638953126710589</v>
+      </c>
+      <c r="F342" t="n">
+        <v>-0.005832407714042341</v>
+      </c>
+      <c r="G342" t="n">
+        <v>-0.05359264415068738</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="B343" t="n">
+        <v>0.0004918379948108537</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0.3436103375092754</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0.8496698555470741</v>
+      </c>
+      <c r="E343" t="n">
+        <v>0.6569893956050701</v>
+      </c>
+      <c r="F343" t="n">
+        <v>-0.005608662965199671</v>
+      </c>
+      <c r="G343" t="n">
+        <v>-0.05216589371623787</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="B344" t="n">
+        <v>0.0006171167268740653</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0.3440043152494551</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0.8482339309465131</v>
+      </c>
+      <c r="E344" t="n">
+        <v>0.6501612624019932</v>
+      </c>
+      <c r="F344" t="n">
+        <v>-0.00539313068861066</v>
+      </c>
+      <c r="G344" t="n">
+        <v>-0.05077746472352606</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="B345" t="n">
+        <v>0.0007459091060630085</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0.3444156584982303</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0.8466752659994441</v>
+      </c>
+      <c r="E345" t="n">
+        <v>0.6434104559576628</v>
+      </c>
+      <c r="F345" t="n">
+        <v>-0.005185521480617574</v>
+      </c>
+      <c r="G345" t="n">
+        <v>-0.04942635709428842</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="B346" t="n">
+        <v>0.0008782460738930853</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0.3448445337747305</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0.8449933359512334</v>
+      </c>
+      <c r="E346" t="n">
+        <v>0.6367365112206514</v>
+      </c>
+      <c r="F346" t="n">
+        <v>-0.004985555570037793</v>
+      </c>
+      <c r="G346" t="n">
+        <v>-0.04811159504749353</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="B347" t="n">
+        <v>0.001014158571879697</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0.3452911075980851</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0.8431876791448767</v>
+      </c>
+      <c r="E347" t="n">
+        <v>0.6301389555959289</v>
+      </c>
+      <c r="F347" t="n">
+        <v>-0.004792962527729013</v>
+      </c>
+      <c r="G347" t="n">
+        <v>-0.04683222659147147</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="B348" t="n">
+        <v>0.001153677541538264</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0.3457555464874238</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0.8412578982325754</v>
+      </c>
+      <c r="E348" t="n">
+        <v>0.6236173093404941</v>
+      </c>
+      <c r="F348" t="n">
+        <v>-0.004607480983149902</v>
+      </c>
+      <c r="G348" t="n">
+        <v>-0.04558732302323055</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="B349" t="n">
+        <v>0.001296833924384184</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0.3462380169618761</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0.8392036613425619</v>
+      </c>
+      <c r="E349" t="n">
+        <v>0.6171710859509937</v>
+      </c>
+      <c r="F349" t="n">
+        <v>-0.004428858347865233</v>
+      </c>
+      <c r="G349" t="n">
+        <v>-0.04437597843499851</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="B350" t="n">
+        <v>0.001443658661932863</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0.3467386855405713</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0.8370247031988155</v>
+      </c>
+      <c r="E350" t="n">
+        <v>0.6107997925433739</v>
+      </c>
+      <c r="F350" t="n">
+        <v>-0.00425685054593488</v>
+      </c>
+      <c r="G350" t="n">
+        <v>-0.04319730922802255</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="B351" t="n">
+        <v>0.001594182695699727</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0.3472577187426392</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0.8347208261913358</v>
+      </c>
+      <c r="E351" t="n">
+        <v>0.6045029302245916</v>
+      </c>
+      <c r="F351" t="n">
+        <v>-0.00409122175111704</v>
+      </c>
+      <c r="G351" t="n">
+        <v>-0.04205045363365213</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B352" t="n">
+        <v>0.001748436967200152</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0.3477952830872091</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0.8322919013946649</v>
+      </c>
+      <c r="E352" t="n">
+        <v>0.5982799944564398</v>
+      </c>
+      <c r="F352" t="n">
+        <v>-0.003931744130808508</v>
+      </c>
+      <c r="G352" t="n">
+        <v>-0.04093457124172591</v>
       </c>
     </row>
   </sheetData>
